--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -44,6 +44,24 @@
     <t>level</t>
   </si>
   <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>ASPD</t>
+  </si>
+  <si>
+    <t>MSPD</t>
+  </si>
+  <si>
     <t>skin_data</t>
   </si>
   <si>
@@ -71,6 +89,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -86,6 +107,24 @@
     <t>等级</t>
   </si>
   <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>魔力</t>
+  </si>
+  <si>
+    <t>护甲</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
     <t>皮肤固定数据</t>
   </si>
   <si>
@@ -119,13 +158,22 @@
     <t>10200001&amp;10300001&amp;11000001</t>
   </si>
   <si>
-    <t>战士</t>
+    <t>冒险者</t>
+  </si>
+  <si>
+    <t>持盾战士-Boss-lv1</t>
   </si>
   <si>
     <t>10100004&amp;10200004&amp;10300004</t>
   </si>
   <si>
     <t>弓箭手</t>
+  </si>
+  <si>
+    <t>强弓手-Boss-lv1</t>
+  </si>
+  <si>
+    <t>连射手-Boss-lv1</t>
   </si>
   <si>
     <t>10100003&amp;10200002&amp;10300002</t>
@@ -162,10 +210,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -628,64 +690,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
@@ -694,10 +756,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
@@ -706,10 +768,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
@@ -718,10 +780,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
@@ -730,10 +792,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
@@ -742,10 +804,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
@@ -754,12 +816,24 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1110,22 +1184,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
     <col min="3" max="3" width="30.125" customWidth="1"/>
-    <col min="4" max="5" width="23.375" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="53.75" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="47.5" customWidth="1"/>
-    <col min="11" max="11" width="42.875" customWidth="1"/>
-    <col min="12" max="12" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="6.375" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="7" width="6.375" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="10" width="8.875" customWidth="1"/>
+    <col min="11" max="11" width="23.375" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="53.75" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="19.375" customWidth="1"/>
+    <col min="16" max="16" width="47.5" customWidth="1"/>
+    <col min="17" max="17" width="42.875" customWidth="1"/>
+    <col min="18" max="18" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1138,99 +1217,153 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1240,17 +1373,17 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="K4">
         <v>2010000</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1260,17 +1393,17 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="K5">
         <v>2010002</v>
       </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1280,541 +1413,707 @@
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="K6">
         <v>2010001</v>
       </c>
-      <c r="H6">
+      <c r="N6">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:17">
+      <c r="A7" s="1">
         <v>1010010001</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>101001</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="F7">
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1">
         <v>1000001</v>
       </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7">
+      <c r="M7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="1">
         <v>1010010001</v>
       </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
+      <c r="Q7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:17">
+      <c r="A8" s="1">
+        <v>1010020001</v>
+      </c>
+      <c r="B8" s="1">
+        <v>101002</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="4">
+        <v>20</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1010020001</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:17">
+      <c r="A9" s="1">
         <v>1020010001</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="1">
         <v>102001</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="F8">
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1">
         <v>1000001</v>
       </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8">
+      <c r="M9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="1">
         <v>1020010001</v>
       </c>
-      <c r="K8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
+      <c r="Q9" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:17">
+      <c r="A10" s="4">
+        <v>1020020001</v>
+      </c>
+      <c r="B10" s="1">
+        <v>102002</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>500</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1020020001</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:17">
+      <c r="A11" s="4">
+        <v>1020030001</v>
+      </c>
+      <c r="B11" s="1">
+        <v>102003</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>500</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1020030001</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:17">
+      <c r="A12" s="1">
         <v>1030010001</v>
       </c>
-      <c r="B9">
+      <c r="B12" s="1">
         <v>103001</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="F9">
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1">
         <v>1000001</v>
       </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9">
+      <c r="M12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="1">
         <v>1030010001</v>
       </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
+      <c r="Q12" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:17">
+      <c r="A13" s="1">
         <v>1030020001</v>
       </c>
-      <c r="B10">
+      <c r="B13" s="1">
         <v>103002</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="F10">
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1">
         <v>1000001</v>
       </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10">
+      <c r="M13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="1">
         <v>1030020001</v>
       </c>
-      <c r="K10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
+      <c r="Q13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:17">
+      <c r="A14" s="2">
         <v>2000000001</v>
       </c>
-      <c r="B11">
+      <c r="B14" s="2">
         <v>101001</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
         <v>9</v>
       </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11">
+      <c r="K14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="2">
         <v>1000001</v>
       </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11">
+      <c r="M14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="2">
         <v>2000000001</v>
       </c>
-      <c r="I11">
+      <c r="O14" s="2">
         <v>5</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
+      <c r="P14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:17">
+      <c r="A15" s="2">
         <v>2000000002</v>
       </c>
-      <c r="B12">
+      <c r="B15" s="2">
         <v>4001</v>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
         <v>9</v>
       </c>
-      <c r="H12">
+      <c r="N15" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I12">
+      <c r="O15" s="2">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
+      <c r="P15" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:17">
+      <c r="A16" s="2">
         <v>2000000003</v>
       </c>
-      <c r="B13">
+      <c r="B16" s="2">
         <v>101001</v>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
         <v>99</v>
       </c>
-      <c r="G13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13">
+      <c r="M16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I13">
+      <c r="O16" s="2">
         <v>6</v>
       </c>
-      <c r="J13">
+      <c r="P16" s="2">
         <v>3</v>
       </c>
-      <c r="K13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
+      <c r="Q16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:15">
+      <c r="A17" s="2">
         <v>2000000004</v>
       </c>
-      <c r="B14">
+      <c r="B17" s="2">
         <v>101001</v>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14">
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
+      <c r="O17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:15">
+      <c r="A18" s="2">
         <v>2000000005</v>
       </c>
-      <c r="B15">
+      <c r="B18" s="2">
         <v>101001</v>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15">
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:15">
+      <c r="A19" s="2">
         <v>2000000006</v>
       </c>
-      <c r="B16">
+      <c r="B19" s="2">
         <v>101001</v>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16">
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:15">
+      <c r="A20" s="2">
         <v>2000000007</v>
       </c>
-      <c r="B17">
+      <c r="B20" s="2">
         <v>101001</v>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17">
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
+      <c r="O20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:15">
+      <c r="A21" s="2">
         <v>2000000008</v>
       </c>
-      <c r="B18">
+      <c r="B21" s="2">
         <v>101001</v>
       </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18">
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:15">
+      <c r="A22" s="2">
         <v>2000000009</v>
       </c>
-      <c r="B19">
+      <c r="B22" s="2">
         <v>101001</v>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="G19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19">
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20">
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:15">
+      <c r="A23" s="2">
         <v>2000000010</v>
       </c>
-      <c r="B20">
+      <c r="B23" s="2">
         <v>101001</v>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20">
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:15">
+      <c r="A24" s="2">
         <v>2000000011</v>
       </c>
-      <c r="B21">
+      <c r="B24" s="2">
         <v>101001</v>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21">
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22">
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:15">
+      <c r="A25" s="2">
         <v>2000000012</v>
       </c>
-      <c r="B22">
+      <c r="B25" s="2">
         <v>101001</v>
       </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22">
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N25" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23">
+      <c r="O25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:15">
+      <c r="A26" s="2">
         <v>2000000013</v>
       </c>
-      <c r="B23">
+      <c r="B26" s="2">
         <v>101001</v>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23">
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N26" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24">
+      <c r="O26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:15">
+      <c r="A27" s="2">
         <v>2000000014</v>
       </c>
-      <c r="B24">
+      <c r="B27" s="2">
         <v>101001</v>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24">
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N27" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25">
+      <c r="O27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:15">
+      <c r="A28" s="2">
         <v>2000000015</v>
       </c>
-      <c r="B25">
+      <c r="B28" s="2">
         <v>101001</v>
       </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25">
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26">
+      <c r="O28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:15">
+      <c r="A29" s="2">
         <v>2000000016</v>
       </c>
-      <c r="B26">
+      <c r="B29" s="2">
         <v>101001</v>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26">
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27">
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:15">
+      <c r="A30" s="2">
         <v>2000000017</v>
       </c>
-      <c r="B27">
+      <c r="B30" s="2">
         <v>101001</v>
       </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27">
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N30" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28">
+      <c r="O30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:15">
+      <c r="A31" s="2">
         <v>2000000018</v>
       </c>
-      <c r="B28">
+      <c r="B31" s="2">
         <v>101001</v>
       </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="G28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28">
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29">
+      <c r="O31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:15">
+      <c r="A32" s="2">
         <v>2000000019</v>
       </c>
-      <c r="B29">
+      <c r="B32" s="2">
         <v>101001</v>
       </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="G29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29">
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:9">
-      <c r="A30">
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+      <c r="A33" s="2">
         <v>2000000020</v>
       </c>
-      <c r="B30">
+      <c r="B33" s="2">
         <v>101001</v>
       </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="G30" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30">
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N33" s="2">
         <v>2000000002</v>
       </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="15" customHeight="1"/>
     <row r="36" ht="15" customHeight="1"/>
@@ -1822,17 +2121,20 @@
     <row r="38" ht="15" customHeight="1"/>
     <row r="39" ht="15" customHeight="1"/>
     <row r="40" ht="15" customHeight="1"/>
-    <row r="72" ht="12" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
     <row r="75" ht="12" customHeight="1"/>
     <row r="76" ht="12" customHeight="1"/>
     <row r="77" ht="12" customHeight="1"/>
     <row r="78" ht="12" customHeight="1"/>
     <row r="79" ht="12" customHeight="1"/>
     <row r="80" ht="12" customHeight="1"/>
+    <row r="81" ht="12" customHeight="1"/>
+    <row r="82" ht="12" customHeight="1"/>
+    <row r="83" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K30" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q33" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -10,7 +10,7 @@
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -155,46 +155,100 @@
     <t>初始创建赠送-忠诚</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11000001&amp;10200003&amp;10300003&amp;</t>
+  </si>
+  <si>
+    <t>冒险者</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10200001&amp;10300001&amp;11020021&amp;</t>
+  </si>
+  <si>
+    <t>持盾战士-Boss-lv1</t>
+  </si>
+  <si>
+    <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
+  </si>
+  <si>
+    <t>弓箭手</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>10200006&amp;10300006&amp;11010002&amp;</t>
+  </si>
+  <si>
+    <t>强弓手-Boss-lv1</t>
+  </si>
+  <si>
+    <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
+  </si>
+  <si>
+    <t>连射手-Boss-lv1</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
+  </si>
+  <si>
+    <t>人类-魔法师（火）</t>
+  </si>
+  <si>
+    <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
+  </si>
+  <si>
+    <t>人类-魔法师（水）</t>
+  </si>
+  <si>
+    <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
+  </si>
+  <si>
+    <t>人类-魔法师（冰）</t>
+  </si>
+  <si>
+    <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
+  </si>
+  <si>
+    <t>人类-魔法师（雷）</t>
+  </si>
+  <si>
+    <t>1050001&amp;1040001&amp;1060004&amp;1030003&amp;</t>
+  </si>
+  <si>
+    <t>11000001&amp;10100002&amp;10300001&amp;10200001&amp;</t>
+  </si>
+  <si>
+    <t>白剑伟</t>
+  </si>
+  <si>
+    <t>宛家伟</t>
+  </si>
+  <si>
     <t>10200001&amp;10300001&amp;11000001</t>
-  </si>
-  <si>
-    <t>冒险者</t>
-  </si>
-  <si>
-    <t>持盾战士-Boss-lv1</t>
-  </si>
-  <si>
-    <t>10100004&amp;10200004&amp;10300004</t>
-  </si>
-  <si>
-    <t>弓箭手</t>
-  </si>
-  <si>
-    <t>强弓手-Boss-lv1</t>
-  </si>
-  <si>
-    <t>连射手-Boss-lv1</t>
-  </si>
-  <si>
-    <t>10100003&amp;10200002&amp;10300002</t>
-  </si>
-  <si>
-    <t>魔法师（火）</t>
-  </si>
-  <si>
-    <t>魔法师（冰）</t>
-  </si>
-  <si>
-    <t>1050001&amp;1040001&amp;1060004&amp;1030003&amp;</t>
-  </si>
-  <si>
-    <t>11000001&amp;10100002&amp;10300001&amp;10200001&amp;</t>
-  </si>
-  <si>
-    <t>白剑伟</t>
-  </si>
-  <si>
-    <t>宛家伟</t>
   </si>
   <si>
     <t>雷神天尊斩</t>
@@ -233,6 +287,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -244,13 +305,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -690,18 +744,18 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -820,7 +874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -830,10 +884,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1184,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1217,22 +1268,22 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1270,22 +1321,22 @@
       <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" t="s">
@@ -1323,22 +1374,22 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>30</v>
       </c>
       <c r="K3" t="s">
@@ -1424,330 +1475,431 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:17">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>1010010001</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>101001</v>
       </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>100</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
-        <v>10</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4">
-        <v>10</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="3">
         <v>1000001</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="1">
+      <c r="M7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="3">
         <v>1010010001</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:17">
+      <c r="A8" s="3">
+        <v>1010020001</v>
+      </c>
+      <c r="B8" s="3">
+        <v>101002</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:17">
-      <c r="A8" s="1">
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1000001</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="3">
         <v>1010020001</v>
       </c>
-      <c r="B8" s="1">
-        <v>101002</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>100</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>1000</v>
-      </c>
-      <c r="H8" s="4">
-        <v>20</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4">
-        <v>10</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:17">
+      <c r="A9" s="3">
+        <v>1020010001</v>
+      </c>
+      <c r="B9" s="3">
+        <v>102001</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>70</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="3">
         <v>1000001</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1010020001</v>
-      </c>
-      <c r="Q8" s="1" t="s">
+      <c r="M9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1020010001</v>
+      </c>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:17">
+      <c r="A10" s="3">
+        <v>1020020001</v>
+      </c>
+      <c r="B10" s="3">
+        <v>102002</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:17">
-      <c r="A9" s="1">
-        <v>1020010001</v>
-      </c>
-      <c r="B9" s="1">
-        <v>102001</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>100</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4">
-        <v>10</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4">
-        <v>10</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="I10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="3">
         <v>1000001</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1020020001</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:17">
+      <c r="A11" s="3">
+        <v>1020030001</v>
+      </c>
+      <c r="B11" s="3">
+        <v>102003</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N9" s="1">
-        <v>1020010001</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+      <c r="J11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:17">
-      <c r="A10" s="4">
-        <v>1020020001</v>
-      </c>
-      <c r="B10" s="1">
-        <v>102002</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>500</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4">
-        <v>10</v>
-      </c>
-      <c r="I10" s="4">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4">
-        <v>10</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="L11" s="3">
         <v>1000001</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1020030001</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:17">
+      <c r="A12" s="3">
+        <v>1030010001</v>
+      </c>
+      <c r="B12" s="3">
+        <v>103001</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="4">
-        <v>1020020001</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:17">
-      <c r="A11" s="4">
-        <v>1020030001</v>
-      </c>
-      <c r="B11" s="1">
-        <v>102003</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>500</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4">
-        <v>10</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1</v>
-      </c>
-      <c r="J11" s="4">
-        <v>10</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="J12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="3">
         <v>1000001</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1030010001</v>
+      </c>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:17">
+      <c r="A13" s="3">
+        <v>1030020001</v>
+      </c>
+      <c r="B13" s="3">
+        <v>103002</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="4">
-        <v>1020030001</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:17">
-      <c r="A12" s="1">
-        <v>1030010001</v>
-      </c>
-      <c r="B12" s="1">
-        <v>103001</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>100</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4">
-        <v>10</v>
-      </c>
-      <c r="I12" s="4">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4">
-        <v>10</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="J13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="3">
         <v>1000001</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1030010001</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:17">
-      <c r="A13" s="1">
+      <c r="M13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="3">
         <v>1030020001</v>
       </c>
-      <c r="B13" s="1">
-        <v>103002</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>100</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4">
-        <v>10</v>
-      </c>
-      <c r="I13" s="4">
-        <v>1</v>
-      </c>
-      <c r="J13" s="4">
-        <v>10</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:17">
+      <c r="A14" s="3">
+        <v>1030030001</v>
+      </c>
+      <c r="B14" s="3">
+        <v>103003</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="3">
         <v>1000001</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1030020001</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:17">
-      <c r="A14" s="2">
-        <v>2000000001</v>
-      </c>
-      <c r="B14" s="2">
-        <v>101001</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>9</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="2">
+      <c r="M14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1030030001</v>
+      </c>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:17">
+      <c r="A15" s="3">
+        <v>1030040001</v>
+      </c>
+      <c r="B15" s="3">
+        <v>103004</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="3">
         <v>1000001</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14" s="2">
-        <v>2000000001</v>
-      </c>
-      <c r="O14" s="2">
-        <v>5</v>
-      </c>
-      <c r="P14" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:17">
-      <c r="A15" s="2">
-        <v>2000000002</v>
-      </c>
-      <c r="B15" s="2">
-        <v>4001</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>9</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2000000002</v>
-      </c>
-      <c r="O15" s="2">
-        <v>5</v>
-      </c>
-      <c r="P15" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>54</v>
+      <c r="M15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1030040001</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:17">
       <c r="A16" s="2">
-        <v>2000000003</v>
+        <v>2000000001</v>
       </c>
       <c r="B16" s="2">
         <v>101001</v>
@@ -1756,47 +1908,57 @@
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>99</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="2"/>
       <c r="M16" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2">
+        <v>2000000001</v>
+      </c>
+      <c r="O16" s="2">
+        <v>5</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:17">
+      <c r="A17" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O16" s="2">
-        <v>6</v>
-      </c>
-      <c r="P16" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:15">
-      <c r="A17" s="2">
-        <v>2000000004</v>
-      </c>
       <c r="B17" s="2">
-        <v>101001</v>
+        <v>4001</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>41</v>
+      <c r="D17" s="2">
+        <v>9</v>
       </c>
       <c r="N17" s="2">
         <v>2000000002</v>
       </c>
       <c r="O17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:15">
+        <v>5</v>
+      </c>
+      <c r="P17" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:17">
       <c r="A18" s="2">
-        <v>2000000005</v>
+        <v>2000000003</v>
       </c>
       <c r="B18" s="2">
         <v>101001</v>
@@ -1804,19 +1966,28 @@
       <c r="C18" s="2">
         <v>2</v>
       </c>
+      <c r="D18" s="2">
+        <v>99</v>
+      </c>
       <c r="M18" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N18" s="2">
         <v>2000000002</v>
       </c>
       <c r="O18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:15">
+        <v>6</v>
+      </c>
+      <c r="P18" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:17">
       <c r="A19" s="2">
-        <v>2000000006</v>
+        <v>2000000004</v>
       </c>
       <c r="B19" s="2">
         <v>101001</v>
@@ -1825,7 +1996,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N19" s="2">
         <v>2000000002</v>
@@ -1834,9 +2005,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:15">
+    <row r="20" s="2" customFormat="1" spans="1:17">
       <c r="A20" s="2">
-        <v>2000000007</v>
+        <v>2000000005</v>
       </c>
       <c r="B20" s="2">
         <v>101001</v>
@@ -1845,7 +2016,7 @@
         <v>2</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N20" s="2">
         <v>2000000002</v>
@@ -1854,9 +2025,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:15">
+    <row r="21" s="2" customFormat="1" spans="1:17">
       <c r="A21" s="2">
-        <v>2000000008</v>
+        <v>2000000006</v>
       </c>
       <c r="B21" s="2">
         <v>101001</v>
@@ -1865,7 +2036,7 @@
         <v>2</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N21" s="2">
         <v>2000000002</v>
@@ -1874,9 +2045,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:15">
+    <row r="22" s="2" customFormat="1" spans="1:17">
       <c r="A22" s="2">
-        <v>2000000009</v>
+        <v>2000000007</v>
       </c>
       <c r="B22" s="2">
         <v>101001</v>
@@ -1885,7 +2056,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N22" s="2">
         <v>2000000002</v>
@@ -1894,9 +2065,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:15">
+    <row r="23" s="2" customFormat="1" spans="1:17">
       <c r="A23" s="2">
-        <v>2000000010</v>
+        <v>2000000008</v>
       </c>
       <c r="B23" s="2">
         <v>101001</v>
@@ -1905,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2">
         <v>2000000002</v>
@@ -1914,9 +2085,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:15">
+    <row r="24" s="2" customFormat="1" spans="1:17">
       <c r="A24" s="2">
-        <v>2000000011</v>
+        <v>2000000009</v>
       </c>
       <c r="B24" s="2">
         <v>101001</v>
@@ -1925,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N24" s="2">
         <v>2000000002</v>
@@ -1934,9 +2105,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:15">
+    <row r="25" s="2" customFormat="1" spans="1:17">
       <c r="A25" s="2">
-        <v>2000000012</v>
+        <v>2000000010</v>
       </c>
       <c r="B25" s="2">
         <v>101001</v>
@@ -1945,7 +2116,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N25" s="2">
         <v>2000000002</v>
@@ -1954,9 +2125,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:15">
+    <row r="26" s="2" customFormat="1" spans="1:17">
       <c r="A26" s="2">
-        <v>2000000013</v>
+        <v>2000000011</v>
       </c>
       <c r="B26" s="2">
         <v>101001</v>
@@ -1965,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N26" s="2">
         <v>2000000002</v>
@@ -1974,9 +2145,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:15">
+    <row r="27" s="2" customFormat="1" spans="1:17">
       <c r="A27" s="2">
-        <v>2000000014</v>
+        <v>2000000012</v>
       </c>
       <c r="B27" s="2">
         <v>101001</v>
@@ -1985,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N27" s="2">
         <v>2000000002</v>
@@ -1994,9 +2165,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:15">
+    <row r="28" s="2" customFormat="1" spans="1:17">
       <c r="A28" s="2">
-        <v>2000000015</v>
+        <v>2000000013</v>
       </c>
       <c r="B28" s="2">
         <v>101001</v>
@@ -2005,7 +2176,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N28" s="2">
         <v>2000000002</v>
@@ -2014,9 +2185,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:15">
+    <row r="29" s="2" customFormat="1" spans="1:17">
       <c r="A29" s="2">
-        <v>2000000016</v>
+        <v>2000000014</v>
       </c>
       <c r="B29" s="2">
         <v>101001</v>
@@ -2025,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N29" s="2">
         <v>2000000002</v>
@@ -2034,9 +2205,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:15">
+    <row r="30" s="2" customFormat="1" spans="1:17">
       <c r="A30" s="2">
-        <v>2000000017</v>
+        <v>2000000015</v>
       </c>
       <c r="B30" s="2">
         <v>101001</v>
@@ -2045,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N30" s="2">
         <v>2000000002</v>
@@ -2054,9 +2225,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:15">
+    <row r="31" s="2" customFormat="1" spans="1:17">
       <c r="A31" s="2">
-        <v>2000000018</v>
+        <v>2000000016</v>
       </c>
       <c r="B31" s="2">
         <v>101001</v>
@@ -2065,7 +2236,7 @@
         <v>2</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N31" s="2">
         <v>2000000002</v>
@@ -2074,9 +2245,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:15">
+    <row r="32" s="2" customFormat="1" spans="1:17">
       <c r="A32" s="2">
-        <v>2000000019</v>
+        <v>2000000017</v>
       </c>
       <c r="B32" s="2">
         <v>101001</v>
@@ -2085,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N32" s="2">
         <v>2000000002</v>
@@ -2094,9 +2265,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+    <row r="33" s="2" customFormat="1" spans="1:15">
       <c r="A33" s="2">
-        <v>2000000020</v>
+        <v>2000000018</v>
       </c>
       <c r="B33" s="2">
         <v>101001</v>
@@ -2105,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="N33" s="2">
         <v>2000000002</v>
@@ -2114,8 +2285,46 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
+    <row r="34" s="2" customFormat="1" spans="1:15">
+      <c r="A34" s="2">
+        <v>2000000019</v>
+      </c>
+      <c r="B34" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N34" s="2">
+        <v>2000000002</v>
+      </c>
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+      <c r="A35" s="2">
+        <v>2000000020</v>
+      </c>
+      <c r="B35" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N35" s="2">
+        <v>2000000002</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="36" ht="15" customHeight="1"/>
     <row r="37" ht="15" customHeight="1"/>
     <row r="38" ht="15" customHeight="1"/>
@@ -2124,8 +2333,8 @@
     <row r="41" ht="15" customHeight="1"/>
     <row r="42" ht="15" customHeight="1"/>
     <row r="43" ht="15" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
+    <row r="45" ht="15" customHeight="1"/>
     <row r="77" ht="12" customHeight="1"/>
     <row r="78" ht="12" customHeight="1"/>
     <row r="79" ht="12" customHeight="1"/>
@@ -2133,8 +2342,10 @@
     <row r="81" ht="12" customHeight="1"/>
     <row r="82" ht="12" customHeight="1"/>
     <row r="83" ht="12" customHeight="1"/>
+    <row r="84" ht="12" customHeight="1"/>
+    <row r="85" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q35" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -234,6 +234,15 @@
   </si>
   <si>
     <t>人类-魔法师（雷）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（火）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（水）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（冰）</t>
   </si>
   <si>
     <t>1050001&amp;1040001&amp;1060004&amp;1030003&amp;</t>
@@ -874,7 +883,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -885,6 +894,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,7 +1247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1897,97 +1909,150 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:17">
-      <c r="A16" s="2">
-        <v>2000000001</v>
-      </c>
-      <c r="B16" s="2">
-        <v>101001</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
-        <v>9</v>
-      </c>
-      <c r="K16" s="2" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:17">
+      <c r="A16" s="3">
+        <v>1031010001</v>
+      </c>
+      <c r="B16" s="3">
+        <v>103001</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1000001</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1031010001</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:17">
+      <c r="A17" s="3">
+        <v>1031010002</v>
+      </c>
+      <c r="B17" s="3">
+        <v>103001</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1000001</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1031010002</v>
+      </c>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N16" s="2">
-        <v>2000000001</v>
-      </c>
-      <c r="O16" s="2">
-        <v>5</v>
-      </c>
-      <c r="P16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:17">
+      <c r="A18" s="3">
+        <v>1031010003</v>
+      </c>
+      <c r="B18" s="3">
+        <v>103001</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1000001</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1031010003</v>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="4" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:17">
-      <c r="A17" s="2">
-        <v>2000000002</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4001</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>9</v>
-      </c>
-      <c r="N17" s="2">
-        <v>2000000002</v>
-      </c>
-      <c r="O17" s="2">
-        <v>5</v>
-      </c>
-      <c r="P17" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:17">
-      <c r="A18" s="2">
-        <v>2000000003</v>
-      </c>
-      <c r="B18" s="2">
-        <v>101001</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>99</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="2">
-        <v>2000000002</v>
-      </c>
-      <c r="O18" s="2">
-        <v>6</v>
-      </c>
-      <c r="P18" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:17">
       <c r="A19" s="2">
-        <v>2000000004</v>
+        <v>2000000001</v>
       </c>
       <c r="B19" s="2">
         <v>101001</v>
@@ -1995,39 +2060,58 @@
       <c r="C19" s="2">
         <v>2</v>
       </c>
+      <c r="D19" s="2">
+        <v>9</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="2"/>
       <c r="M19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="N19" s="2">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="O19" s="2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="P19" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:17">
       <c r="A20" s="2">
-        <v>2000000005</v>
+        <v>2000000002</v>
       </c>
       <c r="B20" s="2">
-        <v>101001</v>
+        <v>4001</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>72</v>
+      <c r="D20" s="2">
+        <v>9</v>
       </c>
       <c r="N20" s="2">
         <v>2000000002</v>
       </c>
       <c r="O20" s="2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="P20" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:17">
       <c r="A21" s="2">
-        <v>2000000006</v>
+        <v>2000000003</v>
       </c>
       <c r="B21" s="2">
         <v>101001</v>
@@ -2035,19 +2119,28 @@
       <c r="C21" s="2">
         <v>2</v>
       </c>
+      <c r="D21" s="2">
+        <v>99</v>
+      </c>
       <c r="M21" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N21" s="2">
         <v>2000000002</v>
       </c>
       <c r="O21" s="2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="P21" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:17">
       <c r="A22" s="2">
-        <v>2000000007</v>
+        <v>2000000004</v>
       </c>
       <c r="B22" s="2">
         <v>101001</v>
@@ -2056,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N22" s="2">
         <v>2000000002</v>
@@ -2067,7 +2160,7 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="1:17">
       <c r="A23" s="2">
-        <v>2000000008</v>
+        <v>2000000005</v>
       </c>
       <c r="B23" s="2">
         <v>101001</v>
@@ -2076,7 +2169,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N23" s="2">
         <v>2000000002</v>
@@ -2087,7 +2180,7 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:17">
       <c r="A24" s="2">
-        <v>2000000009</v>
+        <v>2000000006</v>
       </c>
       <c r="B24" s="2">
         <v>101001</v>
@@ -2096,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N24" s="2">
         <v>2000000002</v>
@@ -2107,7 +2200,7 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="1:17">
       <c r="A25" s="2">
-        <v>2000000010</v>
+        <v>2000000007</v>
       </c>
       <c r="B25" s="2">
         <v>101001</v>
@@ -2116,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N25" s="2">
         <v>2000000002</v>
@@ -2127,7 +2220,7 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="1:17">
       <c r="A26" s="2">
-        <v>2000000011</v>
+        <v>2000000008</v>
       </c>
       <c r="B26" s="2">
         <v>101001</v>
@@ -2136,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N26" s="2">
         <v>2000000002</v>
@@ -2147,7 +2240,7 @@
     </row>
     <row r="27" s="2" customFormat="1" spans="1:17">
       <c r="A27" s="2">
-        <v>2000000012</v>
+        <v>2000000009</v>
       </c>
       <c r="B27" s="2">
         <v>101001</v>
@@ -2156,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N27" s="2">
         <v>2000000002</v>
@@ -2167,7 +2260,7 @@
     </row>
     <row r="28" s="2" customFormat="1" spans="1:17">
       <c r="A28" s="2">
-        <v>2000000013</v>
+        <v>2000000010</v>
       </c>
       <c r="B28" s="2">
         <v>101001</v>
@@ -2176,7 +2269,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N28" s="2">
         <v>2000000002</v>
@@ -2187,7 +2280,7 @@
     </row>
     <row r="29" s="2" customFormat="1" spans="1:17">
       <c r="A29" s="2">
-        <v>2000000014</v>
+        <v>2000000011</v>
       </c>
       <c r="B29" s="2">
         <v>101001</v>
@@ -2196,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N29" s="2">
         <v>2000000002</v>
@@ -2207,7 +2300,7 @@
     </row>
     <row r="30" s="2" customFormat="1" spans="1:17">
       <c r="A30" s="2">
-        <v>2000000015</v>
+        <v>2000000012</v>
       </c>
       <c r="B30" s="2">
         <v>101001</v>
@@ -2216,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N30" s="2">
         <v>2000000002</v>
@@ -2227,7 +2320,7 @@
     </row>
     <row r="31" s="2" customFormat="1" spans="1:17">
       <c r="A31" s="2">
-        <v>2000000016</v>
+        <v>2000000013</v>
       </c>
       <c r="B31" s="2">
         <v>101001</v>
@@ -2236,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N31" s="2">
         <v>2000000002</v>
@@ -2247,7 +2340,7 @@
     </row>
     <row r="32" s="2" customFormat="1" spans="1:17">
       <c r="A32" s="2">
-        <v>2000000017</v>
+        <v>2000000014</v>
       </c>
       <c r="B32" s="2">
         <v>101001</v>
@@ -2256,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N32" s="2">
         <v>2000000002</v>
@@ -2267,7 +2360,7 @@
     </row>
     <row r="33" s="2" customFormat="1" spans="1:15">
       <c r="A33" s="2">
-        <v>2000000018</v>
+        <v>2000000015</v>
       </c>
       <c r="B33" s="2">
         <v>101001</v>
@@ -2276,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N33" s="2">
         <v>2000000002</v>
@@ -2287,7 +2380,7 @@
     </row>
     <row r="34" s="2" customFormat="1" spans="1:15">
       <c r="A34" s="2">
-        <v>2000000019</v>
+        <v>2000000016</v>
       </c>
       <c r="B34" s="2">
         <v>101001</v>
@@ -2296,7 +2389,7 @@
         <v>2</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N34" s="2">
         <v>2000000002</v>
@@ -2305,9 +2398,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+    <row r="35" s="2" customFormat="1" spans="1:15">
       <c r="A35" s="2">
-        <v>2000000020</v>
+        <v>2000000017</v>
       </c>
       <c r="B35" s="2">
         <v>101001</v>
@@ -2316,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N35" s="2">
         <v>2000000002</v>
@@ -2325,9 +2418,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
+    <row r="36" s="2" customFormat="1" spans="1:15">
+      <c r="A36" s="2">
+        <v>2000000018</v>
+      </c>
+      <c r="B36" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N36" s="2">
+        <v>2000000002</v>
+      </c>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:15">
+      <c r="A37" s="2">
+        <v>2000000019</v>
+      </c>
+      <c r="B37" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N37" s="2">
+        <v>2000000002</v>
+      </c>
+      <c r="O37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+      <c r="A38" s="2">
+        <v>2000000020</v>
+      </c>
+      <c r="B38" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N38" s="2">
+        <v>2000000002</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="39" ht="15" customHeight="1"/>
     <row r="40" ht="15" customHeight="1"/>
     <row r="41" ht="15" customHeight="1"/>
@@ -2335,17 +2485,20 @@
     <row r="43" ht="15" customHeight="1"/>
     <row r="44" ht="15" customHeight="1"/>
     <row r="45" ht="15" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
+    <row r="46" ht="15" customHeight="1"/>
+    <row r="47" ht="15" customHeight="1"/>
+    <row r="48" ht="15" customHeight="1"/>
     <row r="80" ht="12" customHeight="1"/>
     <row r="81" ht="12" customHeight="1"/>
     <row r="82" ht="12" customHeight="1"/>
     <row r="83" ht="12" customHeight="1"/>
     <row r="84" ht="12" customHeight="1"/>
     <row r="85" ht="12" customHeight="1"/>
+    <row r="86" ht="12" customHeight="1"/>
+    <row r="87" ht="12" customHeight="1"/>
+    <row r="88" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q35" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q38" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>人类-魔法师（雷）</t>
+  </si>
+  <si>
+    <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
   </si>
   <si>
     <t>人类-大魔法师（火）</t>
@@ -883,7 +886,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -894,9 +897,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1945,15 +1945,15 @@
         <v>1000001</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N16" s="3">
         <v>1031010001</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="4" t="s">
-        <v>68</v>
+      <c r="Q16" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:17">
@@ -1992,15 +1992,15 @@
         <v>1000001</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N17" s="3">
         <v>1031010002</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="4" t="s">
-        <v>69</v>
+      <c r="Q17" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:17">
@@ -2039,15 +2039,15 @@
         <v>1000001</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N18" s="3">
         <v>1031010003</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="4" t="s">
-        <v>70</v>
+      <c r="Q18" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:17">
@@ -2064,11 +2064,11 @@
         <v>9</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N19" s="2">
         <v>2000000001</v>
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:17">
@@ -2106,7 +2106,7 @@
         <v>2</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:17">
@@ -2123,7 +2123,7 @@
         <v>99</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N21" s="2">
         <v>2000000002</v>
@@ -2135,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:17">
@@ -2149,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N22" s="2">
         <v>2000000002</v>
@@ -2169,7 +2169,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N23" s="2">
         <v>2000000002</v>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N24" s="2">
         <v>2000000002</v>
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N25" s="2">
         <v>2000000002</v>
@@ -2229,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N26" s="2">
         <v>2000000002</v>
@@ -2249,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N27" s="2">
         <v>2000000002</v>
@@ -2269,7 +2269,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N28" s="2">
         <v>2000000002</v>
@@ -2289,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N29" s="2">
         <v>2000000002</v>
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N30" s="2">
         <v>2000000002</v>
@@ -2329,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N31" s="2">
         <v>2000000002</v>
@@ -2349,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N32" s="2">
         <v>2000000002</v>
@@ -2369,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N33" s="2">
         <v>2000000002</v>
@@ -2389,7 +2389,7 @@
         <v>2</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N34" s="2">
         <v>2000000002</v>
@@ -2409,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N35" s="2">
         <v>2000000002</v>
@@ -2429,7 +2429,7 @@
         <v>2</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N36" s="2">
         <v>2000000002</v>
@@ -2449,7 +2449,7 @@
         <v>2</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N37" s="2">
         <v>2000000002</v>
@@ -2469,7 +2469,7 @@
         <v>2</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N38" s="2">
         <v>2000000002</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
@@ -1914,7 +1914,7 @@
         <v>1031010001</v>
       </c>
       <c r="B16" s="3">
-        <v>103001</v>
+        <v>103101</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:17">
       <c r="A17" s="3">
-        <v>1031010002</v>
+        <v>1031020001</v>
       </c>
       <c r="B17" s="3">
-        <v>103001</v>
+        <v>103102</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:17">
       <c r="A18" s="3">
-        <v>1031010003</v>
+        <v>1031030001</v>
       </c>
       <c r="B18" s="3">
-        <v>103001</v>
+        <v>103103</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="12705" windowHeight="5655"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12705" windowHeight="5655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$Q$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NpcInfo!$A$1:$R$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
     <t>MSPD</t>
   </si>
   <si>
+    <t>attack_search_range</t>
+  </si>
+  <si>
     <t>skin_data</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>攻击搜索范围</t>
+  </si>
+  <si>
     <t>皮肤固定数据</t>
   </si>
   <si>
@@ -155,18 +161,15 @@
     <t>初始创建赠送-忠诚</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -177,9 +180,6 @@
   </si>
   <si>
     <t>1000</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>10200001&amp;10300001&amp;11020021&amp;</t>
@@ -886,7 +886,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -894,6 +894,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1247,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1257,17 +1260,18 @@
     <col min="6" max="7" width="6.375" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="10" width="8.875" customWidth="1"/>
-    <col min="11" max="11" width="23.375" customWidth="1"/>
-    <col min="12" max="12" width="34" customWidth="1"/>
-    <col min="13" max="13" width="53.75" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="19.375" customWidth="1"/>
-    <col min="16" max="16" width="47.5" customWidth="1"/>
-    <col min="17" max="17" width="42.875" customWidth="1"/>
-    <col min="18" max="18" width="25.125" customWidth="1"/>
+    <col min="11" max="11" width="21.5" customWidth="1"/>
+    <col min="12" max="12" width="23.375" customWidth="1"/>
+    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="14" max="14" width="53.75" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="19.375" customWidth="1"/>
+    <col min="17" max="17" width="47.5" customWidth="1"/>
+    <col min="18" max="18" width="42.875" customWidth="1"/>
+    <col min="19" max="19" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1302,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1319,114 +1323,123 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
         <v>18</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
         <v>31</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1436,17 +1449,17 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>2010000</v>
       </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="R4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1456,17 +1469,17 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>2010002</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>2</v>
       </c>
-      <c r="Q5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1476,581 +1489,613 @@
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>2010001</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="Q6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:17">
-      <c r="A7" s="3">
+      <c r="R6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:18">
+      <c r="A7" s="4">
         <v>1010010001</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>101001</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="G7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" s="4">
+        <v>1010010001</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:18">
+      <c r="A8" s="4">
+        <v>1010020001</v>
+      </c>
+      <c r="B8" s="4">
+        <v>101002</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>200</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4">
+        <v>20</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="3">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="4">
         <v>1000001</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="4">
+        <v>1010020001</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:18">
+      <c r="A9" s="4">
+        <v>1020010001</v>
+      </c>
+      <c r="B9" s="4">
+        <v>102001</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4">
+        <v>70</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="4">
+        <v>5</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="3">
-        <v>1010010001</v>
-      </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:17">
-      <c r="A8" s="3">
-        <v>1010020001</v>
-      </c>
-      <c r="B8" s="3">
-        <v>101002</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>200</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="M9" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1020010001</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:18">
+      <c r="A10" s="4">
+        <v>1020020001</v>
+      </c>
+      <c r="B10" s="4">
+        <v>102002</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="4">
+        <v>5</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1020020001</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:18">
+      <c r="A11" s="4">
+        <v>1020030001</v>
+      </c>
+      <c r="B11" s="4">
+        <v>102003</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="G11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="3">
+      <c r="I11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="4">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" s="4">
         <v>1000001</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1010020001</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:17">
-      <c r="A9" s="3">
-        <v>1020010001</v>
-      </c>
-      <c r="B9" s="3">
-        <v>102001</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
+      <c r="N11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1020030001</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:18">
+      <c r="A12" s="4">
+        <v>1030010001</v>
+      </c>
+      <c r="B12" s="4">
+        <v>103001</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="4">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1030010001</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:18">
+      <c r="A13" s="4">
+        <v>1030020001</v>
+      </c>
+      <c r="B13" s="4">
+        <v>103002</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="4">
+        <v>5</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1030020001</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:18">
+      <c r="A14" s="4">
+        <v>1030030001</v>
+      </c>
+      <c r="B14" s="4">
+        <v>103003</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="4">
+        <v>5</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1030030001</v>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:18">
+      <c r="A15" s="4">
+        <v>1030040001</v>
+      </c>
+      <c r="B15" s="4">
+        <v>103004</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="4">
+        <v>5</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1030040001</v>
+      </c>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:18">
+      <c r="A16" s="4">
+        <v>1031010001</v>
+      </c>
+      <c r="B16" s="4">
+        <v>103101</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="4">
+        <v>5</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O16" s="4">
+        <v>1031010001</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:18">
+      <c r="A17" s="4">
+        <v>1031020001</v>
+      </c>
+      <c r="B17" s="4">
+        <v>103102</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="4">
+        <v>5</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1000001</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1031010002</v>
+      </c>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="3" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:18">
+      <c r="A18" s="4">
+        <v>1031030001</v>
+      </c>
+      <c r="B18" s="4">
+        <v>103103</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="G18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="J18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="3">
+      <c r="K18" s="4">
+        <v>5</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M18" s="4">
         <v>1000001</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1020010001</v>
-      </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:17">
-      <c r="A10" s="3">
-        <v>1020020001</v>
-      </c>
-      <c r="B10" s="3">
-        <v>102002</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1020020001</v>
-      </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:17">
-      <c r="A11" s="3">
-        <v>1020030001</v>
-      </c>
-      <c r="B11" s="3">
-        <v>102003</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1020030001</v>
-      </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:17">
-      <c r="A12" s="3">
-        <v>1030010001</v>
-      </c>
-      <c r="B12" s="3">
-        <v>103001</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1030010001</v>
-      </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:17">
-      <c r="A13" s="3">
-        <v>1030020001</v>
-      </c>
-      <c r="B13" s="3">
-        <v>103002</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1030020001</v>
-      </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:17">
-      <c r="A14" s="3">
-        <v>1030030001</v>
-      </c>
-      <c r="B14" s="3">
-        <v>103003</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1030030001</v>
-      </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:17">
-      <c r="A15" s="3">
-        <v>1030040001</v>
-      </c>
-      <c r="B15" s="3">
-        <v>103004</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1030040001</v>
-      </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:17">
-      <c r="A16" s="3">
-        <v>1031010001</v>
-      </c>
-      <c r="B16" s="3">
-        <v>103101</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="N18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="N16" s="3">
-        <v>1031010001</v>
-      </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:17">
-      <c r="A17" s="3">
-        <v>1031020001</v>
-      </c>
-      <c r="B17" s="3">
-        <v>103102</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1031010002</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:17">
-      <c r="A18" s="3">
-        <v>1031030001</v>
-      </c>
-      <c r="B18" s="3">
-        <v>103103</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="4">
         <v>1031010003</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3" t="s">
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:17">
+    <row r="19" s="2" customFormat="1" spans="1:18">
       <c r="A19" s="2">
         <v>2000000001</v>
       </c>
@@ -2063,27 +2108,27 @@
       <c r="D19" s="2">
         <v>9</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N19" s="2">
+      <c r="O19" s="2">
         <v>2000000001</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>5</v>
       </c>
-      <c r="P19" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="2" t="s">
+      <c r="Q19" s="2">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:17">
+    <row r="20" s="2" customFormat="1" spans="1:18">
       <c r="A20" s="2">
         <v>2000000002</v>
       </c>
@@ -2096,20 +2141,20 @@
       <c r="D20" s="2">
         <v>9</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>5</v>
       </c>
-      <c r="P20" s="2">
+      <c r="Q20" s="2">
         <v>2</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:17">
+    <row r="21" s="2" customFormat="1" spans="1:18">
       <c r="A21" s="2">
         <v>2000000003</v>
       </c>
@@ -2122,23 +2167,23 @@
       <c r="D21" s="2">
         <v>99</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N21" s="2">
+      <c r="O21" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O21" s="2">
+      <c r="P21" s="2">
         <v>6</v>
       </c>
-      <c r="P21" s="2">
+      <c r="Q21" s="2">
         <v>3</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:17">
+    <row r="22" s="2" customFormat="1" spans="1:18">
       <c r="A22" s="2">
         <v>2000000004</v>
       </c>
@@ -2148,17 +2193,17 @@
       <c r="C22" s="2">
         <v>2</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N22" s="2">
+      <c r="O22" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:17">
+      <c r="P22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:18">
       <c r="A23" s="2">
         <v>2000000005</v>
       </c>
@@ -2168,17 +2213,17 @@
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N23" s="2">
+      <c r="O23" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:17">
+      <c r="P23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:18">
       <c r="A24" s="2">
         <v>2000000006</v>
       </c>
@@ -2188,17 +2233,17 @@
       <c r="C24" s="2">
         <v>2</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N24" s="2">
+      <c r="O24" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:17">
+      <c r="P24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:18">
       <c r="A25" s="2">
         <v>2000000007</v>
       </c>
@@ -2208,17 +2253,17 @@
       <c r="C25" s="2">
         <v>2</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N25" s="2">
+      <c r="O25" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:17">
+      <c r="P25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:18">
       <c r="A26" s="2">
         <v>2000000008</v>
       </c>
@@ -2228,17 +2273,17 @@
       <c r="C26" s="2">
         <v>2</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N26" s="2">
+      <c r="O26" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:17">
+      <c r="P26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:18">
       <c r="A27" s="2">
         <v>2000000009</v>
       </c>
@@ -2248,17 +2293,17 @@
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N27" s="2">
+      <c r="O27" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:17">
+      <c r="P27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:18">
       <c r="A28" s="2">
         <v>2000000010</v>
       </c>
@@ -2268,17 +2313,17 @@
       <c r="C28" s="2">
         <v>2</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N28" s="2">
+      <c r="O28" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:17">
+      <c r="P28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:18">
       <c r="A29" s="2">
         <v>2000000011</v>
       </c>
@@ -2288,17 +2333,17 @@
       <c r="C29" s="2">
         <v>2</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N29" s="2">
+      <c r="O29" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:17">
+      <c r="P29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:18">
       <c r="A30" s="2">
         <v>2000000012</v>
       </c>
@@ -2308,17 +2353,17 @@
       <c r="C30" s="2">
         <v>2</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:17">
+      <c r="P30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="1:18">
       <c r="A31" s="2">
         <v>2000000013</v>
       </c>
@@ -2328,17 +2373,17 @@
       <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N31" s="2">
+      <c r="O31" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:17">
+      <c r="P31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:18">
       <c r="A32" s="2">
         <v>2000000014</v>
       </c>
@@ -2348,17 +2393,17 @@
       <c r="C32" s="2">
         <v>2</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N32" s="2">
+      <c r="O32" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:15">
+      <c r="P32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="1:16">
       <c r="A33" s="2">
         <v>2000000015</v>
       </c>
@@ -2368,17 +2413,17 @@
       <c r="C33" s="2">
         <v>2</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N33" s="2">
+      <c r="O33" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:15">
+      <c r="P33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="1:16">
       <c r="A34" s="2">
         <v>2000000016</v>
       </c>
@@ -2388,17 +2433,17 @@
       <c r="C34" s="2">
         <v>2</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O34" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:15">
+      <c r="P34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="1:16">
       <c r="A35" s="2">
         <v>2000000017</v>
       </c>
@@ -2408,17 +2453,17 @@
       <c r="C35" s="2">
         <v>2</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N35" s="2">
+      <c r="O35" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O35" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:15">
+      <c r="P35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:16">
       <c r="A36" s="2">
         <v>2000000018</v>
       </c>
@@ -2428,17 +2473,17 @@
       <c r="C36" s="2">
         <v>2</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N36" s="2">
+      <c r="O36" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O36" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:15">
+      <c r="P36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:16">
       <c r="A37" s="2">
         <v>2000000019</v>
       </c>
@@ -2448,17 +2493,17 @@
       <c r="C37" s="2">
         <v>2</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N37" s="2">
+      <c r="O37" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O37" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" ht="15" customHeight="1" spans="1:15">
+      <c r="P37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="15" customHeight="1" spans="1:16">
       <c r="A38" s="2">
         <v>2000000020</v>
       </c>
@@ -2468,13 +2513,13 @@
       <c r="C38" s="2">
         <v>2</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>2000000002</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2498,7 +2543,7 @@
     <row r="87" ht="12" customHeight="1"/>
     <row r="88" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q38" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R38" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t>冒险者</t>
-  </si>
-  <si>
-    <t>1000</t>
   </si>
   <si>
     <t>10200001&amp;10300001&amp;11020021&amp;</t>
@@ -1564,8 +1561,8 @@
       <c r="F8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>49</v>
+      <c r="G8" s="4">
+        <v>1000</v>
       </c>
       <c r="H8" s="4">
         <v>20</v>
@@ -1573,8 +1570,8 @@
       <c r="I8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>45</v>
+      <c r="J8" s="4">
+        <v>5</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
@@ -1584,7 +1581,7 @@
         <v>1000001</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O8" s="4">
         <v>1010020001</v>
@@ -1592,7 +1589,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:18">
@@ -1634,7 +1631,7 @@
         <v>1000001</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O9" s="4">
         <v>1020010001</v>
@@ -1642,7 +1639,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:18">
@@ -1657,7 +1654,7 @@
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>43</v>
@@ -1684,7 +1681,7 @@
         <v>1000001</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O10" s="4">
         <v>1020020001</v>
@@ -1692,7 +1689,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:18">
@@ -1707,7 +1704,7 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>43</v>
@@ -1734,7 +1731,7 @@
         <v>1000001</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O11" s="4">
         <v>1020030001</v>
@@ -1742,7 +1739,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:18">
@@ -1757,7 +1754,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>43</v>
@@ -1784,7 +1781,7 @@
         <v>1000001</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O12" s="4">
         <v>1030010001</v>
@@ -1792,7 +1789,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:18">
@@ -1807,7 +1804,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>43</v>
@@ -1834,7 +1831,7 @@
         <v>1000001</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O13" s="4">
         <v>1030020001</v>
@@ -1842,7 +1839,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:18">
@@ -1857,7 +1854,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>43</v>
@@ -1884,7 +1881,7 @@
         <v>1000001</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O14" s="4">
         <v>1030030001</v>
@@ -1892,7 +1889,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:18">
@@ -1907,7 +1904,7 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>43</v>
@@ -1934,7 +1931,7 @@
         <v>1000001</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O15" s="4">
         <v>1030040001</v>
@@ -1942,7 +1939,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:18">
@@ -1957,7 +1954,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>43</v>
@@ -1984,7 +1981,7 @@
         <v>1000001</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O16" s="4">
         <v>1031010001</v>
@@ -1992,7 +1989,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:18">
@@ -2007,7 +2004,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>43</v>
@@ -2034,7 +2031,7 @@
         <v>1000001</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O17" s="4">
         <v>1031010002</v>
@@ -2042,7 +2039,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:18">
@@ -2057,7 +2054,7 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>43</v>
@@ -2084,7 +2081,7 @@
         <v>1000001</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O18" s="4">
         <v>1031010003</v>
@@ -2092,7 +2089,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:18">
@@ -2109,11 +2106,11 @@
         <v>9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O19" s="2">
         <v>2000000001</v>
@@ -2125,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:18">
@@ -2151,7 +2148,7 @@
         <v>2</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:18">
@@ -2168,7 +2165,7 @@
         <v>99</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O21" s="2">
         <v>2000000002</v>
@@ -2180,7 +2177,7 @@
         <v>3</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:18">
@@ -2194,7 +2191,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O22" s="2">
         <v>2000000002</v>
@@ -2214,7 +2211,7 @@
         <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O23" s="2">
         <v>2000000002</v>
@@ -2234,7 +2231,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O24" s="2">
         <v>2000000002</v>
@@ -2254,7 +2251,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O25" s="2">
         <v>2000000002</v>
@@ -2274,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O26" s="2">
         <v>2000000002</v>
@@ -2294,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O27" s="2">
         <v>2000000002</v>
@@ -2314,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O28" s="2">
         <v>2000000002</v>
@@ -2334,7 +2331,7 @@
         <v>2</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O29" s="2">
         <v>2000000002</v>
@@ -2354,7 +2351,7 @@
         <v>2</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O30" s="2">
         <v>2000000002</v>
@@ -2374,7 +2371,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O31" s="2">
         <v>2000000002</v>
@@ -2394,7 +2391,7 @@
         <v>2</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O32" s="2">
         <v>2000000002</v>
@@ -2414,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O33" s="2">
         <v>2000000002</v>
@@ -2434,7 +2431,7 @@
         <v>2</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O34" s="2">
         <v>2000000002</v>
@@ -2454,7 +2451,7 @@
         <v>2</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O35" s="2">
         <v>2000000002</v>
@@ -2474,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O36" s="2">
         <v>2000000002</v>
@@ -2494,7 +2491,7 @@
         <v>2</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O37" s="2">
         <v>2000000002</v>
@@ -2514,7 +2511,7 @@
         <v>2</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O38" s="2">
         <v>2000000002</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1571,7 +1571,7 @@
         <v>44</v>
       </c>
       <c r="J8" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -122,7 +122,7 @@
     <t>攻击力</t>
   </si>
   <si>
-    <t>攻击间隔</t>
+    <t>攻击速度</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>10</t>
@@ -1519,21 +1516,21 @@
       <c r="H7" s="4">
         <v>5</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M7" s="4">
         <v>1000001</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O7" s="4">
         <v>1010010001</v>
@@ -1541,7 +1538,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:18">
@@ -1567,21 +1564,21 @@
       <c r="H8" s="4">
         <v>20</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>44</v>
+      <c r="I8" s="4">
+        <v>0</v>
       </c>
       <c r="J8" s="4">
         <v>8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M8" s="4">
         <v>1000001</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O8" s="4">
         <v>1010020001</v>
@@ -1589,7 +1586,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:18">
@@ -1615,23 +1612,23 @@
       <c r="H9" s="4">
         <v>5</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M9" s="4">
         <v>1000001</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O9" s="4">
         <v>1020010001</v>
@@ -1639,7 +1636,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:18">
@@ -1654,7 +1651,7 @@
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>43</v>
@@ -1663,25 +1660,25 @@
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
       <c r="J10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K10" s="4">
         <v>5</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4">
         <v>1000001</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O10" s="4">
         <v>1020020001</v>
@@ -1689,7 +1686,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:18">
@@ -1704,7 +1701,7 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>43</v>
@@ -1713,25 +1710,25 @@
         <v>43</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
       <c r="J11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K11" s="4">
         <v>5</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M11" s="4">
         <v>1000001</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O11" s="4">
         <v>1020030001</v>
@@ -1739,7 +1736,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:18">
@@ -1754,7 +1751,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>43</v>
@@ -1763,25 +1760,25 @@
         <v>43</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
       <c r="J12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M12" s="4">
         <v>1000001</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O12" s="4">
         <v>1030010001</v>
@@ -1789,7 +1786,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:18">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>43</v>
@@ -1813,25 +1810,25 @@
         <v>43</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
       <c r="J13" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M13" s="4">
         <v>1000001</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O13" s="4">
         <v>1030020001</v>
@@ -1839,7 +1836,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:18">
@@ -1854,7 +1851,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>43</v>
@@ -1863,25 +1860,25 @@
         <v>43</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
       <c r="J14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K14" s="4">
         <v>5</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M14" s="4">
         <v>1000001</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O14" s="4">
         <v>1030030001</v>
@@ -1889,7 +1886,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:18">
@@ -1904,7 +1901,7 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>43</v>
@@ -1913,25 +1910,25 @@
         <v>43</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
       <c r="J15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K15" s="4">
         <v>5</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M15" s="4">
         <v>1000001</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O15" s="4">
         <v>1030040001</v>
@@ -1939,7 +1936,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:18">
@@ -1954,7 +1951,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>43</v>
@@ -1963,25 +1960,25 @@
         <v>43</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
       <c r="J16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K16" s="4">
         <v>5</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M16" s="4">
         <v>1000001</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O16" s="4">
         <v>1031010001</v>
@@ -1989,7 +1986,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:18">
@@ -2004,7 +2001,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>43</v>
@@ -2013,25 +2010,25 @@
         <v>43</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
       <c r="J17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K17" s="4">
         <v>5</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M17" s="4">
         <v>1000001</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O17" s="4">
         <v>1031010002</v>
@@ -2039,7 +2036,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:18">
@@ -2054,7 +2051,7 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>43</v>
@@ -2063,25 +2060,25 @@
         <v>43</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K18" s="4">
         <v>5</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M18" s="4">
         <v>1000001</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O18" s="4">
         <v>1031010003</v>
@@ -2089,7 +2086,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:18">
@@ -2106,11 +2103,11 @@
         <v>9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O19" s="2">
         <v>2000000001</v>
@@ -2122,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:18">
@@ -2148,7 +2145,7 @@
         <v>2</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:18">
@@ -2165,7 +2162,7 @@
         <v>99</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O21" s="2">
         <v>2000000002</v>
@@ -2177,7 +2174,7 @@
         <v>3</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:18">
@@ -2191,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O22" s="2">
         <v>2000000002</v>
@@ -2211,7 +2208,7 @@
         <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O23" s="2">
         <v>2000000002</v>
@@ -2231,7 +2228,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O24" s="2">
         <v>2000000002</v>
@@ -2251,7 +2248,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O25" s="2">
         <v>2000000002</v>
@@ -2271,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O26" s="2">
         <v>2000000002</v>
@@ -2291,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O27" s="2">
         <v>2000000002</v>
@@ -2311,7 +2308,7 @@
         <v>2</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O28" s="2">
         <v>2000000002</v>
@@ -2331,7 +2328,7 @@
         <v>2</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O29" s="2">
         <v>2000000002</v>
@@ -2351,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O30" s="2">
         <v>2000000002</v>
@@ -2371,7 +2368,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O31" s="2">
         <v>2000000002</v>
@@ -2391,7 +2388,7 @@
         <v>2</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O32" s="2">
         <v>2000000002</v>
@@ -2411,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O33" s="2">
         <v>2000000002</v>
@@ -2431,7 +2428,7 @@
         <v>2</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O34" s="2">
         <v>2000000002</v>
@@ -2451,7 +2448,7 @@
         <v>2</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O35" s="2">
         <v>2000000002</v>
@@ -2471,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O36" s="2">
         <v>2000000002</v>
@@ -2491,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O37" s="2">
         <v>2000000002</v>
@@ -2511,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O38" s="2">
         <v>2000000002</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
     <t>11000001&amp;10200003&amp;10300003&amp;</t>
   </si>
   <si>
-    <t>0.95,1.05</t>
+    <t>0.9,1.1</t>
   </si>
   <si>
     <t>冒险者</t>
@@ -2055,7 +2055,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="1">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>52</v>
@@ -2479,7 +2479,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="1">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>70</v>
@@ -2532,7 +2532,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="1">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="S17" s="4" t="s">
         <v>71</v>
@@ -2585,7 +2585,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="1">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>72</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcInfo" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -86,6 +86,9 @@
     <t>body_size</t>
   </si>
   <si>
+    <t>attack_mode_ext</t>
+  </si>
+  <si>
     <t>remark</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>体型大小（空或0=默认1倍；"0.9,1.1"=区间随机；"1.1"=固定倍数；最终在目标大小基础上相乘）</t>
   </si>
   <si>
+    <t>Boss额外技能(AttackModeExtInfo的id,多个用,分隔)</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -186,6 +192,9 @@
   </si>
   <si>
     <t>10200001&amp;10300001&amp;11020021&amp;</t>
+  </si>
+  <si>
+    <t>100001</t>
   </si>
   <si>
     <t>持盾战士-Boss-lv1</t>
@@ -1701,7 +1710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S171"/>
+  <dimension ref="A1:T171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" style="3" customWidth="1"/>
@@ -1722,7 +1731,7 @@
     <col min="19" max="19" width="25.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1780,126 +1789,135 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="P2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" t="s">
-        <v>20</v>
-      </c>
       <c r="Q2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1915,11 +1933,11 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1935,11 +1953,11 @@
       <c r="O5">
         <v>2</v>
       </c>
-      <c r="S5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1955,11 +1973,11 @@
       <c r="O6">
         <v>3</v>
       </c>
-      <c r="S6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:19">
+      <c r="T6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:20">
       <c r="A7" s="4">
         <v>1010010001</v>
       </c>
@@ -1974,10 +1992,10 @@
         <v>100</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="4">
         <v>5</v>
@@ -1986,17 +2004,17 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M7" s="4">
         <v>1000001</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O7" s="4">
         <v>1010010001</v>
@@ -2004,13 +2022,13 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:20">
       <c r="A8" s="4">
         <v>1010020001</v>
       </c>
@@ -2025,7 +2043,7 @@
         <v>200</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="4">
         <v>1000</v>
@@ -2041,13 +2059,13 @@
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" s="4">
         <v>1000001</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O8" s="4">
         <v>1010020001</v>
@@ -2057,11 +2075,14 @@
       <c r="R8" s="1">
         <v>1.2</v>
       </c>
-      <c r="S8" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:19">
+      <c r="S8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:20">
       <c r="A9" s="4">
         <v>1020010001</v>
       </c>
@@ -2076,10 +2097,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9" s="4">
         <v>5</v>
@@ -2088,19 +2109,19 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M9" s="4">
         <v>1000001</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O9" s="4">
         <v>1020010001</v>
@@ -2108,13 +2129,13 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:20">
       <c r="A10" s="4">
         <v>1020020001</v>
       </c>
@@ -2126,34 +2147,34 @@
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K10" s="4">
         <v>5</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" s="4">
         <v>1000001</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O10" s="4">
         <v>1020020001</v>
@@ -2161,13 +2182,13 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:20">
       <c r="A11" s="4">
         <v>1020030001</v>
       </c>
@@ -2179,34 +2200,34 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K11" s="4">
         <v>5</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M11" s="4">
         <v>1000001</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O11" s="4">
         <v>1020030001</v>
@@ -2214,13 +2235,13 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:20">
       <c r="A12" s="4">
         <v>1030010001</v>
       </c>
@@ -2232,34 +2253,34 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M12" s="4">
         <v>1000001</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O12" s="4">
         <v>1030010001</v>
@@ -2267,13 +2288,13 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:20">
       <c r="A13" s="4">
         <v>1030020001</v>
       </c>
@@ -2285,34 +2306,34 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="4">
         <v>1000001</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O13" s="4">
         <v>1030020001</v>
@@ -2320,13 +2341,13 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:20">
       <c r="A14" s="4">
         <v>1030030001</v>
       </c>
@@ -2338,34 +2359,34 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K14" s="4">
         <v>5</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" s="4">
         <v>1000001</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O14" s="4">
         <v>1030030001</v>
@@ -2373,13 +2394,13 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:20">
       <c r="A15" s="4">
         <v>1030040001</v>
       </c>
@@ -2391,34 +2412,34 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K15" s="4">
         <v>5</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M15" s="4">
         <v>1000001</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O15" s="4">
         <v>1030040001</v>
@@ -2426,13 +2447,13 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:19">
+        <v>51</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:20">
       <c r="A16" s="4">
         <v>1031010001</v>
       </c>
@@ -2444,34 +2465,34 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K16" s="4">
         <v>5</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M16" s="4">
         <v>1000001</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O16" s="4">
         <v>1031010001</v>
@@ -2481,11 +2502,11 @@
       <c r="R16" s="1">
         <v>1.2</v>
       </c>
-      <c r="S16" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:19">
+      <c r="T16" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:20">
       <c r="A17" s="4">
         <v>1031020001</v>
       </c>
@@ -2497,34 +2518,34 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K17" s="4">
         <v>5</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M17" s="4">
         <v>1000001</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O17" s="4">
         <v>1031010002</v>
@@ -2534,11 +2555,11 @@
       <c r="R17" s="1">
         <v>1.2</v>
       </c>
-      <c r="S17" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:19">
+      <c r="T17" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:20">
       <c r="A18" s="4">
         <v>1031030001</v>
       </c>
@@ -2550,34 +2571,34 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" s="4">
         <v>5</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M18" s="4">
         <v>1000001</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O18" s="4">
         <v>1031010003</v>
@@ -2587,11 +2608,11 @@
       <c r="R18" s="1">
         <v>1.2</v>
       </c>
-      <c r="S18" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:19">
+      <c r="T18" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:20">
       <c r="A19" s="2">
         <v>2000000001</v>
       </c>
@@ -2605,11 +2626,11 @@
         <v>9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O19" s="2">
         <v>2000000001</v>
@@ -2620,11 +2641,11 @@
       <c r="Q19" s="2">
         <v>1</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:19">
+      <c r="T19" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:20">
       <c r="A20" s="2">
         <v>2000000002</v>
       </c>
@@ -2646,11 +2667,11 @@
       <c r="Q20" s="2">
         <v>2</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:19">
+      <c r="T20" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:20">
       <c r="A21" s="2">
         <v>2000000003</v>
       </c>
@@ -2664,7 +2685,7 @@
         <v>99</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2">
         <v>2000000002</v>
@@ -2675,11 +2696,11 @@
       <c r="Q21" s="2">
         <v>3</v>
       </c>
-      <c r="S21" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:19">
+      <c r="T21" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:20">
       <c r="A22">
         <v>3000010011</v>
       </c>
@@ -2701,11 +2722,11 @@
       <c r="P22">
         <v>1</v>
       </c>
-      <c r="S22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:19">
+      <c r="T22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:20">
       <c r="A23">
         <v>3000010012</v>
       </c>
@@ -2727,11 +2748,11 @@
       <c r="P23">
         <v>2</v>
       </c>
-      <c r="S23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:19">
+      <c r="T23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:20">
       <c r="A24">
         <v>3000010013</v>
       </c>
@@ -2753,11 +2774,11 @@
       <c r="P24">
         <v>3</v>
       </c>
-      <c r="S24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:19">
+      <c r="T24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:20">
       <c r="A25">
         <v>3000010014</v>
       </c>
@@ -2779,11 +2800,11 @@
       <c r="P25">
         <v>4</v>
       </c>
-      <c r="S25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:19">
+      <c r="T25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:20">
       <c r="A26">
         <v>3000010015</v>
       </c>
@@ -2805,11 +2826,11 @@
       <c r="P26">
         <v>5</v>
       </c>
-      <c r="S26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:19">
+      <c r="T26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:20">
       <c r="A27">
         <v>3000010021</v>
       </c>
@@ -2831,11 +2852,11 @@
       <c r="P27">
         <v>1</v>
       </c>
-      <c r="S27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19">
+      <c r="T27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:20">
       <c r="A28">
         <v>3000010022</v>
       </c>
@@ -2857,11 +2878,11 @@
       <c r="P28">
         <v>2</v>
       </c>
-      <c r="S28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:19">
+      <c r="T28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:20">
       <c r="A29">
         <v>3000010023</v>
       </c>
@@ -2883,11 +2904,11 @@
       <c r="P29">
         <v>3</v>
       </c>
-      <c r="S29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19">
+      <c r="T29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:20">
       <c r="A30">
         <v>3000010024</v>
       </c>
@@ -2909,11 +2930,11 @@
       <c r="P30">
         <v>4</v>
       </c>
-      <c r="S30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:19">
+      <c r="T30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:20">
       <c r="A31">
         <v>3000010025</v>
       </c>
@@ -2935,11 +2956,11 @@
       <c r="P31">
         <v>5</v>
       </c>
-      <c r="S31" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="T31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>3000010031</v>
       </c>
@@ -2961,11 +2982,11 @@
       <c r="P32">
         <v>1</v>
       </c>
-      <c r="S32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="T32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33">
         <v>3000010032</v>
       </c>
@@ -2987,11 +3008,11 @@
       <c r="P33">
         <v>2</v>
       </c>
-      <c r="S33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="T33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34">
         <v>3000010033</v>
       </c>
@@ -3013,11 +3034,11 @@
       <c r="P34">
         <v>3</v>
       </c>
-      <c r="S34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="T34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>3000010034</v>
       </c>
@@ -3039,11 +3060,11 @@
       <c r="P35">
         <v>4</v>
       </c>
-      <c r="S35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36">
         <v>3000010035</v>
       </c>
@@ -3065,11 +3086,11 @@
       <c r="P36">
         <v>5</v>
       </c>
-      <c r="S36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="T36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37">
         <v>3000010041</v>
       </c>
@@ -3091,11 +3112,11 @@
       <c r="P37">
         <v>1</v>
       </c>
-      <c r="S37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="T37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38">
         <v>3000010042</v>
       </c>
@@ -3117,11 +3138,11 @@
       <c r="P38">
         <v>2</v>
       </c>
-      <c r="S38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="T38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39">
         <v>3000010043</v>
       </c>
@@ -3143,11 +3164,11 @@
       <c r="P39">
         <v>3</v>
       </c>
-      <c r="S39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="T39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40">
         <v>3000010044</v>
       </c>
@@ -3169,11 +3190,11 @@
       <c r="P40">
         <v>4</v>
       </c>
-      <c r="S40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="T40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41">
         <v>3000010045</v>
       </c>
@@ -3195,11 +3216,11 @@
       <c r="P41">
         <v>5</v>
       </c>
-      <c r="S41" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="T41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42">
         <v>3000020011</v>
       </c>
@@ -3221,11 +3242,11 @@
       <c r="P42">
         <v>1</v>
       </c>
-      <c r="S42" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="T42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43">
         <v>3000020012</v>
       </c>
@@ -3247,11 +3268,11 @@
       <c r="P43">
         <v>2</v>
       </c>
-      <c r="S43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
+      <c r="T43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44">
         <v>3000020013</v>
       </c>
@@ -3273,11 +3294,11 @@
       <c r="P44">
         <v>3</v>
       </c>
-      <c r="S44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="T44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45">
         <v>3000020014</v>
       </c>
@@ -3299,11 +3320,11 @@
       <c r="P45">
         <v>4</v>
       </c>
-      <c r="S45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="T45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46">
         <v>3000020015</v>
       </c>
@@ -3325,11 +3346,11 @@
       <c r="P46">
         <v>5</v>
       </c>
-      <c r="S46" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19">
+      <c r="T46" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47">
         <v>3000020021</v>
       </c>
@@ -3351,11 +3372,11 @@
       <c r="P47">
         <v>1</v>
       </c>
-      <c r="S47" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="T47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48">
         <v>3000020022</v>
       </c>
@@ -3377,11 +3398,11 @@
       <c r="P48">
         <v>2</v>
       </c>
-      <c r="S48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="T48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49">
         <v>3000020023</v>
       </c>
@@ -3403,11 +3424,11 @@
       <c r="P49">
         <v>3</v>
       </c>
-      <c r="S49" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="T49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50">
         <v>3000020024</v>
       </c>
@@ -3429,11 +3450,11 @@
       <c r="P50">
         <v>4</v>
       </c>
-      <c r="S50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="T50" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51">
         <v>3000020025</v>
       </c>
@@ -3455,11 +3476,11 @@
       <c r="P51">
         <v>5</v>
       </c>
-      <c r="S51" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="T51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52">
         <v>3000020031</v>
       </c>
@@ -3481,11 +3502,11 @@
       <c r="P52">
         <v>1</v>
       </c>
-      <c r="S52" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19">
+      <c r="T52" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53">
         <v>3000020032</v>
       </c>
@@ -3507,11 +3528,11 @@
       <c r="P53">
         <v>2</v>
       </c>
-      <c r="S53" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="T53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54">
         <v>3000020033</v>
       </c>
@@ -3533,11 +3554,11 @@
       <c r="P54">
         <v>3</v>
       </c>
-      <c r="S54" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="T54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55">
         <v>3000020034</v>
       </c>
@@ -3559,11 +3580,11 @@
       <c r="P55">
         <v>4</v>
       </c>
-      <c r="S55" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="T55" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56">
         <v>3000020035</v>
       </c>
@@ -3585,11 +3606,11 @@
       <c r="P56">
         <v>5</v>
       </c>
-      <c r="S56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="T56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57">
         <v>3000020041</v>
       </c>
@@ -3611,11 +3632,11 @@
       <c r="P57">
         <v>1</v>
       </c>
-      <c r="S57" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="T57" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58">
         <v>3000020042</v>
       </c>
@@ -3637,11 +3658,11 @@
       <c r="P58">
         <v>2</v>
       </c>
-      <c r="S58" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="T58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59">
         <v>3000020043</v>
       </c>
@@ -3663,11 +3684,11 @@
       <c r="P59">
         <v>3</v>
       </c>
-      <c r="S59" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="T59" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60">
         <v>3000020044</v>
       </c>
@@ -3689,11 +3710,11 @@
       <c r="P60">
         <v>4</v>
       </c>
-      <c r="S60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="T60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61">
         <v>3000020045</v>
       </c>
@@ -3715,11 +3736,11 @@
       <c r="P61">
         <v>5</v>
       </c>
-      <c r="S61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19">
+      <c r="T61" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
       <c r="A62">
         <v>3000030011</v>
       </c>
@@ -3741,11 +3762,11 @@
       <c r="P62">
         <v>1</v>
       </c>
-      <c r="S62" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" ht="12" customHeight="1" spans="1:19">
+      <c r="T62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" ht="12" customHeight="1" spans="1:20">
       <c r="A63">
         <v>3000030012</v>
       </c>
@@ -3767,11 +3788,11 @@
       <c r="P63">
         <v>2</v>
       </c>
-      <c r="S63" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" ht="12" customHeight="1" spans="1:19">
+      <c r="T63" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" ht="12" customHeight="1" spans="1:20">
       <c r="A64">
         <v>3000030013</v>
       </c>
@@ -3793,11 +3814,11 @@
       <c r="P64">
         <v>3</v>
       </c>
-      <c r="S64" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" ht="12" customHeight="1" spans="1:19">
+      <c r="T64" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" ht="12" customHeight="1" spans="1:20">
       <c r="A65">
         <v>3000030014</v>
       </c>
@@ -3819,11 +3840,11 @@
       <c r="P65">
         <v>4</v>
       </c>
-      <c r="S65" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="66" ht="12" customHeight="1" spans="1:19">
+      <c r="T65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" ht="12" customHeight="1" spans="1:20">
       <c r="A66">
         <v>3000030015</v>
       </c>
@@ -3845,11 +3866,11 @@
       <c r="P66">
         <v>5</v>
       </c>
-      <c r="S66" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="67" ht="12" customHeight="1" spans="1:19">
+      <c r="T66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" ht="12" customHeight="1" spans="1:20">
       <c r="A67">
         <v>3000030021</v>
       </c>
@@ -3871,11 +3892,11 @@
       <c r="P67">
         <v>1</v>
       </c>
-      <c r="S67" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="68" ht="12" customHeight="1" spans="1:19">
+      <c r="T67" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="68" ht="12" customHeight="1" spans="1:20">
       <c r="A68">
         <v>3000030022</v>
       </c>
@@ -3897,11 +3918,11 @@
       <c r="P68">
         <v>2</v>
       </c>
-      <c r="S68" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="69" ht="12" customHeight="1" spans="1:19">
+      <c r="T68" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" ht="12" customHeight="1" spans="1:20">
       <c r="A69">
         <v>3000030023</v>
       </c>
@@ -3923,11 +3944,11 @@
       <c r="P69">
         <v>3</v>
       </c>
-      <c r="S69" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="70" ht="12" customHeight="1" spans="1:19">
+      <c r="T69" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" ht="12" customHeight="1" spans="1:20">
       <c r="A70">
         <v>3000030024</v>
       </c>
@@ -3949,11 +3970,11 @@
       <c r="P70">
         <v>4</v>
       </c>
-      <c r="S70" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" ht="12" customHeight="1" spans="1:19">
+      <c r="T70" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" ht="12" customHeight="1" spans="1:20">
       <c r="A71">
         <v>3000030025</v>
       </c>
@@ -3975,11 +3996,11 @@
       <c r="P71">
         <v>5</v>
       </c>
-      <c r="S71" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19">
+      <c r="T71" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
       <c r="A72">
         <v>3000030031</v>
       </c>
@@ -4001,11 +4022,11 @@
       <c r="P72">
         <v>1</v>
       </c>
-      <c r="S72" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19">
+      <c r="T72" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
       <c r="A73">
         <v>3000030032</v>
       </c>
@@ -4027,11 +4048,11 @@
       <c r="P73">
         <v>2</v>
       </c>
-      <c r="S73" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19">
+      <c r="T73" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
       <c r="A74">
         <v>3000030033</v>
       </c>
@@ -4053,11 +4074,11 @@
       <c r="P74">
         <v>3</v>
       </c>
-      <c r="S74" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19">
+      <c r="T74" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
       <c r="A75">
         <v>3000030034</v>
       </c>
@@ -4079,11 +4100,11 @@
       <c r="P75">
         <v>4</v>
       </c>
-      <c r="S75" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="T75" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
       <c r="A76">
         <v>3000030035</v>
       </c>
@@ -4105,11 +4126,11 @@
       <c r="P76">
         <v>5</v>
       </c>
-      <c r="S76" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="T76" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
       <c r="A77">
         <v>3000030041</v>
       </c>
@@ -4131,11 +4152,11 @@
       <c r="P77">
         <v>1</v>
       </c>
-      <c r="S77" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19">
+      <c r="T77" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
       <c r="A78">
         <v>3000030042</v>
       </c>
@@ -4157,11 +4178,11 @@
       <c r="P78">
         <v>2</v>
       </c>
-      <c r="S78" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19">
+      <c r="T78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
       <c r="A79">
         <v>3000030043</v>
       </c>
@@ -4183,11 +4204,11 @@
       <c r="P79">
         <v>3</v>
       </c>
-      <c r="S79" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19">
+      <c r="T79" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
       <c r="A80">
         <v>3000030044</v>
       </c>
@@ -4209,11 +4230,11 @@
       <c r="P80">
         <v>4</v>
       </c>
-      <c r="S80" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19">
+      <c r="T80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
       <c r="A81">
         <v>3000030045</v>
       </c>
@@ -4235,11 +4256,11 @@
       <c r="P81">
         <v>5</v>
       </c>
-      <c r="S81" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19">
+      <c r="T81" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
       <c r="A82">
         <v>3000040011</v>
       </c>
@@ -4261,11 +4282,11 @@
       <c r="P82">
         <v>1</v>
       </c>
-      <c r="S82" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19">
+      <c r="T82" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
       <c r="A83">
         <v>3000040012</v>
       </c>
@@ -4287,11 +4308,11 @@
       <c r="P83">
         <v>2</v>
       </c>
-      <c r="S83" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="T83" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
       <c r="A84">
         <v>3000040013</v>
       </c>
@@ -4313,11 +4334,11 @@
       <c r="P84">
         <v>3</v>
       </c>
-      <c r="S84" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="T84" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
       <c r="A85">
         <v>3000040014</v>
       </c>
@@ -4339,11 +4360,11 @@
       <c r="P85">
         <v>4</v>
       </c>
-      <c r="S85" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="T85" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
       <c r="A86">
         <v>3000040015</v>
       </c>
@@ -4365,11 +4386,11 @@
       <c r="P86">
         <v>5</v>
       </c>
-      <c r="S86" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="T86" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
       <c r="A87">
         <v>3000040021</v>
       </c>
@@ -4391,11 +4412,11 @@
       <c r="P87">
         <v>1</v>
       </c>
-      <c r="S87" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="T87" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20">
       <c r="A88">
         <v>3000040022</v>
       </c>
@@ -4417,11 +4438,11 @@
       <c r="P88">
         <v>2</v>
       </c>
-      <c r="S88" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19">
+      <c r="T88" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20">
       <c r="A89">
         <v>3000040023</v>
       </c>
@@ -4443,11 +4464,11 @@
       <c r="P89">
         <v>3</v>
       </c>
-      <c r="S89" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="T89" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20">
       <c r="A90">
         <v>3000040024</v>
       </c>
@@ -4469,11 +4490,11 @@
       <c r="P90">
         <v>4</v>
       </c>
-      <c r="S90" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="T90" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20">
       <c r="A91">
         <v>3000040025</v>
       </c>
@@ -4495,11 +4516,11 @@
       <c r="P91">
         <v>5</v>
       </c>
-      <c r="S91" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19">
+      <c r="T91" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20">
       <c r="A92">
         <v>3000040031</v>
       </c>
@@ -4521,11 +4542,11 @@
       <c r="P92">
         <v>1</v>
       </c>
-      <c r="S92" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19">
+      <c r="T92" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20">
       <c r="A93">
         <v>3000040032</v>
       </c>
@@ -4547,11 +4568,11 @@
       <c r="P93">
         <v>2</v>
       </c>
-      <c r="S93" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19">
+      <c r="T93" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20">
       <c r="A94">
         <v>3000040033</v>
       </c>
@@ -4573,11 +4594,11 @@
       <c r="P94">
         <v>3</v>
       </c>
-      <c r="S94" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19">
+      <c r="T94" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20">
       <c r="A95">
         <v>3000040034</v>
       </c>
@@ -4599,11 +4620,11 @@
       <c r="P95">
         <v>4</v>
       </c>
-      <c r="S95" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19">
+      <c r="T95" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20">
       <c r="A96">
         <v>3000040035</v>
       </c>
@@ -4625,11 +4646,11 @@
       <c r="P96">
         <v>5</v>
       </c>
-      <c r="S96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19">
+      <c r="T96" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
       <c r="A97">
         <v>3000040041</v>
       </c>
@@ -4651,11 +4672,11 @@
       <c r="P97">
         <v>1</v>
       </c>
-      <c r="S97" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19">
+      <c r="T97" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
       <c r="A98">
         <v>3000040042</v>
       </c>
@@ -4677,11 +4698,11 @@
       <c r="P98">
         <v>2</v>
       </c>
-      <c r="S98" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19">
+      <c r="T98" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
       <c r="A99">
         <v>3000040043</v>
       </c>
@@ -4703,11 +4724,11 @@
       <c r="P99">
         <v>3</v>
       </c>
-      <c r="S99" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19">
+      <c r="T99" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20">
       <c r="A100">
         <v>3000040044</v>
       </c>
@@ -4729,11 +4750,11 @@
       <c r="P100">
         <v>4</v>
       </c>
-      <c r="S100" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19">
+      <c r="T100" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20">
       <c r="A101">
         <v>3000040045</v>
       </c>
@@ -4755,11 +4776,11 @@
       <c r="P101">
         <v>5</v>
       </c>
-      <c r="S101" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19">
+      <c r="T101" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20">
       <c r="A102">
         <v>3000040051</v>
       </c>
@@ -4781,11 +4802,11 @@
       <c r="P102">
         <v>1</v>
       </c>
-      <c r="S102" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19">
+      <c r="T102" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20">
       <c r="A103">
         <v>3000040052</v>
       </c>
@@ -4807,11 +4828,11 @@
       <c r="P103">
         <v>2</v>
       </c>
-      <c r="S103" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19">
+      <c r="T103" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20">
       <c r="A104">
         <v>3000040053</v>
       </c>
@@ -4833,11 +4854,11 @@
       <c r="P104">
         <v>3</v>
       </c>
-      <c r="S104" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19">
+      <c r="T104" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20">
       <c r="A105">
         <v>3000040054</v>
       </c>
@@ -4859,11 +4880,11 @@
       <c r="P105">
         <v>4</v>
       </c>
-      <c r="S105" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19">
+      <c r="T105" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20">
       <c r="A106">
         <v>3000040055</v>
       </c>
@@ -4885,11 +4906,11 @@
       <c r="P106">
         <v>5</v>
       </c>
-      <c r="S106" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19">
+      <c r="T106" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20">
       <c r="A107">
         <v>3000050011</v>
       </c>
@@ -4911,11 +4932,11 @@
       <c r="P107">
         <v>1</v>
       </c>
-      <c r="S107" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19">
+      <c r="T107" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20">
       <c r="A108">
         <v>3000050012</v>
       </c>
@@ -4937,11 +4958,11 @@
       <c r="P108">
         <v>2</v>
       </c>
-      <c r="S108" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19">
+      <c r="T108" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20">
       <c r="A109">
         <v>3000050013</v>
       </c>
@@ -4963,11 +4984,11 @@
       <c r="P109">
         <v>3</v>
       </c>
-      <c r="S109" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19">
+      <c r="T109" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20">
       <c r="A110">
         <v>3000050014</v>
       </c>
@@ -4989,11 +5010,11 @@
       <c r="P110">
         <v>4</v>
       </c>
-      <c r="S110" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="111" spans="1:19">
+      <c r="T110" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20">
       <c r="A111">
         <v>3000050015</v>
       </c>
@@ -5015,11 +5036,11 @@
       <c r="P111">
         <v>5</v>
       </c>
-      <c r="S111" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="112" spans="1:19">
+      <c r="T111" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20">
       <c r="A112">
         <v>3000050021</v>
       </c>
@@ -5041,11 +5062,11 @@
       <c r="P112">
         <v>1</v>
       </c>
-      <c r="S112" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="113" spans="1:19">
+      <c r="T112" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20">
       <c r="A113">
         <v>3000050022</v>
       </c>
@@ -5067,11 +5088,11 @@
       <c r="P113">
         <v>2</v>
       </c>
-      <c r="S113" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19">
+      <c r="T113" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20">
       <c r="A114">
         <v>3000050023</v>
       </c>
@@ -5093,11 +5114,11 @@
       <c r="P114">
         <v>3</v>
       </c>
-      <c r="S114" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19">
+      <c r="T114" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20">
       <c r="A115">
         <v>3000050024</v>
       </c>
@@ -5119,11 +5140,11 @@
       <c r="P115">
         <v>4</v>
       </c>
-      <c r="S115" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19">
+      <c r="T115" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20">
       <c r="A116">
         <v>3000050025</v>
       </c>
@@ -5145,11 +5166,11 @@
       <c r="P116">
         <v>5</v>
       </c>
-      <c r="S116" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19">
+      <c r="T116" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20">
       <c r="A117">
         <v>3000050031</v>
       </c>
@@ -5171,11 +5192,11 @@
       <c r="P117">
         <v>1</v>
       </c>
-      <c r="S117" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19">
+      <c r="T117" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20">
       <c r="A118">
         <v>3000050032</v>
       </c>
@@ -5197,11 +5218,11 @@
       <c r="P118">
         <v>2</v>
       </c>
-      <c r="S118" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19">
+      <c r="T118" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20">
       <c r="A119">
         <v>3000050033</v>
       </c>
@@ -5223,11 +5244,11 @@
       <c r="P119">
         <v>3</v>
       </c>
-      <c r="S119" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19">
+      <c r="T119" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20">
       <c r="A120">
         <v>3000050034</v>
       </c>
@@ -5249,11 +5270,11 @@
       <c r="P120">
         <v>4</v>
       </c>
-      <c r="S120" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19">
+      <c r="T120" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20">
       <c r="A121">
         <v>3000050035</v>
       </c>
@@ -5275,11 +5296,11 @@
       <c r="P121">
         <v>5</v>
       </c>
-      <c r="S121" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19">
+      <c r="T121" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20">
       <c r="A122">
         <v>3000050041</v>
       </c>
@@ -5301,11 +5322,11 @@
       <c r="P122">
         <v>1</v>
       </c>
-      <c r="S122" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19">
+      <c r="T122" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20">
       <c r="A123">
         <v>3000050042</v>
       </c>
@@ -5327,11 +5348,11 @@
       <c r="P123">
         <v>2</v>
       </c>
-      <c r="S123" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="124" spans="1:19">
+      <c r="T123" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20">
       <c r="A124">
         <v>3000050043</v>
       </c>
@@ -5353,11 +5374,11 @@
       <c r="P124">
         <v>3</v>
       </c>
-      <c r="S124" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19">
+      <c r="T124" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20">
       <c r="A125">
         <v>3000050044</v>
       </c>
@@ -5379,11 +5400,11 @@
       <c r="P125">
         <v>4</v>
       </c>
-      <c r="S125" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19">
+      <c r="T125" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20">
       <c r="A126">
         <v>3000050045</v>
       </c>
@@ -5405,11 +5426,11 @@
       <c r="P126">
         <v>5</v>
       </c>
-      <c r="S126" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19">
+      <c r="T126" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20">
       <c r="A127">
         <v>3000060011</v>
       </c>
@@ -5431,11 +5452,11 @@
       <c r="P127">
         <v>1</v>
       </c>
-      <c r="S127" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19">
+      <c r="T127" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20">
       <c r="A128">
         <v>3000060012</v>
       </c>
@@ -5457,11 +5478,11 @@
       <c r="P128">
         <v>2</v>
       </c>
-      <c r="S128" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19">
+      <c r="T128" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20">
       <c r="A129">
         <v>3000060013</v>
       </c>
@@ -5483,11 +5504,11 @@
       <c r="P129">
         <v>3</v>
       </c>
-      <c r="S129" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19">
+      <c r="T129" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20">
       <c r="A130">
         <v>3000060014</v>
       </c>
@@ -5509,11 +5530,11 @@
       <c r="P130">
         <v>4</v>
       </c>
-      <c r="S130" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19">
+      <c r="T130" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20">
       <c r="A131">
         <v>3000060015</v>
       </c>
@@ -5535,11 +5556,11 @@
       <c r="P131">
         <v>5</v>
       </c>
-      <c r="S131" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19">
+      <c r="T131" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20">
       <c r="A132">
         <v>3000060021</v>
       </c>
@@ -5561,11 +5582,11 @@
       <c r="P132">
         <v>1</v>
       </c>
-      <c r="S132" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="133" spans="1:19">
+      <c r="T132" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20">
       <c r="A133">
         <v>3000060022</v>
       </c>
@@ -5587,11 +5608,11 @@
       <c r="P133">
         <v>2</v>
       </c>
-      <c r="S133" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19">
+      <c r="T133" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20">
       <c r="A134">
         <v>3000060023</v>
       </c>
@@ -5613,11 +5634,11 @@
       <c r="P134">
         <v>3</v>
       </c>
-      <c r="S134" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19">
+      <c r="T134" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20">
       <c r="A135">
         <v>3000060024</v>
       </c>
@@ -5639,11 +5660,11 @@
       <c r="P135">
         <v>4</v>
       </c>
-      <c r="S135" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19">
+      <c r="T135" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20">
       <c r="A136">
         <v>3000060025</v>
       </c>
@@ -5665,11 +5686,11 @@
       <c r="P136">
         <v>5</v>
       </c>
-      <c r="S136" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19">
+      <c r="T136" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20">
       <c r="A137">
         <v>3000060031</v>
       </c>
@@ -5691,11 +5712,11 @@
       <c r="P137">
         <v>1</v>
       </c>
-      <c r="S137" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19">
+      <c r="T137" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20">
       <c r="A138">
         <v>3000060032</v>
       </c>
@@ -5717,11 +5738,11 @@
       <c r="P138">
         <v>2</v>
       </c>
-      <c r="S138" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="139" spans="1:19">
+      <c r="T138" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20">
       <c r="A139">
         <v>3000060033</v>
       </c>
@@ -5743,11 +5764,11 @@
       <c r="P139">
         <v>3</v>
       </c>
-      <c r="S139" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19">
+      <c r="T139" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20">
       <c r="A140">
         <v>3000060034</v>
       </c>
@@ -5769,11 +5790,11 @@
       <c r="P140">
         <v>4</v>
       </c>
-      <c r="S140" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="141" spans="1:19">
+      <c r="T140" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20">
       <c r="A141">
         <v>3000060035</v>
       </c>
@@ -5795,11 +5816,11 @@
       <c r="P141">
         <v>5</v>
       </c>
-      <c r="S141" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="142" spans="1:19">
+      <c r="T141" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20">
       <c r="A142">
         <v>3000060041</v>
       </c>
@@ -5821,11 +5842,11 @@
       <c r="P142">
         <v>1</v>
       </c>
-      <c r="S142" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19">
+      <c r="T142" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20">
       <c r="A143">
         <v>3000060042</v>
       </c>
@@ -5847,11 +5868,11 @@
       <c r="P143">
         <v>2</v>
       </c>
-      <c r="S143" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19">
+      <c r="T143" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20">
       <c r="A144">
         <v>3000060043</v>
       </c>
@@ -5873,11 +5894,11 @@
       <c r="P144">
         <v>3</v>
       </c>
-      <c r="S144" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="145" spans="1:19">
+      <c r="T144" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20">
       <c r="A145">
         <v>3000060044</v>
       </c>
@@ -5899,11 +5920,11 @@
       <c r="P145">
         <v>4</v>
       </c>
-      <c r="S145" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="146" spans="1:19">
+      <c r="T145" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20">
       <c r="A146">
         <v>3000060045</v>
       </c>
@@ -5925,11 +5946,11 @@
       <c r="P146">
         <v>5</v>
       </c>
-      <c r="S146" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="147" spans="1:19">
+      <c r="T146" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20">
       <c r="A147">
         <v>3000060051</v>
       </c>
@@ -5951,11 +5972,11 @@
       <c r="P147">
         <v>1</v>
       </c>
-      <c r="S147" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="148" spans="1:19">
+      <c r="T147" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20">
       <c r="A148">
         <v>3000060052</v>
       </c>
@@ -5977,11 +5998,11 @@
       <c r="P148">
         <v>2</v>
       </c>
-      <c r="S148" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="149" spans="1:19">
+      <c r="T148" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20">
       <c r="A149">
         <v>3000060053</v>
       </c>
@@ -6003,11 +6024,11 @@
       <c r="P149">
         <v>3</v>
       </c>
-      <c r="S149" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="150" spans="1:19">
+      <c r="T149" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20">
       <c r="A150">
         <v>3000060054</v>
       </c>
@@ -6029,11 +6050,11 @@
       <c r="P150">
         <v>4</v>
       </c>
-      <c r="S150" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="151" spans="1:19">
+      <c r="T150" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20">
       <c r="A151">
         <v>3000060055</v>
       </c>
@@ -6055,11 +6076,11 @@
       <c r="P151">
         <v>5</v>
       </c>
-      <c r="S151" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="152" spans="1:19">
+      <c r="T151" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20">
       <c r="A152">
         <v>3000070011</v>
       </c>
@@ -6081,11 +6102,11 @@
       <c r="P152">
         <v>1</v>
       </c>
-      <c r="S152" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="153" spans="1:19">
+      <c r="T152" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20">
       <c r="A153">
         <v>3000070012</v>
       </c>
@@ -6107,11 +6128,11 @@
       <c r="P153">
         <v>2</v>
       </c>
-      <c r="S153" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="154" spans="1:19">
+      <c r="T153" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20">
       <c r="A154">
         <v>3000070013</v>
       </c>
@@ -6133,11 +6154,11 @@
       <c r="P154">
         <v>3</v>
       </c>
-      <c r="S154" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="155" spans="1:19">
+      <c r="T154" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20">
       <c r="A155">
         <v>3000070014</v>
       </c>
@@ -6159,11 +6180,11 @@
       <c r="P155">
         <v>4</v>
       </c>
-      <c r="S155" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="156" spans="1:19">
+      <c r="T155" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20">
       <c r="A156">
         <v>3000070015</v>
       </c>
@@ -6185,11 +6206,11 @@
       <c r="P156">
         <v>5</v>
       </c>
-      <c r="S156" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="157" spans="1:19">
+      <c r="T156" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20">
       <c r="A157">
         <v>3000070021</v>
       </c>
@@ -6211,11 +6232,11 @@
       <c r="P157">
         <v>1</v>
       </c>
-      <c r="S157" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="158" spans="1:19">
+      <c r="T157" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20">
       <c r="A158">
         <v>3000070022</v>
       </c>
@@ -6237,11 +6258,11 @@
       <c r="P158">
         <v>2</v>
       </c>
-      <c r="S158" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="159" spans="1:19">
+      <c r="T158" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20">
       <c r="A159">
         <v>3000070023</v>
       </c>
@@ -6263,11 +6284,11 @@
       <c r="P159">
         <v>3</v>
       </c>
-      <c r="S159" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="160" spans="1:19">
+      <c r="T159" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20">
       <c r="A160">
         <v>3000070024</v>
       </c>
@@ -6289,11 +6310,11 @@
       <c r="P160">
         <v>4</v>
       </c>
-      <c r="S160" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="161" spans="1:19">
+      <c r="T160" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20">
       <c r="A161">
         <v>3000070025</v>
       </c>
@@ -6315,11 +6336,11 @@
       <c r="P161">
         <v>5</v>
       </c>
-      <c r="S161" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="162" spans="1:19">
+      <c r="T161" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20">
       <c r="A162">
         <v>3000070031</v>
       </c>
@@ -6341,11 +6362,11 @@
       <c r="P162">
         <v>1</v>
       </c>
-      <c r="S162" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="163" spans="1:19">
+      <c r="T162" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20">
       <c r="A163">
         <v>3000070032</v>
       </c>
@@ -6367,11 +6388,11 @@
       <c r="P163">
         <v>2</v>
       </c>
-      <c r="S163" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="164" spans="1:19">
+      <c r="T163" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20">
       <c r="A164">
         <v>3000070033</v>
       </c>
@@ -6393,11 +6414,11 @@
       <c r="P164">
         <v>3</v>
       </c>
-      <c r="S164" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="165" spans="1:19">
+      <c r="T164" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20">
       <c r="A165">
         <v>3000070034</v>
       </c>
@@ -6419,11 +6440,11 @@
       <c r="P165">
         <v>4</v>
       </c>
-      <c r="S165" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="166" spans="1:19">
+      <c r="T165" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20">
       <c r="A166">
         <v>3000070035</v>
       </c>
@@ -6445,11 +6466,11 @@
       <c r="P166">
         <v>5</v>
       </c>
-      <c r="S166" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="167" spans="1:19">
+      <c r="T166" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20">
       <c r="A167">
         <v>3000070041</v>
       </c>
@@ -6471,11 +6492,11 @@
       <c r="P167">
         <v>1</v>
       </c>
-      <c r="S167" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="168" spans="1:19">
+      <c r="T167" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20">
       <c r="A168">
         <v>3000070042</v>
       </c>
@@ -6497,11 +6518,11 @@
       <c r="P168">
         <v>2</v>
       </c>
-      <c r="S168" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="169" spans="1:19">
+      <c r="T168" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20">
       <c r="A169">
         <v>3000070043</v>
       </c>
@@ -6523,11 +6544,11 @@
       <c r="P169">
         <v>3</v>
       </c>
-      <c r="S169" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="170" spans="1:19">
+      <c r="T169" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20">
       <c r="A170">
         <v>3000070044</v>
       </c>
@@ -6549,11 +6570,11 @@
       <c r="P170">
         <v>4</v>
       </c>
-      <c r="S170" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="171" spans="1:19">
+      <c r="T170" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20">
       <c r="A171">
         <v>3000070045</v>
       </c>
@@ -6575,8 +6596,8 @@
       <c r="P171">
         <v>5</v>
       </c>
-      <c r="S171" t="s">
-        <v>228</v>
+      <c r="T171" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -197,7 +197,7 @@
     <t>100001</t>
   </si>
   <si>
-    <t>持盾战士-Boss-lv1</t>
+    <t>持盾战士-Boss</t>
   </si>
   <si>
     <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
@@ -206,19 +206,16 @@
     <t>弓箭手</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
     <t>10200006&amp;10300006&amp;11010002&amp;</t>
   </si>
   <si>
-    <t>强弓手-Boss-lv1</t>
+    <t>强弓手-Boss</t>
   </si>
   <si>
     <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
   </si>
   <si>
-    <t>连射手-Boss-lv1</t>
+    <t>连射手-Boss</t>
   </si>
   <si>
     <t>50</t>
@@ -2146,14 +2143,14 @@
         <v>1</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>47</v>
+      <c r="E10" s="4">
+        <v>200</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>48</v>
@@ -2174,7 +2171,7 @@
         <v>1000001</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O10" s="4">
         <v>1020020001</v>
@@ -2185,7 +2182,7 @@
         <v>51</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:20">
@@ -2199,14 +2196,14 @@
         <v>1</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>58</v>
+      <c r="E11" s="4">
+        <v>200</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>47</v>
+      <c r="G11" s="4">
+        <v>200</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>48</v>
@@ -2227,7 +2224,7 @@
         <v>1000001</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O11" s="4">
         <v>1020030001</v>
@@ -2238,7 +2235,7 @@
         <v>51</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:20">
@@ -2253,7 +2250,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>47</v>
@@ -2280,7 +2277,7 @@
         <v>1000001</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O12" s="4">
         <v>1030010001</v>
@@ -2291,7 +2288,7 @@
         <v>51</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:20">
@@ -2306,7 +2303,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>47</v>
@@ -2333,7 +2330,7 @@
         <v>1000001</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O13" s="4">
         <v>1030020001</v>
@@ -2344,7 +2341,7 @@
         <v>51</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:20">
@@ -2359,7 +2356,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>47</v>
@@ -2386,7 +2383,7 @@
         <v>1000001</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O14" s="4">
         <v>1030030001</v>
@@ -2397,7 +2394,7 @@
         <v>51</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:20">
@@ -2412,7 +2409,7 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>47</v>
@@ -2439,7 +2436,7 @@
         <v>1000001</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O15" s="4">
         <v>1030040001</v>
@@ -2450,7 +2447,7 @@
         <v>51</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:20">
@@ -2465,7 +2462,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>47</v>
@@ -2492,7 +2489,7 @@
         <v>1000001</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O16" s="4">
         <v>1031010001</v>
@@ -2503,7 +2500,7 @@
         <v>1.2</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:20">
@@ -2518,7 +2515,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>47</v>
@@ -2545,7 +2542,7 @@
         <v>1000001</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O17" s="4">
         <v>1031010002</v>
@@ -2556,7 +2553,7 @@
         <v>1.2</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:20">
@@ -2571,7 +2568,7 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>47</v>
@@ -2598,7 +2595,7 @@
         <v>1000001</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O18" s="4">
         <v>1031010003</v>
@@ -2609,7 +2606,7 @@
         <v>1.2</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:20">
@@ -2626,11 +2623,11 @@
         <v>9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2">
         <v>2000000001</v>
@@ -2642,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:20">
@@ -2668,7 +2665,7 @@
         <v>2</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:20">
@@ -2685,7 +2682,7 @@
         <v>99</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O21" s="2">
         <v>2000000002</v>
@@ -2697,7 +2694,7 @@
         <v>3</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:20">
@@ -2723,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:20">
@@ -2749,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="T23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:20">
@@ -2775,7 +2772,7 @@
         <v>3</v>
       </c>
       <c r="T24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:20">
@@ -2801,7 +2798,7 @@
         <v>4</v>
       </c>
       <c r="T25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:20">
@@ -2827,7 +2824,7 @@
         <v>5</v>
       </c>
       <c r="T26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:20">
@@ -2853,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:20">
@@ -2879,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="T28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:20">
@@ -2905,7 +2902,7 @@
         <v>3</v>
       </c>
       <c r="T29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:20">
@@ -2931,7 +2928,7 @@
         <v>4</v>
       </c>
       <c r="T30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:20">
@@ -2957,7 +2954,7 @@
         <v>5</v>
       </c>
       <c r="T31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2983,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -3009,7 +3006,7 @@
         <v>2</v>
       </c>
       <c r="T33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -3035,7 +3032,7 @@
         <v>3</v>
       </c>
       <c r="T34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -3061,7 +3058,7 @@
         <v>4</v>
       </c>
       <c r="T35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -3087,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="T36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -3113,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -3139,7 +3136,7 @@
         <v>2</v>
       </c>
       <c r="T38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3165,7 +3162,7 @@
         <v>3</v>
       </c>
       <c r="T39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3191,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="T40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -3217,7 +3214,7 @@
         <v>5</v>
       </c>
       <c r="T41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -3243,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3269,7 +3266,7 @@
         <v>2</v>
       </c>
       <c r="T43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3295,7 +3292,7 @@
         <v>3</v>
       </c>
       <c r="T44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3321,7 +3318,7 @@
         <v>4</v>
       </c>
       <c r="T45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3347,7 +3344,7 @@
         <v>5</v>
       </c>
       <c r="T46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3373,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3399,7 +3396,7 @@
         <v>2</v>
       </c>
       <c r="T48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -3425,7 +3422,7 @@
         <v>3</v>
       </c>
       <c r="T49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -3451,7 +3448,7 @@
         <v>4</v>
       </c>
       <c r="T50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3477,7 +3474,7 @@
         <v>5</v>
       </c>
       <c r="T51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3503,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -3529,7 +3526,7 @@
         <v>2</v>
       </c>
       <c r="T53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3555,7 +3552,7 @@
         <v>3</v>
       </c>
       <c r="T54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -3581,7 +3578,7 @@
         <v>4</v>
       </c>
       <c r="T55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -3607,7 +3604,7 @@
         <v>5</v>
       </c>
       <c r="T56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -3633,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="T57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -3659,7 +3656,7 @@
         <v>2</v>
       </c>
       <c r="T58" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -3685,7 +3682,7 @@
         <v>3</v>
       </c>
       <c r="T59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -3711,7 +3708,7 @@
         <v>4</v>
       </c>
       <c r="T60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -3737,7 +3734,7 @@
         <v>5</v>
       </c>
       <c r="T61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -3763,7 +3760,7 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" spans="1:20">
@@ -3789,7 +3786,7 @@
         <v>2</v>
       </c>
       <c r="T63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" spans="1:20">
@@ -3815,7 +3812,7 @@
         <v>3</v>
       </c>
       <c r="T64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" spans="1:20">
@@ -3841,7 +3838,7 @@
         <v>4</v>
       </c>
       <c r="T65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" spans="1:20">
@@ -3867,7 +3864,7 @@
         <v>5</v>
       </c>
       <c r="T66" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" spans="1:20">
@@ -3893,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" spans="1:20">
@@ -3919,7 +3916,7 @@
         <v>2</v>
       </c>
       <c r="T68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" spans="1:20">
@@ -3945,7 +3942,7 @@
         <v>3</v>
       </c>
       <c r="T69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" spans="1:20">
@@ -3971,7 +3968,7 @@
         <v>4</v>
       </c>
       <c r="T70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" spans="1:20">
@@ -3997,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="T71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -4023,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="T72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -4049,7 +4046,7 @@
         <v>2</v>
       </c>
       <c r="T73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -4075,7 +4072,7 @@
         <v>3</v>
       </c>
       <c r="T74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -4101,7 +4098,7 @@
         <v>4</v>
       </c>
       <c r="T75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -4127,7 +4124,7 @@
         <v>5</v>
       </c>
       <c r="T76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -4153,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -4179,7 +4176,7 @@
         <v>2</v>
       </c>
       <c r="T78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -4205,7 +4202,7 @@
         <v>3</v>
       </c>
       <c r="T79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -4231,7 +4228,7 @@
         <v>4</v>
       </c>
       <c r="T80" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4257,7 +4254,7 @@
         <v>5</v>
       </c>
       <c r="T81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -4283,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -4309,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="T83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -4335,7 +4332,7 @@
         <v>3</v>
       </c>
       <c r="T84" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -4361,7 +4358,7 @@
         <v>4</v>
       </c>
       <c r="T85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -4387,7 +4384,7 @@
         <v>5</v>
       </c>
       <c r="T86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -4413,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -4439,7 +4436,7 @@
         <v>2</v>
       </c>
       <c r="T88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -4465,7 +4462,7 @@
         <v>3</v>
       </c>
       <c r="T89" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -4491,7 +4488,7 @@
         <v>4</v>
       </c>
       <c r="T90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -4517,7 +4514,7 @@
         <v>5</v>
       </c>
       <c r="T91" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -4543,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="T92" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -4569,7 +4566,7 @@
         <v>2</v>
       </c>
       <c r="T93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -4595,7 +4592,7 @@
         <v>3</v>
       </c>
       <c r="T94" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -4621,7 +4618,7 @@
         <v>4</v>
       </c>
       <c r="T95" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -4647,7 +4644,7 @@
         <v>5</v>
       </c>
       <c r="T96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -4673,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="T97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -4699,7 +4696,7 @@
         <v>2</v>
       </c>
       <c r="T98" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -4725,7 +4722,7 @@
         <v>3</v>
       </c>
       <c r="T99" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -4751,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="T100" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -4777,7 +4774,7 @@
         <v>5</v>
       </c>
       <c r="T101" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -4803,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="T102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -4829,7 +4826,7 @@
         <v>2</v>
       </c>
       <c r="T103" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -4855,7 +4852,7 @@
         <v>3</v>
       </c>
       <c r="T104" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -4881,7 +4878,7 @@
         <v>4</v>
       </c>
       <c r="T105" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -4907,7 +4904,7 @@
         <v>5</v>
       </c>
       <c r="T106" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -4933,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -4959,7 +4956,7 @@
         <v>2</v>
       </c>
       <c r="T108" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -4985,7 +4982,7 @@
         <v>3</v>
       </c>
       <c r="T109" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:20">
@@ -5011,7 +5008,7 @@
         <v>4</v>
       </c>
       <c r="T110" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="1:20">
@@ -5037,7 +5034,7 @@
         <v>5</v>
       </c>
       <c r="T111" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="112" spans="1:20">
@@ -5063,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="T112" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="1:20">
@@ -5089,7 +5086,7 @@
         <v>2</v>
       </c>
       <c r="T113" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:20">
@@ -5115,7 +5112,7 @@
         <v>3</v>
       </c>
       <c r="T114" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="115" spans="1:20">
@@ -5141,7 +5138,7 @@
         <v>4</v>
       </c>
       <c r="T115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:20">
@@ -5167,7 +5164,7 @@
         <v>5</v>
       </c>
       <c r="T116" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="117" spans="1:20">
@@ -5193,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="T117" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="118" spans="1:20">
@@ -5219,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="T118" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119" spans="1:20">
@@ -5245,7 +5242,7 @@
         <v>3</v>
       </c>
       <c r="T119" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="120" spans="1:20">
@@ -5271,7 +5268,7 @@
         <v>4</v>
       </c>
       <c r="T120" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:20">
@@ -5297,7 +5294,7 @@
         <v>5</v>
       </c>
       <c r="T121" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="122" spans="1:20">
@@ -5323,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123" spans="1:20">
@@ -5349,7 +5346,7 @@
         <v>2</v>
       </c>
       <c r="T123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="124" spans="1:20">
@@ -5375,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="T124" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="125" spans="1:20">
@@ -5401,7 +5398,7 @@
         <v>4</v>
       </c>
       <c r="T125" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:20">
@@ -5427,7 +5424,7 @@
         <v>5</v>
       </c>
       <c r="T126" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:20">
@@ -5453,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="T127" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="128" spans="1:20">
@@ -5479,7 +5476,7 @@
         <v>2</v>
       </c>
       <c r="T128" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:20">
@@ -5505,7 +5502,7 @@
         <v>3</v>
       </c>
       <c r="T129" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="130" spans="1:20">
@@ -5531,7 +5528,7 @@
         <v>4</v>
       </c>
       <c r="T130" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="131" spans="1:20">
@@ -5557,7 +5554,7 @@
         <v>5</v>
       </c>
       <c r="T131" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="132" spans="1:20">
@@ -5583,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="T132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="133" spans="1:20">
@@ -5609,7 +5606,7 @@
         <v>2</v>
       </c>
       <c r="T133" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="134" spans="1:20">
@@ -5635,7 +5632,7 @@
         <v>3</v>
       </c>
       <c r="T134" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:20">
@@ -5661,7 +5658,7 @@
         <v>4</v>
       </c>
       <c r="T135" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="136" spans="1:20">
@@ -5687,7 +5684,7 @@
         <v>5</v>
       </c>
       <c r="T136" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:20">
@@ -5713,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="T137" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -5739,7 +5736,7 @@
         <v>2</v>
       </c>
       <c r="T138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="139" spans="1:20">
@@ -5765,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="T139" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:20">
@@ -5791,7 +5788,7 @@
         <v>4</v>
       </c>
       <c r="T140" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:20">
@@ -5817,7 +5814,7 @@
         <v>5</v>
       </c>
       <c r="T141" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" spans="1:20">
@@ -5843,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="T142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="143" spans="1:20">
@@ -5869,7 +5866,7 @@
         <v>2</v>
       </c>
       <c r="T143" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="144" spans="1:20">
@@ -5895,7 +5892,7 @@
         <v>3</v>
       </c>
       <c r="T144" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="145" spans="1:20">
@@ -5921,7 +5918,7 @@
         <v>4</v>
       </c>
       <c r="T145" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:20">
@@ -5947,7 +5944,7 @@
         <v>5</v>
       </c>
       <c r="T146" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="147" spans="1:20">
@@ -5973,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="T147" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:20">
@@ -5999,7 +5996,7 @@
         <v>2</v>
       </c>
       <c r="T148" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="149" spans="1:20">
@@ -6025,7 +6022,7 @@
         <v>3</v>
       </c>
       <c r="T149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:20">
@@ -6051,7 +6048,7 @@
         <v>4</v>
       </c>
       <c r="T150" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:20">
@@ -6077,7 +6074,7 @@
         <v>5</v>
       </c>
       <c r="T151" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="152" spans="1:20">
@@ -6103,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="T152" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:20">
@@ -6129,7 +6126,7 @@
         <v>2</v>
       </c>
       <c r="T153" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:20">
@@ -6155,7 +6152,7 @@
         <v>3</v>
       </c>
       <c r="T154" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="155" spans="1:20">
@@ -6181,7 +6178,7 @@
         <v>4</v>
       </c>
       <c r="T155" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="156" spans="1:20">
@@ -6207,7 +6204,7 @@
         <v>5</v>
       </c>
       <c r="T156" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="157" spans="1:20">
@@ -6233,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="T157" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="158" spans="1:20">
@@ -6259,7 +6256,7 @@
         <v>2</v>
       </c>
       <c r="T158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="159" spans="1:20">
@@ -6285,7 +6282,7 @@
         <v>3</v>
       </c>
       <c r="T159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="160" spans="1:20">
@@ -6311,7 +6308,7 @@
         <v>4</v>
       </c>
       <c r="T160" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="161" spans="1:20">
@@ -6337,7 +6334,7 @@
         <v>5</v>
       </c>
       <c r="T161" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="162" spans="1:20">
@@ -6363,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="T162" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="163" spans="1:20">
@@ -6389,7 +6386,7 @@
         <v>2</v>
       </c>
       <c r="T163" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="164" spans="1:20">
@@ -6415,7 +6412,7 @@
         <v>3</v>
       </c>
       <c r="T164" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="1:20">
@@ -6441,7 +6438,7 @@
         <v>4</v>
       </c>
       <c r="T165" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="166" spans="1:20">
@@ -6467,7 +6464,7 @@
         <v>5</v>
       </c>
       <c r="T166" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="167" spans="1:20">
@@ -6493,7 +6490,7 @@
         <v>1</v>
       </c>
       <c r="T167" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" spans="1:20">
@@ -6519,7 +6516,7 @@
         <v>2</v>
       </c>
       <c r="T168" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="169" spans="1:20">
@@ -6545,7 +6542,7 @@
         <v>3</v>
       </c>
       <c r="T169" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="170" spans="1:20">
@@ -6571,7 +6568,7 @@
         <v>4</v>
       </c>
       <c r="T170" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="171" spans="1:20">
@@ -6597,7 +6594,7 @@
         <v>5</v>
       </c>
       <c r="T171" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T171"/>
+  <dimension ref="A1:T172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -1075,6 +1075,7 @@
     <col width="47.5" customWidth="1" style="3" min="17" max="17"/>
     <col width="17.25" customWidth="1" style="3" min="18" max="18"/>
     <col width="25.125" customWidth="1" style="3" min="19" max="19"/>
+    <col width="30.25" customWidth="1" style="3" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1571,92 +1572,84 @@
       </c>
     </row>
     <row r="9" customFormat="1" s="1">
-      <c r="A9" s="4" t="n">
-        <v>1020010001</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>102001</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="A9" s="0" t="n">
+        <v>1010020002</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>1020010001</v>
-      </c>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="1" t="inlineStr">
+      <c r="G9" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="0" t="inlineStr"/>
+      <c r="M9" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>10200001&amp;10300001&amp;11020021&amp;</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>1010020001</v>
+      </c>
+      <c r="R9" s="0" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>弓箭手</t>
+      <c r="T9" s="0" t="inlineStr">
+        <is>
+          <t>持盾战士</t>
         </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="A10" s="4" t="n">
-        <v>1020020001</v>
+        <v>1020010001</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>102002</v>
+        <v>102001</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
@@ -1675,11 +1668,11 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>10200006&amp;10300006&amp;11010002&amp;</t>
+          <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
         </is>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1020020001</v>
+        <v>1020010001</v>
       </c>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
@@ -1690,16 +1683,16 @@
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>强弓手-Boss</t>
+          <t>弓箭手</t>
         </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="A11" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020001</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>102003</v>
+        <v>102002</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1</v>
@@ -1708,10 +1701,8 @@
       <c r="E11" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>200</v>
@@ -1738,50 +1729,44 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
+          <t>10200006&amp;10300006&amp;11010002&amp;</t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020001</v>
       </c>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+      <c r="R11" s="1" t="n">
+        <v>1.2</v>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>连射手-Boss</t>
+          <t>强弓手-Boss</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>103001</v>
+        <v>102003</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E12" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1805,31 +1790,29 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
         </is>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+      <c r="R12" s="1" t="n">
+        <v>1.2</v>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（火）</t>
+          <t>连射手-Boss</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" s="4" t="n">
-        <v>1030020001</v>
+        <v>1030010001</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>103002</v>
+        <v>103001</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
@@ -1872,11 +1855,11 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
+          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
         </is>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1030020001</v>
+        <v>1030010001</v>
       </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
@@ -1887,16 +1870,16 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（水）</t>
+          <t>人类-魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030020001</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>103003</v>
+        <v>103002</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
@@ -1939,11 +1922,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
+          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
         </is>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030020001</v>
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
@@ -1954,16 +1937,16 @@
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（冰）</t>
+          <t>人类-魔法师（水）</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
       <c r="A15" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030030001</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>103004</v>
+        <v>103003</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1</v>
@@ -2006,11 +1989,11 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
+          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
         </is>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030030001</v>
       </c>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
@@ -2021,16 +2004,16 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（雷）</t>
+          <t>人类-魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030040001</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>103101</v>
+        <v>103004</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1</v>
@@ -2073,29 +2056,31 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
         </is>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030040001</v>
       </c>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="1" t="n">
-        <v>1.2</v>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（火）</t>
+          <t>人类-魔法师（雷）</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" s="4" t="n">
-        <v>1031020001</v>
+        <v>1031010001</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>103102</v>
+        <v>103101</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1</v>
@@ -2142,25 +2127,28 @@
         </is>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1031010002</v>
+        <v>1031010001</v>
       </c>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="1" t="n">
         <v>1.2</v>
       </c>
+      <c r="S17" t="n">
+        <v>100002</v>
+      </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（水）</t>
+          <t>人类-大魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="4" t="n">
-        <v>1031030001</v>
+        <v>1031020001</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>103103</v>
+        <v>103102</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1</v>
@@ -2207,64 +2195,93 @@
         </is>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1031010003</v>
+        <v>1031010002</v>
       </c>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="1" t="n">
         <v>1.2</v>
       </c>
+      <c r="S18" t="n">
+        <v>100003</v>
+      </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
+          <t>人类-大魔法师（水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="2">
+      <c r="A19" s="4" t="n">
+        <v>1031030001</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>103103</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1031010003</v>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
           <t>人类-大魔法师（冰）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="1" s="2">
-      <c r="A19" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>101001</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1050001&amp;1040001&amp;1060004&amp;1030003&amp;</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>11000001&amp;10100002&amp;10300001&amp;10200001&amp;</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="20" customFormat="1" s="2">
       <c r="A20" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4001</v>
+        <v>101001</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>2</v>
@@ -2272,85 +2289,96 @@
       <c r="D20" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1050001&amp;1040001&amp;1060004&amp;1030003&amp;</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>11000001&amp;10100002&amp;10300001&amp;10200001&amp;</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>5</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>宛家伟</t>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="2">
       <c r="A21" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000002</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>101001</v>
+        <v>4001</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>2000000002</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>宛家伟</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="2" t="n">
+        <v>2000000003</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>101001</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>10200001&amp;10300001&amp;11000001</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>2000000003</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>雷神天尊斩</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="3">
-      <c r="A22" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000010012</v>
+        <v>3000010011</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>1001</v>
@@ -2365,20 +2393,20 @@
         <v>1000001</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级2</t>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010012</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>1001</v>
@@ -2393,20 +2421,20 @@
         <v>1000001</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T24" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级3</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010013</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>1001</v>
@@ -2421,20 +2449,20 @@
         <v>1000001</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P25" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级4</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="3">
       <c r="A26" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010014</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>1001</v>
@@ -2449,23 +2477,23 @@
         <v>1000001</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010015</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2477,20 +2505,20 @@
         <v>1000001</v>
       </c>
       <c r="O27" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P27" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010021</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>1002</v>
@@ -2505,20 +2533,20 @@
         <v>1000001</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010022</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>1002</v>
@@ -2533,20 +2561,20 @@
         <v>1000001</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T29" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010023</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1002</v>
@@ -2561,20 +2589,20 @@
         <v>1000001</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010024</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1002</v>
@@ -2589,23 +2617,23 @@
         <v>1000001</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010025</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -2617,20 +2645,20 @@
         <v>1000001</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010031</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>1003</v>
@@ -2645,20 +2673,20 @@
         <v>1000001</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T33" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010032</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>1003</v>
@@ -2673,20 +2701,20 @@
         <v>1000001</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P34" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010033</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>1003</v>
@@ -2701,20 +2729,20 @@
         <v>1000001</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P35" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T35" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010034</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1003</v>
@@ -2729,23 +2757,23 @@
         <v>1000001</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P36" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010035</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -2757,20 +2785,20 @@
         <v>1000001</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P37" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010041</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1004</v>
@@ -2785,20 +2813,20 @@
         <v>1000001</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T38" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010042</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1004</v>
@@ -2813,20 +2841,20 @@
         <v>1000001</v>
       </c>
       <c r="O39" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P39" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010043</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1004</v>
@@ -2841,20 +2869,20 @@
         <v>1000001</v>
       </c>
       <c r="O40" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P40" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010044</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1004</v>
@@ -2869,23 +2897,23 @@
         <v>1000001</v>
       </c>
       <c r="O41" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010045</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -2897,20 +2925,20 @@
         <v>1000001</v>
       </c>
       <c r="O42" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000020011</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>2001</v>
@@ -2925,20 +2953,20 @@
         <v>1000001</v>
       </c>
       <c r="O43" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020012</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>2001</v>
@@ -2953,20 +2981,20 @@
         <v>1000001</v>
       </c>
       <c r="O44" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020013</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>2001</v>
@@ -2981,20 +3009,20 @@
         <v>1000001</v>
       </c>
       <c r="O45" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020014</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>2001</v>
@@ -3009,23 +3037,23 @@
         <v>1000001</v>
       </c>
       <c r="O46" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P46" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020015</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3037,20 +3065,20 @@
         <v>1000001</v>
       </c>
       <c r="O47" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P47" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020021</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>2002</v>
@@ -3065,20 +3093,20 @@
         <v>1000001</v>
       </c>
       <c r="O48" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020022</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>2002</v>
@@ -3093,20 +3121,20 @@
         <v>1000001</v>
       </c>
       <c r="O49" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P49" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020023</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>2002</v>
@@ -3121,20 +3149,20 @@
         <v>1000001</v>
       </c>
       <c r="O50" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P50" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020024</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>2002</v>
@@ -3149,23 +3177,23 @@
         <v>1000001</v>
       </c>
       <c r="O51" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P51" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020025</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>3</v>
@@ -3177,20 +3205,20 @@
         <v>1000001</v>
       </c>
       <c r="O52" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P52" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020031</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2003</v>
@@ -3205,20 +3233,20 @@
         <v>1000001</v>
       </c>
       <c r="O53" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020032</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2003</v>
@@ -3233,20 +3261,20 @@
         <v>1000001</v>
       </c>
       <c r="O54" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P54" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020033</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2003</v>
@@ -3261,20 +3289,20 @@
         <v>1000001</v>
       </c>
       <c r="O55" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020034</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2003</v>
@@ -3289,23 +3317,23 @@
         <v>1000001</v>
       </c>
       <c r="O56" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P56" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020035</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
@@ -3317,20 +3345,20 @@
         <v>1000001</v>
       </c>
       <c r="O57" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P57" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020041</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>2004</v>
@@ -3345,20 +3373,20 @@
         <v>1000001</v>
       </c>
       <c r="O58" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P58" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020042</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2004</v>
@@ -3373,20 +3401,20 @@
         <v>1000001</v>
       </c>
       <c r="O59" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P59" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020043</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2004</v>
@@ -3401,20 +3429,20 @@
         <v>1000001</v>
       </c>
       <c r="O60" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P60" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020044</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2004</v>
@@ -3429,23 +3457,23 @@
         <v>1000001</v>
       </c>
       <c r="O61" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P61" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020045</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>3</v>
@@ -3457,20 +3485,20 @@
         <v>1000001</v>
       </c>
       <c r="O62" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P62" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="3">
       <c r="A63" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000030011</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>3001</v>
@@ -3485,20 +3513,20 @@
         <v>1000001</v>
       </c>
       <c r="O63" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P63" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030012</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>3001</v>
@@ -3513,20 +3541,20 @@
         <v>1000001</v>
       </c>
       <c r="O64" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P64" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030013</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>3001</v>
@@ -3541,20 +3569,20 @@
         <v>1000001</v>
       </c>
       <c r="O65" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P65" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030014</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>3001</v>
@@ -3569,23 +3597,23 @@
         <v>1000001</v>
       </c>
       <c r="O66" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P66" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030015</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>3</v>
@@ -3597,20 +3625,20 @@
         <v>1000001</v>
       </c>
       <c r="O67" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P67" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030021</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>3002</v>
@@ -3625,20 +3653,20 @@
         <v>1000001</v>
       </c>
       <c r="O68" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P68" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030022</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>3002</v>
@@ -3653,20 +3681,20 @@
         <v>1000001</v>
       </c>
       <c r="O69" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P69" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030023</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>3002</v>
@@ -3681,20 +3709,20 @@
         <v>1000001</v>
       </c>
       <c r="O70" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P70" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030024</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3002</v>
@@ -3709,23 +3737,23 @@
         <v>1000001</v>
       </c>
       <c r="O71" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P71" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030025</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>3</v>
@@ -3737,20 +3765,20 @@
         <v>1000001</v>
       </c>
       <c r="O72" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P72" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030031</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>3003</v>
@@ -3765,20 +3793,20 @@
         <v>1000001</v>
       </c>
       <c r="O73" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P73" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030032</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>3003</v>
@@ -3793,20 +3821,20 @@
         <v>1000001</v>
       </c>
       <c r="O74" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P74" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030033</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>3003</v>
@@ -3821,20 +3849,20 @@
         <v>1000001</v>
       </c>
       <c r="O75" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P75" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030034</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3003</v>
@@ -3849,23 +3877,23 @@
         <v>1000001</v>
       </c>
       <c r="O76" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P76" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030035</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>3</v>
@@ -3877,20 +3905,20 @@
         <v>1000001</v>
       </c>
       <c r="O77" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P77" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030041</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>3004</v>
@@ -3905,20 +3933,20 @@
         <v>1000001</v>
       </c>
       <c r="O78" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P78" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030042</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>3004</v>
@@ -3933,20 +3961,20 @@
         <v>1000001</v>
       </c>
       <c r="O79" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P79" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030043</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3004</v>
@@ -3961,20 +3989,20 @@
         <v>1000001</v>
       </c>
       <c r="O80" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P80" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030044</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3004</v>
@@ -3989,23 +4017,23 @@
         <v>1000001</v>
       </c>
       <c r="O81" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P81" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030045</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>3</v>
@@ -4017,20 +4045,20 @@
         <v>1000001</v>
       </c>
       <c r="O82" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P82" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000040011</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>4001</v>
@@ -4045,20 +4073,20 @@
         <v>1000001</v>
       </c>
       <c r="O83" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040012</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>4001</v>
@@ -4073,20 +4101,20 @@
         <v>1000001</v>
       </c>
       <c r="O84" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P84" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040013</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>4001</v>
@@ -4101,20 +4129,20 @@
         <v>1000001</v>
       </c>
       <c r="O85" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P85" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040014</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>4001</v>
@@ -4129,23 +4157,23 @@
         <v>1000001</v>
       </c>
       <c r="O86" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P86" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040015</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>3</v>
@@ -4157,20 +4185,20 @@
         <v>1000001</v>
       </c>
       <c r="O87" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P87" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040021</v>
       </c>
       <c r="B88" s="0" t="n">
         <v>4002</v>
@@ -4185,20 +4213,20 @@
         <v>1000001</v>
       </c>
       <c r="O88" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P88" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040022</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>4002</v>
@@ -4213,20 +4241,20 @@
         <v>1000001</v>
       </c>
       <c r="O89" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P89" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040023</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>4002</v>
@@ -4241,20 +4269,20 @@
         <v>1000001</v>
       </c>
       <c r="O90" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P90" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040024</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>4002</v>
@@ -4269,23 +4297,23 @@
         <v>1000001</v>
       </c>
       <c r="O91" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P91" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040025</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>3</v>
@@ -4297,20 +4325,20 @@
         <v>1000001</v>
       </c>
       <c r="O92" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P92" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040031</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>4003</v>
@@ -4325,20 +4353,20 @@
         <v>1000001</v>
       </c>
       <c r="O93" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P93" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040032</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>4003</v>
@@ -4353,20 +4381,20 @@
         <v>1000001</v>
       </c>
       <c r="O94" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P94" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040033</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>4003</v>
@@ -4381,20 +4409,20 @@
         <v>1000001</v>
       </c>
       <c r="O95" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P95" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040034</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>4003</v>
@@ -4409,23 +4437,23 @@
         <v>1000001</v>
       </c>
       <c r="O96" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P96" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040035</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>3</v>
@@ -4437,20 +4465,20 @@
         <v>1000001</v>
       </c>
       <c r="O97" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P97" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040041</v>
       </c>
       <c r="B98" s="0" t="n">
         <v>4004</v>
@@ -4465,20 +4493,20 @@
         <v>1000001</v>
       </c>
       <c r="O98" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P98" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040042</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>4004</v>
@@ -4493,20 +4521,20 @@
         <v>1000001</v>
       </c>
       <c r="O99" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P99" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040043</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>4004</v>
@@ -4521,20 +4549,20 @@
         <v>1000001</v>
       </c>
       <c r="O100" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P100" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040044</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4004</v>
@@ -4549,23 +4577,23 @@
         <v>1000001</v>
       </c>
       <c r="O101" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P101" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040045</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>3</v>
@@ -4577,20 +4605,20 @@
         <v>1000001</v>
       </c>
       <c r="O102" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P102" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040051</v>
       </c>
       <c r="B103" s="0" t="n">
         <v>4005</v>
@@ -4605,20 +4633,20 @@
         <v>1000001</v>
       </c>
       <c r="O103" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P103" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040052</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>4005</v>
@@ -4633,20 +4661,20 @@
         <v>1000001</v>
       </c>
       <c r="O104" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P104" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040053</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>4005</v>
@@ -4661,20 +4689,20 @@
         <v>1000001</v>
       </c>
       <c r="O105" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P105" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040054</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4005</v>
@@ -4689,23 +4717,23 @@
         <v>1000001</v>
       </c>
       <c r="O106" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P106" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040055</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>3</v>
@@ -4717,20 +4745,20 @@
         <v>1000001</v>
       </c>
       <c r="O107" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P107" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000050011</v>
       </c>
       <c r="B108" s="0" t="n">
         <v>5001</v>
@@ -4745,20 +4773,20 @@
         <v>1000001</v>
       </c>
       <c r="O108" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P108" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050012</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>5001</v>
@@ -4773,20 +4801,20 @@
         <v>1000001</v>
       </c>
       <c r="O109" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P109" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050013</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>5001</v>
@@ -4801,20 +4829,20 @@
         <v>1000001</v>
       </c>
       <c r="O110" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P110" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050014</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>5001</v>
@@ -4829,23 +4857,23 @@
         <v>1000001</v>
       </c>
       <c r="O111" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P111" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050015</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>3</v>
@@ -4857,20 +4885,20 @@
         <v>1000001</v>
       </c>
       <c r="O112" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P112" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050021</v>
       </c>
       <c r="B113" s="0" t="n">
         <v>5002</v>
@@ -4885,20 +4913,20 @@
         <v>1000001</v>
       </c>
       <c r="O113" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P113" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050022</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>5002</v>
@@ -4913,20 +4941,20 @@
         <v>1000001</v>
       </c>
       <c r="O114" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P114" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050023</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>5002</v>
@@ -4941,20 +4969,20 @@
         <v>1000001</v>
       </c>
       <c r="O115" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P115" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050024</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>5002</v>
@@ -4969,23 +4997,23 @@
         <v>1000001</v>
       </c>
       <c r="O116" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P116" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050025</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>3</v>
@@ -4997,20 +5025,20 @@
         <v>1000001</v>
       </c>
       <c r="O117" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P117" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050031</v>
       </c>
       <c r="B118" s="0" t="n">
         <v>5003</v>
@@ -5025,20 +5053,20 @@
         <v>1000001</v>
       </c>
       <c r="O118" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P118" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050032</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>5003</v>
@@ -5053,20 +5081,20 @@
         <v>1000001</v>
       </c>
       <c r="O119" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P119" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050033</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>5003</v>
@@ -5081,20 +5109,20 @@
         <v>1000001</v>
       </c>
       <c r="O120" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P120" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050034</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>5003</v>
@@ -5109,23 +5137,23 @@
         <v>1000001</v>
       </c>
       <c r="O121" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P121" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050035</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>3</v>
@@ -5137,20 +5165,20 @@
         <v>1000001</v>
       </c>
       <c r="O122" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P122" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050041</v>
       </c>
       <c r="B123" s="0" t="n">
         <v>5004</v>
@@ -5165,20 +5193,20 @@
         <v>1000001</v>
       </c>
       <c r="O123" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P123" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050042</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>5004</v>
@@ -5193,20 +5221,20 @@
         <v>1000001</v>
       </c>
       <c r="O124" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P124" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050043</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>5004</v>
@@ -5221,20 +5249,20 @@
         <v>1000001</v>
       </c>
       <c r="O125" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P125" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050044</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5004</v>
@@ -5249,23 +5277,23 @@
         <v>1000001</v>
       </c>
       <c r="O126" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P126" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050045</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>3</v>
@@ -5277,20 +5305,20 @@
         <v>1000001</v>
       </c>
       <c r="O127" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P127" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000060011</v>
       </c>
       <c r="B128" s="0" t="n">
         <v>6001</v>
@@ -5305,20 +5333,20 @@
         <v>1000001</v>
       </c>
       <c r="O128" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P128" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060012</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>6001</v>
@@ -5333,20 +5361,20 @@
         <v>1000001</v>
       </c>
       <c r="O129" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P129" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060013</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>6001</v>
@@ -5361,20 +5389,20 @@
         <v>1000001</v>
       </c>
       <c r="O130" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P130" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060014</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>6001</v>
@@ -5389,23 +5417,23 @@
         <v>1000001</v>
       </c>
       <c r="O131" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P131" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060015</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>3</v>
@@ -5417,20 +5445,20 @@
         <v>1000001</v>
       </c>
       <c r="O132" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P132" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060021</v>
       </c>
       <c r="B133" s="0" t="n">
         <v>6002</v>
@@ -5445,20 +5473,20 @@
         <v>1000001</v>
       </c>
       <c r="O133" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P133" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060022</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>6002</v>
@@ -5473,20 +5501,20 @@
         <v>1000001</v>
       </c>
       <c r="O134" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P134" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060023</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>6002</v>
@@ -5501,20 +5529,20 @@
         <v>1000001</v>
       </c>
       <c r="O135" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P135" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060024</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>6002</v>
@@ -5529,23 +5557,23 @@
         <v>1000001</v>
       </c>
       <c r="O136" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P136" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060025</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>3</v>
@@ -5557,20 +5585,20 @@
         <v>1000001</v>
       </c>
       <c r="O137" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P137" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060031</v>
       </c>
       <c r="B138" s="0" t="n">
         <v>6003</v>
@@ -5585,20 +5613,20 @@
         <v>1000001</v>
       </c>
       <c r="O138" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P138" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060032</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>6003</v>
@@ -5613,20 +5641,20 @@
         <v>1000001</v>
       </c>
       <c r="O139" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P139" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060033</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>6003</v>
@@ -5641,20 +5669,20 @@
         <v>1000001</v>
       </c>
       <c r="O140" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P140" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060034</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>6003</v>
@@ -5669,23 +5697,23 @@
         <v>1000001</v>
       </c>
       <c r="O141" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P141" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060035</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>3</v>
@@ -5697,20 +5725,20 @@
         <v>1000001</v>
       </c>
       <c r="O142" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P142" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060041</v>
       </c>
       <c r="B143" s="0" t="n">
         <v>6004</v>
@@ -5725,20 +5753,20 @@
         <v>1000001</v>
       </c>
       <c r="O143" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P143" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060042</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>6004</v>
@@ -5753,20 +5781,20 @@
         <v>1000001</v>
       </c>
       <c r="O144" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P144" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060043</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>6004</v>
@@ -5781,20 +5809,20 @@
         <v>1000001</v>
       </c>
       <c r="O145" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P145" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060044</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6004</v>
@@ -5809,23 +5837,23 @@
         <v>1000001</v>
       </c>
       <c r="O146" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P146" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060045</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>3</v>
@@ -5837,20 +5865,20 @@
         <v>1000001</v>
       </c>
       <c r="O147" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P147" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060051</v>
       </c>
       <c r="B148" s="0" t="n">
         <v>6005</v>
@@ -5865,20 +5893,20 @@
         <v>1000001</v>
       </c>
       <c r="O148" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P148" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060052</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>6005</v>
@@ -5893,20 +5921,20 @@
         <v>1000001</v>
       </c>
       <c r="O149" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P149" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060053</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>6005</v>
@@ -5921,20 +5949,20 @@
         <v>1000001</v>
       </c>
       <c r="O150" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P150" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060054</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6005</v>
@@ -5949,23 +5977,23 @@
         <v>1000001</v>
       </c>
       <c r="O151" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P151" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060055</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>3</v>
@@ -5977,20 +6005,20 @@
         <v>1000001</v>
       </c>
       <c r="O152" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P152" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000070011</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>7001</v>
@@ -6005,20 +6033,20 @@
         <v>1000001</v>
       </c>
       <c r="O153" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P153" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070012</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>7001</v>
@@ -6033,20 +6061,20 @@
         <v>1000001</v>
       </c>
       <c r="O154" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P154" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070013</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>7001</v>
@@ -6061,20 +6089,20 @@
         <v>1000001</v>
       </c>
       <c r="O155" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P155" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070014</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>7001</v>
@@ -6089,23 +6117,23 @@
         <v>1000001</v>
       </c>
       <c r="O156" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P156" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070015</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>3</v>
@@ -6117,20 +6145,20 @@
         <v>1000001</v>
       </c>
       <c r="O157" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P157" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070021</v>
       </c>
       <c r="B158" s="0" t="n">
         <v>7002</v>
@@ -6145,20 +6173,20 @@
         <v>1000001</v>
       </c>
       <c r="O158" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P158" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070022</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>7002</v>
@@ -6173,20 +6201,20 @@
         <v>1000001</v>
       </c>
       <c r="O159" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P159" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070023</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>7002</v>
@@ -6201,20 +6229,20 @@
         <v>1000001</v>
       </c>
       <c r="O160" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P160" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070024</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>7002</v>
@@ -6229,23 +6257,23 @@
         <v>1000001</v>
       </c>
       <c r="O161" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P161" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070025</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>3</v>
@@ -6257,20 +6285,20 @@
         <v>1000001</v>
       </c>
       <c r="O162" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P162" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070031</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>7003</v>
@@ -6285,20 +6313,20 @@
         <v>1000001</v>
       </c>
       <c r="O163" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P163" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070032</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>7003</v>
@@ -6313,20 +6341,20 @@
         <v>1000001</v>
       </c>
       <c r="O164" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P164" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070033</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>7003</v>
@@ -6341,20 +6369,20 @@
         <v>1000001</v>
       </c>
       <c r="O165" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P165" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070034</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>7003</v>
@@ -6369,23 +6397,23 @@
         <v>1000001</v>
       </c>
       <c r="O166" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P166" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070035</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>3</v>
@@ -6397,20 +6425,20 @@
         <v>1000001</v>
       </c>
       <c r="O167" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P167" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070041</v>
       </c>
       <c r="B168" s="0" t="n">
         <v>7004</v>
@@ -6425,20 +6453,20 @@
         <v>1000001</v>
       </c>
       <c r="O168" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P168" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070042</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>7004</v>
@@ -6453,20 +6481,20 @@
         <v>1000001</v>
       </c>
       <c r="O169" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P169" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070043</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>7004</v>
@@ -6481,20 +6509,20 @@
         <v>1000001</v>
       </c>
       <c r="O170" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P170" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级4</t>
+          <t>议会随机议员-生物7004-评级3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070044</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7004</v>
@@ -6509,12 +6537,40 @@
         <v>1000001</v>
       </c>
       <c r="O171" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P171" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T171" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B172" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       <c r="R17" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="0" t="n">
         <v>100002</v>
       </c>
       <c r="T17" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="R18" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="0" t="n">
         <v>100003</v>
       </c>
       <c r="T18" s="4" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X173"/>
+  <dimension ref="A1:Y174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -1200,6 +1200,11 @@
       </c>
       <c r="X1" s="0" t="inlineStr">
         <is>
+          <t>icon_res</t>
+        </is>
+      </c>
+      <c r="Y1" s="0" t="inlineStr">
+        <is>
           <t>remark</t>
         </is>
       </c>
@@ -1325,6 +1330,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="Y2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1444,6 +1454,11 @@
       </c>
       <c r="X3" s="0" t="inlineStr">
         <is>
+          <t>头像图片-UI图集sprite名(支持「名,图集」后缀;空=用spine形象展示;无spine资源的NPC(如仅对话使用)配置此字段)</t>
+        </is>
+      </c>
+      <c r="Y3" s="0" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -1464,7 +1479,7 @@
       <c r="P4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="X4" s="0" t="inlineStr">
+      <c r="Y4" s="0" t="inlineStr">
         <is>
           <t>初始创建赠送-没头脑</t>
         </is>
@@ -1486,7 +1501,7 @@
       <c r="P5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="X5" s="0" t="inlineStr">
+      <c r="Y5" s="0" t="inlineStr">
         <is>
           <t>初始创建赠送-不高兴</t>
         </is>
@@ -1508,103 +1523,91 @@
       <c r="P6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="X6" s="0" t="inlineStr">
+      <c r="Y6" s="0" t="inlineStr">
         <is>
           <t>初始创建赠送-忠诚</t>
         </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="1">
-      <c r="A7" s="4" t="n">
-        <v>1010010001</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>101001</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>11000001&amp;10200003&amp;10300003&amp;</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>1010010001</v>
-      </c>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>冒险者</t>
+      <c r="A7" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>ui_book_1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>特殊NPC-监视之塔(新手引导,仅对话系统使用,无生物资源)</t>
         </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="A8" s="4" t="n">
-        <v>1010020001</v>
+        <v>1010010001</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>101002</v>
+        <v>101001</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>1000</v>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>8</v>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
@@ -1613,170 +1616,166 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>10200001&amp;10300001&amp;11020021&amp;</t>
+          <t>11000001&amp;10200003&amp;10300003&amp;</t>
         </is>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1010020001</v>
+        <v>1010010001</v>
       </c>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="1" t="n">
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>冒险者</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="1">
+      <c r="A9" s="4" t="n">
+        <v>1010020001</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>10200001&amp;10300001&amp;11020021&amp;</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>1010020001</v>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="T8" s="1" t="inlineStr">
+      <c r="T9" s="1" t="inlineStr">
         <is>
           <t>100001</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>持盾战士-Boss</t>
         </is>
       </c>
     </row>
-    <row r="9" customFormat="1" s="1">
-      <c r="A9" s="1" t="n">
+    <row r="10" customFormat="1" s="1">
+      <c r="A10" s="1" t="n">
         <v>1010020002</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B10" s="1" t="n">
         <v>101002</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="C10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="1" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="M10" s="1" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>10200001&amp;10300001&amp;11020021&amp;</t>
         </is>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P10" s="1" t="n">
         <v>1010020001</v>
       </c>
-      <c r="S9" s="1" t="inlineStr">
+      <c r="S10" s="1" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="X9" s="1" t="inlineStr">
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>持盾战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="1">
-      <c r="A10" s="4" t="n">
-        <v>1020010001</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>102001</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>1020010001</v>
-      </c>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>弓箭手</t>
         </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="A11" s="4" t="n">
-        <v>1020020001</v>
+        <v>1020010001</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>102002</v>
+        <v>102001</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1792,29 +1791,31 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>10200006&amp;10300006&amp;11010002&amp;</t>
+          <t>10100004&amp;10200004&amp;10300004&amp;11010001&amp;</t>
         </is>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1020020001</v>
+        <v>1020010001</v>
       </c>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
-      <c r="S11" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>强弓手-Boss</t>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>弓箭手</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020001</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>102003</v>
+        <v>102002</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1</v>
@@ -1823,10 +1824,8 @@
       <c r="E12" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>200</v>
@@ -1853,48 +1852,44 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
+          <t>10200006&amp;10300006&amp;11010002&amp;</t>
         </is>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1020030001</v>
+        <v>1020020001</v>
       </c>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>连射手-Boss</t>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>强弓手-Boss</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>103001</v>
+        <v>102003</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E13" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G13" s="4" t="n">
+        <v>200</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1902,7 +1897,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1918,31 +1913,29 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11010003&amp;</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1030010001</v>
+        <v>1020030001</v>
       </c>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>人类-魔法师（火）</t>
+      <c r="S13" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>连射手-Boss</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" s="4" t="n">
-        <v>1030020001</v>
+        <v>1030010001</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>103002</v>
+        <v>103001</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
@@ -1985,11 +1978,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
+          <t>10200007&amp;10300007&amp;11000003&amp;10100007&amp;</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1030020001</v>
+        <v>1030010001</v>
       </c>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
@@ -1998,18 +1991,18 @@
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>人类-魔法师（水）</t>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>人类-魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
       <c r="A15" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030020001</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>103003</v>
+        <v>103002</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1</v>
@@ -2052,11 +2045,11 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
+          <t>10100007&amp;10200007&amp;10300007&amp;11000004&amp;</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1030030001</v>
+        <v>1030020001</v>
       </c>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
@@ -2065,18 +2058,18 @@
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>人类-魔法师（冰）</t>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>人类-魔法师（水）</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030030001</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>103004</v>
+        <v>103003</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1</v>
@@ -2119,11 +2112,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
+          <t>10200007&amp;10100007&amp;10300007&amp;11000010&amp;</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1030040001</v>
+        <v>1030030001</v>
       </c>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
@@ -2132,18 +2125,18 @@
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>人类-魔法师（雷）</t>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>人类-魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030040001</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>103101</v>
+        <v>103004</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1</v>
@@ -2186,32 +2179,31 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+          <t>10200005&amp;10300005&amp;10100007&amp;11000011&amp;</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1031010001</v>
+        <v>1030040001</v>
       </c>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
-      <c r="S17" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>100002</v>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>人类-大魔法师（火）</t>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>人类-魔法师（雷）</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="4" t="n">
-        <v>1031020001</v>
+        <v>1031010001</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>103102</v>
+        <v>103101</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1</v>
@@ -2258,7 +2250,7 @@
         </is>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1031010002</v>
+        <v>1031010001</v>
       </c>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
@@ -2266,20 +2258,20 @@
         <v>1.2</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>100003</v>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>人类-大魔法师（水）</t>
+        <v>100002</v>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>人类-大魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="19" customFormat="1" s="2">
       <c r="A19" s="4" t="n">
-        <v>1031030001</v>
+        <v>1031020001</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>103103</v>
+        <v>103102</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1</v>
@@ -2326,120 +2318,94 @@
         </is>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1031010003</v>
+        <v>1031010002</v>
       </c>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="X19" s="4" t="inlineStr">
+      <c r="T19" s="1" t="n">
+        <v>100003</v>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>人类-大魔法师（水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="1" s="2">
+      <c r="A20" s="4" t="n">
+        <v>1031030001</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>103103</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>11000007&amp;10100015&amp;10200015&amp;10300015&amp;</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>1031010003</v>
+      </c>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>人类-大魔法师（冰）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="1" s="2">
-      <c r="A20" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>10200016&amp;10300016&amp;</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="n">
-        <v>2000000001</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>cn</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="2">
       <c r="A21" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2485,7 +2451,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5050011&amp;5070005&amp;</t>
+          <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2495,17 +2461,23 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
-        </is>
-      </c>
+          <t>10200016&amp;10300016&amp;</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>2000000002</v>
+        <v>2000000001</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>5</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
+        </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2515,107 +2487,107 @@
       <c r="W21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>宛家伟</t>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>白剑伟</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000002</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="0" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="0" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="0" t="inlineStr">
-        <is>
-          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
-        </is>
-      </c>
-      <c r="M22" s="0" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5050011&amp;5070005&amp;</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+          <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>2000000003</v>
+        <v>2000000002</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W22" s="0" t="n">
+      <c r="W22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>雷神天尊斩</t>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>宛家伟</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="2" t="n">
-        <v>2000000004</v>
+        <v>2000000003</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2661,7 +2633,7 @@
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
+          <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
         </is>
       </c>
       <c r="M23" s="0" t="inlineStr">
@@ -2671,21 +2643,17 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10300011&amp;10200011&amp;</t>
-        </is>
-      </c>
-      <c r="O23" s="0" t="inlineStr"/>
+          <t>40200006&amp;40300003&amp;41000004&amp;</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n">
-        <v>2000000004</v>
+        <v>2000000003</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R23" s="2" t="n"/>
-      <c r="U23" s="0" t="inlineStr">
-        <is>
-          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
-        </is>
+      <c r="R23" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -2695,51 +2663,107 @@
       <c r="W23" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>雷神天尊斩</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="2" t="n">
+        <v>2000000004</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
+        </is>
+      </c>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10300011&amp;10200011&amp;</t>
+        </is>
+      </c>
+      <c r="O24" s="0" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>2000000004</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" s="2" t="n"/>
+      <c r="U24" s="0" t="inlineStr">
+        <is>
+          <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="W24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>卡米莉娅</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O24" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N</t>
-        </is>
-      </c>
-      <c r="P24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000010012</v>
+        <v>3000010011</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>1001</v>
@@ -2755,27 +2779,27 @@
       </c>
       <c r="O25" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="3">
       <c r="A26" s="0" t="n">
-        <v>3000010013</v>
+        <v>3000010012</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>1001</v>
@@ -2791,27 +2815,27 @@
       </c>
       <c r="O26" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2</v>
-      </c>
-      <c r="X26" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000010014</v>
+        <v>3000010013</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>1001</v>
@@ -2827,27 +2851,27 @@
       </c>
       <c r="O27" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010014</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>1001</v>
@@ -2863,31 +2887,30 @@
       </c>
       <c r="O28" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S28" s="0" t="inlineStr"/>
-      <c r="W28" t="n">
-        <v>3</v>
-      </c>
-      <c r="X28" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y28" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010015</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2900,27 +2923,28 @@
       </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="S29" s="0" t="inlineStr"/>
+      <c r="W29" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010021</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1002</v>
@@ -2936,27 +2960,27 @@
       </c>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010022</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1002</v>
@@ -2972,27 +2996,27 @@
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X31" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010023</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>1002</v>
@@ -3008,27 +3032,27 @@
       </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2</v>
-      </c>
-      <c r="X32" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W32" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010024</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>1002</v>
@@ -3044,30 +3068,30 @@
       </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3</v>
-      </c>
-      <c r="X33" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010025</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -3080,27 +3104,27 @@
       </c>
       <c r="O34" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010031</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>1003</v>
@@ -3116,27 +3140,27 @@
       </c>
       <c r="O35" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010032</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1003</v>
@@ -3152,27 +3176,27 @@
       </c>
       <c r="O36" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2</v>
-      </c>
-      <c r="X36" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010033</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>1003</v>
@@ -3188,27 +3212,27 @@
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2</v>
-      </c>
-      <c r="X37" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y37" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010034</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1003</v>
@@ -3224,30 +3248,30 @@
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3</v>
-      </c>
-      <c r="X38" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W38" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y38" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010035</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3260,27 +3284,27 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W39" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010041</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1004</v>
@@ -3296,27 +3320,27 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1</v>
-      </c>
-      <c r="X40" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010042</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1004</v>
@@ -3332,27 +3356,27 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2</v>
-      </c>
-      <c r="X41" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010043</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1004</v>
@@ -3368,27 +3392,27 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2</v>
-      </c>
-      <c r="X42" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W42" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y42" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010044</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>1004</v>
@@ -3404,30 +3428,30 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3</v>
-      </c>
-      <c r="X43" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W43" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y43" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010045</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3440,27 +3464,27 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W44" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000020011</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>2001</v>
@@ -3476,27 +3500,27 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
-      <c r="X45" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000020012</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>2001</v>
@@ -3512,27 +3536,27 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W46" t="n">
-        <v>2</v>
-      </c>
-      <c r="X46" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000020013</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>2001</v>
@@ -3548,27 +3572,27 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W47" t="n">
-        <v>2</v>
-      </c>
-      <c r="X47" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020014</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>2001</v>
@@ -3584,30 +3608,30 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>3</v>
-      </c>
-      <c r="X48" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W48" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020015</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>3</v>
@@ -3620,27 +3644,27 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
-      <c r="X49" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020021</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>2002</v>
@@ -3656,27 +3680,27 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X50" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020022</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>2002</v>
@@ -3692,27 +3716,27 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2</v>
-      </c>
-      <c r="X51" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020023</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2002</v>
@@ -3728,27 +3752,27 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W52" t="n">
-        <v>2</v>
-      </c>
-      <c r="X52" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W52" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y52" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020024</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2002</v>
@@ -3764,30 +3788,30 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W53" t="n">
-        <v>3</v>
-      </c>
-      <c r="X53" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W53" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y53" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020025</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -3800,27 +3824,27 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W54" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020031</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>2003</v>
@@ -3836,27 +3860,27 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020032</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>2003</v>
@@ -3872,27 +3896,27 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X56" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020033</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>2003</v>
@@ -3908,27 +3932,27 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W57" t="n">
-        <v>2</v>
-      </c>
-      <c r="X57" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W57" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y57" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020034</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>2003</v>
@@ -3944,30 +3968,30 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W58" t="n">
-        <v>3</v>
-      </c>
-      <c r="X58" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W58" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y58" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020035</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>3</v>
@@ -3980,27 +4004,27 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1</v>
-      </c>
-      <c r="X59" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W59" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020041</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2004</v>
@@ -4016,27 +4040,27 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1</v>
-      </c>
-      <c r="X60" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020042</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2004</v>
@@ -4052,27 +4076,27 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W61" t="n">
-        <v>2</v>
-      </c>
-      <c r="X61" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020043</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>2004</v>
@@ -4088,27 +4112,27 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W62" t="n">
-        <v>2</v>
-      </c>
-      <c r="X62" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y62" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020044</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>2004</v>
@@ -4124,30 +4148,30 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W63" t="n">
-        <v>3</v>
-      </c>
-      <c r="X63" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物2004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y63" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020045</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>3</v>
@@ -4160,27 +4184,27 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W64" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y64" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000030011</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>3001</v>
@@ -4196,27 +4220,27 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1</v>
-      </c>
-      <c r="X65" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000030012</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>3001</v>
@@ -4232,27 +4256,27 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W66" t="n">
-        <v>2</v>
-      </c>
-      <c r="X66" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000030013</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>3001</v>
@@ -4268,27 +4292,27 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W67" t="n">
-        <v>2</v>
-      </c>
-      <c r="X67" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W67" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y67" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030014</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>3001</v>
@@ -4304,30 +4328,30 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W68" t="n">
-        <v>3</v>
-      </c>
-      <c r="X68" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W68" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y68" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030015</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>3</v>
@@ -4340,27 +4364,27 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1</v>
-      </c>
-      <c r="X69" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W69" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y69" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030021</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>3002</v>
@@ -4376,27 +4400,27 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030022</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3002</v>
@@ -4412,27 +4436,27 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W71" t="n">
-        <v>2</v>
-      </c>
-      <c r="X71" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y71" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030023</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>3002</v>
@@ -4448,27 +4472,27 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W72" t="n">
-        <v>2</v>
-      </c>
-      <c r="X72" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W72" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y72" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030024</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>3002</v>
@@ -4484,30 +4508,30 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W73" t="n">
-        <v>3</v>
-      </c>
-      <c r="X73" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y73" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030025</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>3</v>
@@ -4520,27 +4544,27 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1</v>
-      </c>
-      <c r="X74" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W74" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y74" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030031</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>3003</v>
@@ -4556,27 +4580,27 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W75" t="n">
-        <v>1</v>
-      </c>
-      <c r="X75" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030032</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3003</v>
@@ -4592,27 +4616,27 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W76" t="n">
-        <v>2</v>
-      </c>
-      <c r="X76" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030033</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>3003</v>
@@ -4628,27 +4652,27 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W77" t="n">
-        <v>2</v>
-      </c>
-      <c r="X77" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W77" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y77" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030034</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>3003</v>
@@ -4664,30 +4688,30 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W78" t="n">
-        <v>3</v>
-      </c>
-      <c r="X78" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W78" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y78" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030035</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>3</v>
@@ -4700,27 +4724,27 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1</v>
-      </c>
-      <c r="X79" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W79" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y79" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030041</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3004</v>
@@ -4736,27 +4760,27 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1</v>
-      </c>
-      <c r="X80" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030042</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>3004</v>
@@ -4772,27 +4796,27 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W81" t="n">
-        <v>2</v>
-      </c>
-      <c r="X81" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030043</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>3004</v>
@@ -4808,27 +4832,27 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W82" t="n">
-        <v>2</v>
-      </c>
-      <c r="X82" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W82" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y82" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030044</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>3004</v>
@@ -4844,30 +4868,30 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W83" t="n">
-        <v>3</v>
-      </c>
-      <c r="X83" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物3004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W83" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y83" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030045</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>3</v>
@@ -4880,27 +4904,27 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W84" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y84" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000040011</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>4001</v>
@@ -4916,27 +4940,27 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1</v>
-      </c>
-      <c r="X85" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000040012</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>4001</v>
@@ -4952,27 +4976,27 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W86" t="n">
-        <v>2</v>
-      </c>
-      <c r="X86" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000040013</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>4001</v>
@@ -4988,27 +5012,27 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W87" t="n">
-        <v>2</v>
-      </c>
-      <c r="X87" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W87" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y87" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040014</v>
       </c>
       <c r="B88" s="0" t="n">
         <v>4001</v>
@@ -5024,30 +5048,30 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W88" t="n">
-        <v>3</v>
-      </c>
-      <c r="X88" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W88" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y88" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040015</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>3</v>
@@ -5060,27 +5084,27 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W89" t="n">
-        <v>1</v>
-      </c>
-      <c r="X89" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W89" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040021</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>4002</v>
@@ -5096,27 +5120,27 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
-      <c r="X90" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W90" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040022</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>4002</v>
@@ -5132,27 +5156,27 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W91" t="n">
-        <v>2</v>
-      </c>
-      <c r="X91" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040023</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>4002</v>
@@ -5168,27 +5192,27 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W92" t="n">
-        <v>2</v>
-      </c>
-      <c r="X92" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y92" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040024</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>4002</v>
@@ -5204,30 +5228,30 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W93" t="n">
-        <v>3</v>
-      </c>
-      <c r="X93" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W93" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y93" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040025</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>3</v>
@@ -5240,27 +5264,27 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W94" t="n">
-        <v>1</v>
-      </c>
-      <c r="X94" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W94" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040031</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>4003</v>
@@ -5276,27 +5300,27 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W95" t="n">
-        <v>1</v>
-      </c>
-      <c r="X95" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y95" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040032</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>4003</v>
@@ -5312,27 +5336,27 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W96" t="n">
-        <v>2</v>
-      </c>
-      <c r="X96" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W96" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040033</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>4003</v>
@@ -5348,27 +5372,27 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W97" t="n">
-        <v>2</v>
-      </c>
-      <c r="X97" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W97" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y97" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040034</v>
       </c>
       <c r="B98" s="0" t="n">
         <v>4003</v>
@@ -5384,30 +5408,30 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W98" t="n">
-        <v>3</v>
-      </c>
-      <c r="X98" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W98" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y98" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040035</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>3</v>
@@ -5420,27 +5444,27 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W99" t="n">
-        <v>1</v>
-      </c>
-      <c r="X99" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W99" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y99" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040041</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>4004</v>
@@ -5456,27 +5480,27 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W100" t="n">
-        <v>1</v>
-      </c>
-      <c r="X100" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W100" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040042</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>4004</v>
@@ -5492,27 +5516,27 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W101" t="n">
-        <v>2</v>
-      </c>
-      <c r="X101" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W101" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040043</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>4004</v>
@@ -5528,27 +5552,27 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W102" t="n">
-        <v>2</v>
-      </c>
-      <c r="X102" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W102" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y102" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040044</v>
       </c>
       <c r="B103" s="0" t="n">
         <v>4004</v>
@@ -5564,30 +5588,30 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W103" t="n">
-        <v>3</v>
-      </c>
-      <c r="X103" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W103" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y103" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040045</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>3</v>
@@ -5600,27 +5624,27 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W104" t="n">
-        <v>1</v>
-      </c>
-      <c r="X104" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4005-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W104" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y104" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040051</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>4005</v>
@@ -5636,27 +5660,27 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W105" t="n">
-        <v>1</v>
-      </c>
-      <c r="X105" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4005-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W105" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040052</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>4005</v>
@@ -5672,27 +5696,27 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W106" t="n">
-        <v>2</v>
-      </c>
-      <c r="X106" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4005-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W106" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040053</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>4005</v>
@@ -5708,27 +5732,27 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W107" t="n">
-        <v>2</v>
-      </c>
-      <c r="X107" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4005-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W107" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y107" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040054</v>
       </c>
       <c r="B108" s="0" t="n">
         <v>4005</v>
@@ -5744,30 +5768,30 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W108" t="n">
-        <v>3</v>
-      </c>
-      <c r="X108" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物4005-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W108" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y108" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040055</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>3</v>
@@ -5780,27 +5804,27 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W109" t="n">
-        <v>1</v>
-      </c>
-      <c r="X109" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W109" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y109" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000050011</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>5001</v>
@@ -5816,27 +5840,27 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W110" t="n">
-        <v>1</v>
-      </c>
-      <c r="X110" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W110" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y110" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000050012</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>5001</v>
@@ -5852,27 +5876,27 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W111" t="n">
-        <v>2</v>
-      </c>
-      <c r="X111" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W111" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000050013</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>5001</v>
@@ -5888,27 +5912,27 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W112" t="n">
-        <v>2</v>
-      </c>
-      <c r="X112" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W112" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y112" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050014</v>
       </c>
       <c r="B113" s="0" t="n">
         <v>5001</v>
@@ -5924,30 +5948,30 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W113" t="n">
-        <v>3</v>
-      </c>
-      <c r="X113" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W113" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y113" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050015</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>3</v>
@@ -5960,27 +5984,27 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W114" t="n">
-        <v>1</v>
-      </c>
-      <c r="X114" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W114" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y114" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050021</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>5002</v>
@@ -5996,27 +6020,27 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W115" t="n">
-        <v>1</v>
-      </c>
-      <c r="X115" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050022</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>5002</v>
@@ -6032,27 +6056,27 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W116" t="n">
-        <v>2</v>
-      </c>
-      <c r="X116" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y116" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050023</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>5002</v>
@@ -6068,27 +6092,27 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W117" t="n">
-        <v>2</v>
-      </c>
-      <c r="X117" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W117" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y117" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050024</v>
       </c>
       <c r="B118" s="0" t="n">
         <v>5002</v>
@@ -6104,30 +6128,30 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W118" t="n">
-        <v>3</v>
-      </c>
-      <c r="X118" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W118" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y118" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050025</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>3</v>
@@ -6140,27 +6164,27 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W119" t="n">
-        <v>1</v>
-      </c>
-      <c r="X119" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W119" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y119" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050031</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>5003</v>
@@ -6176,27 +6200,27 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W120" t="n">
-        <v>1</v>
-      </c>
-      <c r="X120" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050032</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>5003</v>
@@ -6212,27 +6236,27 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W121" t="n">
-        <v>2</v>
-      </c>
-      <c r="X121" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y121" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050033</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>5003</v>
@@ -6248,27 +6272,27 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W122" t="n">
-        <v>2</v>
-      </c>
-      <c r="X122" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W122" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y122" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050034</v>
       </c>
       <c r="B123" s="0" t="n">
         <v>5003</v>
@@ -6284,30 +6308,30 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W123" t="n">
-        <v>3</v>
-      </c>
-      <c r="X123" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W123" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y123" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050035</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>3</v>
@@ -6320,27 +6344,27 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W124" t="n">
-        <v>1</v>
-      </c>
-      <c r="X124" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W124" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y124" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050041</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>5004</v>
@@ -6356,27 +6380,27 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W125" t="n">
-        <v>1</v>
-      </c>
-      <c r="X125" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W125" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y125" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050042</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>5004</v>
@@ -6392,27 +6416,27 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W126" t="n">
-        <v>2</v>
-      </c>
-      <c r="X126" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W126" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y126" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050043</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>5004</v>
@@ -6428,27 +6452,27 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W127" t="n">
-        <v>2</v>
-      </c>
-      <c r="X127" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W127" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y127" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050044</v>
       </c>
       <c r="B128" s="0" t="n">
         <v>5004</v>
@@ -6464,30 +6488,30 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W128" t="n">
-        <v>3</v>
-      </c>
-      <c r="X128" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物5004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W128" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y128" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050045</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>3</v>
@@ -6500,27 +6524,27 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W129" t="n">
-        <v>1</v>
-      </c>
-      <c r="X129" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W129" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y129" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000060011</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>6001</v>
@@ -6536,27 +6560,27 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W130" t="n">
-        <v>1</v>
-      </c>
-      <c r="X130" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y130" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000060012</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>6001</v>
@@ -6572,27 +6596,27 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W131" t="n">
-        <v>2</v>
-      </c>
-      <c r="X131" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W131" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y131" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000060013</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>6001</v>
@@ -6608,27 +6632,27 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W132" t="n">
-        <v>2</v>
-      </c>
-      <c r="X132" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W132" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y132" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060014</v>
       </c>
       <c r="B133" s="0" t="n">
         <v>6001</v>
@@ -6644,30 +6668,30 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W133" t="n">
-        <v>3</v>
-      </c>
-      <c r="X133" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W133" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y133" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060015</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>3</v>
@@ -6680,27 +6704,27 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W134" t="n">
-        <v>1</v>
-      </c>
-      <c r="X134" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W134" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y134" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060021</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>6002</v>
@@ -6716,27 +6740,27 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W135" t="n">
-        <v>1</v>
-      </c>
-      <c r="X135" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W135" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y135" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060022</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>6002</v>
@@ -6752,27 +6776,27 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W136" t="n">
-        <v>2</v>
-      </c>
-      <c r="X136" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y136" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060023</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>6002</v>
@@ -6788,27 +6812,27 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W137" t="n">
-        <v>2</v>
-      </c>
-      <c r="X137" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W137" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y137" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060024</v>
       </c>
       <c r="B138" s="0" t="n">
         <v>6002</v>
@@ -6824,30 +6848,30 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W138" t="n">
-        <v>3</v>
-      </c>
-      <c r="X138" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W138" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y138" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060025</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C139" s="0" t="n">
         <v>3</v>
@@ -6860,27 +6884,27 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1</v>
-      </c>
-      <c r="X139" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W139" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y139" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060031</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>6003</v>
@@ -6896,27 +6920,27 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W140" t="n">
-        <v>1</v>
-      </c>
-      <c r="X140" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W140" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y140" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060032</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>6003</v>
@@ -6932,27 +6956,27 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W141" t="n">
-        <v>2</v>
-      </c>
-      <c r="X141" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W141" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060033</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>6003</v>
@@ -6968,27 +6992,27 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W142" t="n">
-        <v>2</v>
-      </c>
-      <c r="X142" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W142" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y142" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060034</v>
       </c>
       <c r="B143" s="0" t="n">
         <v>6003</v>
@@ -7004,30 +7028,30 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W143" t="n">
-        <v>3</v>
-      </c>
-      <c r="X143" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W143" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060035</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C144" s="0" t="n">
         <v>3</v>
@@ -7040,27 +7064,27 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W144" t="n">
-        <v>1</v>
-      </c>
-      <c r="X144" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W144" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y144" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060041</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>6004</v>
@@ -7076,27 +7100,27 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W145" t="n">
-        <v>1</v>
-      </c>
-      <c r="X145" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W145" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060042</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>6004</v>
@@ -7112,27 +7136,27 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W146" t="n">
-        <v>2</v>
-      </c>
-      <c r="X146" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y146" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060043</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>6004</v>
@@ -7148,27 +7172,27 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W147" t="n">
-        <v>2</v>
-      </c>
-      <c r="X147" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W147" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y147" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060044</v>
       </c>
       <c r="B148" s="0" t="n">
         <v>6004</v>
@@ -7184,30 +7208,30 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W148" t="n">
-        <v>3</v>
-      </c>
-      <c r="X148" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6004-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W148" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y148" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060045</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C149" s="0" t="n">
         <v>3</v>
@@ -7220,27 +7244,27 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W149" t="n">
-        <v>1</v>
-      </c>
-      <c r="X149" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6005-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W149" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y149" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060051</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>6005</v>
@@ -7256,27 +7280,27 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W150" t="n">
-        <v>1</v>
-      </c>
-      <c r="X150" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6005-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y150" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060052</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>6005</v>
@@ -7292,27 +7316,27 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W151" t="n">
-        <v>2</v>
-      </c>
-      <c r="X151" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6005-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W151" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y151" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060053</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>6005</v>
@@ -7328,27 +7352,27 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W152" t="n">
-        <v>2</v>
-      </c>
-      <c r="X152" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6005-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W152" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y152" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060054</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>6005</v>
@@ -7364,30 +7388,30 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W153" t="n">
-        <v>3</v>
-      </c>
-      <c r="X153" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物6005-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W153" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y153" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060055</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C154" s="0" t="n">
         <v>3</v>
@@ -7400,27 +7424,27 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1</v>
-      </c>
-      <c r="X154" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7001-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W154" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y154" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000070011</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>7001</v>
@@ -7436,27 +7460,27 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W155" t="n">
-        <v>1</v>
-      </c>
-      <c r="X155" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7001-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W155" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000070012</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>7001</v>
@@ -7472,27 +7496,27 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W156" t="n">
-        <v>2</v>
-      </c>
-      <c r="X156" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7001-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W156" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y156" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000070013</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>7001</v>
@@ -7508,27 +7532,27 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W157" t="n">
-        <v>2</v>
-      </c>
-      <c r="X157" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7001-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W157" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y157" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070014</v>
       </c>
       <c r="B158" s="0" t="n">
         <v>7001</v>
@@ -7544,30 +7568,30 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W158" t="n">
-        <v>3</v>
-      </c>
-      <c r="X158" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7001-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W158" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y158" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070015</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C159" s="0" t="n">
         <v>3</v>
@@ -7580,27 +7604,27 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W159" t="n">
-        <v>1</v>
-      </c>
-      <c r="X159" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7002-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W159" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y159" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070021</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>7002</v>
@@ -7616,27 +7640,27 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W160" t="n">
-        <v>1</v>
-      </c>
-      <c r="X160" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7002-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W160" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y160" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070022</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>7002</v>
@@ -7652,27 +7676,27 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W161" t="n">
-        <v>2</v>
-      </c>
-      <c r="X161" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7002-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W161" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070023</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>7002</v>
@@ -7688,27 +7712,27 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W162" t="n">
-        <v>2</v>
-      </c>
-      <c r="X162" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7002-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W162" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y162" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070024</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>7002</v>
@@ -7724,30 +7748,30 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W163" t="n">
-        <v>3</v>
-      </c>
-      <c r="X163" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7002-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W163" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y163" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070025</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C164" s="0" t="n">
         <v>3</v>
@@ -7760,27 +7784,27 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W164" t="n">
-        <v>1</v>
-      </c>
-      <c r="X164" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W164" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y164" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070031</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>7003</v>
@@ -7796,27 +7820,27 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W165" t="n">
-        <v>1</v>
-      </c>
-      <c r="X165" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W165" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y165" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070032</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>7003</v>
@@ -7832,27 +7856,27 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W166" t="n">
-        <v>2</v>
-      </c>
-      <c r="X166" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W166" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y166" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070033</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>7003</v>
@@ -7868,27 +7892,27 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W167" t="n">
-        <v>2</v>
-      </c>
-      <c r="X167" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W167" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y167" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070034</v>
       </c>
       <c r="B168" s="0" t="n">
         <v>7003</v>
@@ -7904,30 +7928,30 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W168" t="n">
-        <v>3</v>
-      </c>
-      <c r="X168" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7003-评级5</t>
+        <v>4</v>
+      </c>
+      <c r="W168" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y168" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070035</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C169" s="0" t="n">
         <v>3</v>
@@ -7940,27 +7964,27 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W169" t="n">
-        <v>1</v>
-      </c>
-      <c r="X169" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级1</t>
+        <v>5</v>
+      </c>
+      <c r="W169" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y169" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070041</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>7004</v>
@@ -7976,27 +8000,27 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W170" t="n">
-        <v>1</v>
-      </c>
-      <c r="X170" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级2</t>
+        <v>1</v>
+      </c>
+      <c r="W170" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y170" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级1</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070042</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>7004</v>
@@ -8012,27 +8036,27 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W171" t="n">
-        <v>2</v>
-      </c>
-      <c r="X171" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级3</t>
+        <v>2</v>
+      </c>
+      <c r="W171" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070043</v>
       </c>
       <c r="B172" s="0" t="n">
         <v>7004</v>
@@ -8048,27 +8072,27 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W172" t="n">
-        <v>2</v>
-      </c>
-      <c r="X172" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物7004-评级4</t>
+        <v>3</v>
+      </c>
+      <c r="W172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y172" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070044</v>
       </c>
       <c r="B173" s="0" t="n">
         <v>7004</v>
@@ -8084,19 +8108,55 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
+          <t>70000002,R,SR</t>
+        </is>
+      </c>
+      <c r="P173" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y173" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B174" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O174" s="0" t="inlineStr">
+        <is>
           <t>70000002,SR,SSR</t>
         </is>
       </c>
-      <c r="P173" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q173" s="0" t="n">
+      <c r="P174" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="W173" t="n">
-        <v>3</v>
-      </c>
-      <c r="X173" s="0" t="inlineStr">
+      <c r="W174" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y174" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1530,45 +1530,45 @@
       </c>
     </row>
     <row r="7" customFormat="1" s="1">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>10001</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="0" t="n">
         <v>9999</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="0" t="n">
         <v>10001</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X7" s="0" t="inlineStr">
         <is>
           <t>ui_book_1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" s="0" t="inlineStr">
         <is>
           <t>特殊NPC-监视之塔(新手引导,仅对话系统使用,无生物资源)</t>
         </is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_npc_info[NPC信息].xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y174"/>
+  <dimension ref="A1:Y178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.375" customWidth="1" style="3" min="1" max="2"/>
@@ -2400,514 +2400,593 @@
       </c>
     </row>
     <row r="21" customFormat="1" s="2">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="0" t="n">
+        <v>1040010001</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>104001</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N21" s="0" t="inlineStr">
+        <is>
+          <t>10100008&amp;10200008&amp;10300008&amp;11000006&amp;</t>
+        </is>
+      </c>
+      <c r="P21" s="0" t="n">
+        <v>1040010001</v>
+      </c>
+      <c r="S21" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Y21" s="0" t="inlineStr">
+        <is>
+          <t>盗贼</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="0" t="n">
+        <v>1040020001</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>104002</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
+          <t>10100010&amp;10200010&amp;10300010&amp;11000006&amp;</t>
+        </is>
+      </c>
+      <c r="P22" s="0" t="n">
+        <v>1040020001</v>
+      </c>
+      <c r="S22" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="Y22" s="0" t="inlineStr">
+        <is>
+          <t>双持战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="0" t="n">
+        <v>1041010001</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>104101</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N23" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11000012&amp;</t>
+        </is>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>1041010001</v>
+      </c>
+      <c r="S23" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>100004</v>
+      </c>
+      <c r="Y23" s="0" t="inlineStr">
+        <is>
+          <t>BOSS-大剑战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>10200009&amp;10300009&amp;11020022&amp;</t>
+        </is>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>1041020001</v>
+      </c>
+      <c r="S24" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T24" s="0" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="Y24" s="0" t="inlineStr">
+        <is>
+          <t>BOSS-大盾战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="2" t="n">
         <v>2000000001</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>1040001&amp;1050009&amp;1060003&amp;1030007&amp;</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>10200016&amp;10300016&amp;</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
         <v>2000000001</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="R25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>3,26,26,31,255&amp;6,140,26,51,255&amp;</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W21" s="2" t="n">
+      <c r="W25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>白剑伟</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="3">
-      <c r="A22" s="2" t="n">
+    <row r="26" ht="15" customHeight="1" s="3">
+      <c r="A26" s="2" t="n">
         <v>2000000002</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>5001</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>5050011&amp;5070005&amp;</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>50100003&amp;50200003&amp;50300002&amp;50500004&amp;</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>2000000002</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="R26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W22" s="2" t="n">
+      <c r="W26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>宛家伟</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="3">
-      <c r="A23" s="2" t="n">
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" s="2" t="n">
         <v>2000000003</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>4001</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="n">
+      <c r="C27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" s="0" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="0" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="0" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>4050007&amp;4060005&amp;4070010&amp;4080003&amp;4030005&amp;</t>
         </is>
       </c>
-      <c r="M23" s="0" t="inlineStr">
+      <c r="M27" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>40200006&amp;40300003&amp;41000004&amp;</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P27" s="2" t="n">
         <v>2000000003</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="R27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W23" s="0" t="n">
+      <c r="W27" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>雷神天尊斩</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="2" t="n">
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="n">
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" s="0" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="0" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>1030006&amp;1040002&amp;1050012&amp;1060002&amp;</t>
         </is>
       </c>
-      <c r="M24" s="0" t="inlineStr">
+      <c r="M28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>10300011&amp;10200011&amp;</t>
         </is>
       </c>
-      <c r="O24" s="0" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
+      <c r="O28" s="0" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
         <v>2000000004</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="R24" s="2" t="n"/>
-      <c r="U24" s="0" t="inlineStr">
+      <c r="R28" s="2" t="n"/>
+      <c r="U28" s="0" t="inlineStr">
         <is>
           <t>3,255,255,255,255&amp;6,178,38,38,255&amp;</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
-      <c r="W24" s="0" t="n">
+      <c r="W28" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>卡米莉娅</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" s="0" t="n">
-        <v>3000010011</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O25" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N</t>
-        </is>
-      </c>
-      <c r="P25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="3">
-      <c r="A26" s="0" t="n">
-        <v>3000010012</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O26" s="0" t="inlineStr">
-        <is>
-          <t>10000002,N,R</t>
-        </is>
-      </c>
-      <c r="P26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="W26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="3">
-      <c r="A27" s="0" t="n">
-        <v>3000010013</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O27" s="0" t="inlineStr">
-        <is>
-          <t>10000002,R</t>
-        </is>
-      </c>
-      <c r="P27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W27" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y27" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="0" t="n">
-        <v>3000010014</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="O28" s="0" t="inlineStr">
-        <is>
-          <t>10000002,R,SR</t>
-        </is>
-      </c>
-      <c r="P28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="W28" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y28" s="0" t="inlineStr">
-        <is>
-          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000010015</v>
+        <v>3000010011</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>1001</v>
@@ -2923,31 +3002,30 @@
       </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S29" s="0" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="W29" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1001-评级5</t>
+          <t>议会随机议员-生物1001-评级1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000010021</v>
+        <v>3000010012</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2960,30 +3038,30 @@
       </c>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级1</t>
+          <t>议会随机议员-生物1001-评级2</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="3">
       <c r="A31" s="0" t="n">
-        <v>3000010022</v>
+        <v>3000010013</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
@@ -2996,30 +3074,30 @@
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级2</t>
+          <t>议会随机议员-生物1001-评级3</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="3">
       <c r="A32" s="0" t="n">
-        <v>3000010023</v>
+        <v>3000010014</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -3032,30 +3110,30 @@
       </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级3</t>
+          <t>议会随机议员-生物1001-评级4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>3000010024</v>
+        <v>3000010015</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -3068,27 +3146,28 @@
       </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S33" s="0" t="inlineStr"/>
       <c r="W33" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级4</t>
+          <t>议会随机议员-生物1001-评级5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3000010025</v>
+        <v>3000010021</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>1002</v>
@@ -3104,30 +3183,30 @@
       </c>
       <c r="O34" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W34" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1002-评级5</t>
+          <t>议会随机议员-生物1002-评级1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>3000010031</v>
+        <v>3000010022</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3140,30 +3219,30 @@
       </c>
       <c r="O35" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级1</t>
+          <t>议会随机议员-生物1002-评级2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>3000010032</v>
+        <v>3000010023</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
@@ -3176,30 +3255,30 @@
       </c>
       <c r="O36" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W36" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级2</t>
+          <t>议会随机议员-生物1002-评级3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>3000010033</v>
+        <v>3000010024</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3212,30 +3291,30 @@
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W37" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级3</t>
+          <t>议会随机议员-生物1002-评级4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>3000010034</v>
+        <v>3000010025</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3248,27 +3327,27 @@
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级4</t>
+          <t>议会随机议员-生物1002-评级5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>3000010035</v>
+        <v>3000010031</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1003</v>
@@ -3284,30 +3363,30 @@
       </c>
       <c r="O39" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1003-评级5</t>
+          <t>议会随机议员-生物1003-评级1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>3000010041</v>
+        <v>3000010032</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3320,30 +3399,30 @@
       </c>
       <c r="O40" s="0" t="inlineStr">
         <is>
-          <t>10000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W40" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级1</t>
+          <t>议会随机议员-生物1003-评级2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>3000010042</v>
+        <v>3000010033</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3356,30 +3435,30 @@
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>10000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级2</t>
+          <t>议会随机议员-生物1003-评级3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>3000010043</v>
+        <v>3000010034</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3392,30 +3471,30 @@
       </c>
       <c r="O42" s="0" t="inlineStr">
         <is>
-          <t>10000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W42" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级3</t>
+          <t>议会随机议员-生物1003-评级4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3000010044</v>
+        <v>3000010035</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3428,27 +3507,27 @@
       </c>
       <c r="O43" s="0" t="inlineStr">
         <is>
-          <t>10000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级4</t>
+          <t>议会随机议员-生物1003-评级5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>3000010045</v>
+        <v>3000010041</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1004</v>
@@ -3464,30 +3543,30 @@
       </c>
       <c r="O44" s="0" t="inlineStr">
         <is>
-          <t>10000002,SR,SSR</t>
+          <t>10000002,N</t>
         </is>
       </c>
       <c r="P44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物1004-评级5</t>
+          <t>议会随机议员-生物1004-评级1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>3000020011</v>
+        <v>3000010042</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3500,30 +3579,30 @@
       </c>
       <c r="O45" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>10000002,N,R</t>
         </is>
       </c>
       <c r="P45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级1</t>
+          <t>议会随机议员-生物1004-评级2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>3000020012</v>
+        <v>3000010043</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>3</v>
@@ -3536,30 +3615,30 @@
       </c>
       <c r="O46" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>10000002,R</t>
         </is>
       </c>
       <c r="P46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级2</t>
+          <t>议会随机议员-生物1004-评级3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>3000020013</v>
+        <v>3000010044</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3572,30 +3651,30 @@
       </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>10000002,R,SR</t>
         </is>
       </c>
       <c r="P47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W47" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级3</t>
+          <t>议会随机议员-生物1004-评级4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>3000020014</v>
+        <v>3000010045</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>3</v>
@@ -3608,27 +3687,27 @@
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>10000002,SR,SSR</t>
         </is>
       </c>
       <c r="P48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级4</t>
+          <t>议会随机议员-生物1004-评级5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000020015</v>
+        <v>3000020011</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>2001</v>
@@ -3644,30 +3723,30 @@
       </c>
       <c r="O49" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W49" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2001-评级5</t>
+          <t>议会随机议员-生物2001-评级1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>3000020021</v>
+        <v>3000020012</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>3</v>
@@ -3680,30 +3759,30 @@
       </c>
       <c r="O50" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级1</t>
+          <t>议会随机议员-生物2001-评级2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>3000020022</v>
+        <v>3000020013</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>3</v>
@@ -3716,30 +3795,30 @@
       </c>
       <c r="O51" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级2</t>
+          <t>议会随机议员-生物2001-评级3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>3000020023</v>
+        <v>3000020014</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>3</v>
@@ -3752,30 +3831,30 @@
       </c>
       <c r="O52" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W52" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级3</t>
+          <t>议会随机议员-生物2001-评级4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>3000020024</v>
+        <v>3000020015</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -3788,27 +3867,27 @@
       </c>
       <c r="O53" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级4</t>
+          <t>议会随机议员-生物2001-评级5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>3000020025</v>
+        <v>3000020021</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2002</v>
@@ -3824,30 +3903,30 @@
       </c>
       <c r="O54" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2002-评级5</t>
+          <t>议会随机议员-生物2002-评级1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3000020031</v>
+        <v>3000020022</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
@@ -3860,30 +3939,30 @@
       </c>
       <c r="O55" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级1</t>
+          <t>议会随机议员-生物2002-评级2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>3000020032</v>
+        <v>3000020023</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>3</v>
@@ -3896,30 +3975,30 @@
       </c>
       <c r="O56" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级2</t>
+          <t>议会随机议员-生物2002-评级3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>3000020033</v>
+        <v>3000020024</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>3</v>
@@ -3932,30 +4011,30 @@
       </c>
       <c r="O57" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W57" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级3</t>
+          <t>议会随机议员-生物2002-评级4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>3000020034</v>
+        <v>3000020025</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>3</v>
@@ -3968,27 +4047,27 @@
       </c>
       <c r="O58" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级4</t>
+          <t>议会随机议员-生物2002-评级5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>3000020035</v>
+        <v>3000020031</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2003</v>
@@ -4004,30 +4083,30 @@
       </c>
       <c r="O59" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2003-评级5</t>
+          <t>议会随机议员-生物2003-评级1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>3000020041</v>
+        <v>3000020032</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>3</v>
@@ -4040,30 +4119,30 @@
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>20000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级1</t>
+          <t>议会随机议员-生物2003-评级2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3000020042</v>
+        <v>3000020033</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>3</v>
@@ -4076,30 +4155,30 @@
       </c>
       <c r="O61" s="0" t="inlineStr">
         <is>
-          <t>20000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级2</t>
+          <t>议会随机议员-生物2003-评级3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3000020043</v>
+        <v>3000020034</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>3</v>
@@ -4112,30 +4191,30 @@
       </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
-          <t>20000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W62" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级3</t>
+          <t>议会随机议员-生物2003-评级4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3000020044</v>
+        <v>3000020035</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>3</v>
@@ -4148,27 +4227,27 @@
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>20000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级4</t>
+          <t>议会随机议员-生物2003-评级5</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="3">
       <c r="A64" s="0" t="n">
-        <v>3000020045</v>
+        <v>3000020041</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>2004</v>
@@ -4184,30 +4263,30 @@
       </c>
       <c r="O64" s="0" t="inlineStr">
         <is>
-          <t>20000002,SR,SSR</t>
+          <t>20000002,N</t>
         </is>
       </c>
       <c r="P64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物2004-评级5</t>
+          <t>议会随机议员-生物2004-评级1</t>
         </is>
       </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="3">
       <c r="A65" s="0" t="n">
-        <v>3000030011</v>
+        <v>3000020042</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>3</v>
@@ -4220,30 +4299,30 @@
       </c>
       <c r="O65" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>20000002,N,R</t>
         </is>
       </c>
       <c r="P65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W65" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级1</t>
+          <t>议会随机议员-生物2004-评级2</t>
         </is>
       </c>
     </row>
     <row r="66" ht="12" customHeight="1" s="3">
       <c r="A66" s="0" t="n">
-        <v>3000030012</v>
+        <v>3000020043</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>3</v>
@@ -4256,30 +4335,30 @@
       </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>20000002,R</t>
         </is>
       </c>
       <c r="P66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级2</t>
+          <t>议会随机议员-生物2004-评级3</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="3">
       <c r="A67" s="0" t="n">
-        <v>3000030013</v>
+        <v>3000020044</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>3</v>
@@ -4292,30 +4371,30 @@
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>20000002,R,SR</t>
         </is>
       </c>
       <c r="P67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W67" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级3</t>
+          <t>议会随机议员-生物2004-评级4</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="3">
       <c r="A68" s="0" t="n">
-        <v>3000030014</v>
+        <v>3000020045</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>3</v>
@@ -4328,27 +4407,27 @@
       </c>
       <c r="O68" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>20000002,SR,SSR</t>
         </is>
       </c>
       <c r="P68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级4</t>
+          <t>议会随机议员-生物2004-评级5</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>3000030015</v>
+        <v>3000030011</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>3001</v>
@@ -4364,30 +4443,30 @@
       </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3001-评级5</t>
+          <t>议会随机议员-生物3001-评级1</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>3000030021</v>
+        <v>3000030012</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>3</v>
@@ -4400,30 +4479,30 @@
       </c>
       <c r="O70" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级1</t>
+          <t>议会随机议员-生物3001-评级2</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>3000030022</v>
+        <v>3000030013</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>3</v>
@@ -4436,30 +4515,30 @@
       </c>
       <c r="O71" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级2</t>
+          <t>议会随机议员-生物3001-评级3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="3">
       <c r="A72" s="0" t="n">
-        <v>3000030023</v>
+        <v>3000030014</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>3</v>
@@ -4472,30 +4551,30 @@
       </c>
       <c r="O72" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W72" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级3</t>
+          <t>议会随机议员-生物3001-评级4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3000030024</v>
+        <v>3000030015</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>3</v>
@@ -4508,27 +4587,27 @@
       </c>
       <c r="O73" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级4</t>
+          <t>议会随机议员-生物3001-评级5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3000030025</v>
+        <v>3000030021</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>3002</v>
@@ -4544,30 +4623,30 @@
       </c>
       <c r="O74" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3002-评级5</t>
+          <t>议会随机议员-生物3002-评级1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3000030031</v>
+        <v>3000030022</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>3</v>
@@ -4580,30 +4659,30 @@
       </c>
       <c r="O75" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级1</t>
+          <t>议会随机议员-生物3002-评级2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3000030032</v>
+        <v>3000030023</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>3</v>
@@ -4616,30 +4695,30 @@
       </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级2</t>
+          <t>议会随机议员-生物3002-评级3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3000030033</v>
+        <v>3000030024</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>3</v>
@@ -4652,30 +4731,30 @@
       </c>
       <c r="O77" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W77" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级3</t>
+          <t>议会随机议员-生物3002-评级4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3000030034</v>
+        <v>3000030025</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>3</v>
@@ -4688,27 +4767,27 @@
       </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级4</t>
+          <t>议会随机议员-生物3002-评级5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3000030035</v>
+        <v>3000030031</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>3003</v>
@@ -4724,30 +4803,30 @@
       </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3003-评级5</t>
+          <t>议会随机议员-生物3003-评级1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3000030041</v>
+        <v>3000030032</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>3</v>
@@ -4760,30 +4839,30 @@
       </c>
       <c r="O80" s="0" t="inlineStr">
         <is>
-          <t>30000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级1</t>
+          <t>议会随机议员-生物3003-评级2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>3000030042</v>
+        <v>3000030033</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>3</v>
@@ -4796,30 +4875,30 @@
       </c>
       <c r="O81" s="0" t="inlineStr">
         <is>
-          <t>30000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级2</t>
+          <t>议会随机议员-生物3003-评级3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>3000030043</v>
+        <v>3000030034</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>3</v>
@@ -4832,30 +4911,30 @@
       </c>
       <c r="O82" s="0" t="inlineStr">
         <is>
-          <t>30000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W82" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级3</t>
+          <t>议会随机议员-生物3003-评级4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>3000030044</v>
+        <v>3000030035</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>3</v>
@@ -4868,27 +4947,27 @@
       </c>
       <c r="O83" s="0" t="inlineStr">
         <is>
-          <t>30000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级4</t>
+          <t>议会随机议员-生物3003-评级5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>3000030045</v>
+        <v>3000030041</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>3004</v>
@@ -4904,30 +4983,30 @@
       </c>
       <c r="O84" s="0" t="inlineStr">
         <is>
-          <t>30000002,SR,SSR</t>
+          <t>30000002,N</t>
         </is>
       </c>
       <c r="P84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物3004-评级5</t>
+          <t>议会随机议员-生物3004-评级1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>3000040011</v>
+        <v>3000030042</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>3</v>
@@ -4940,30 +5019,30 @@
       </c>
       <c r="O85" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>30000002,N,R</t>
         </is>
       </c>
       <c r="P85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级1</t>
+          <t>议会随机议员-生物3004-评级2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>3000040012</v>
+        <v>3000030043</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>3</v>
@@ -4976,30 +5055,30 @@
       </c>
       <c r="O86" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>30000002,R</t>
         </is>
       </c>
       <c r="P86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级2</t>
+          <t>议会随机议员-生物3004-评级3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>3000040013</v>
+        <v>3000030044</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>3</v>
@@ -5012,30 +5091,30 @@
       </c>
       <c r="O87" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>30000002,R,SR</t>
         </is>
       </c>
       <c r="P87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W87" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级3</t>
+          <t>议会随机议员-生物3004-评级4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>3000040014</v>
+        <v>3000030045</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>4001</v>
+        <v>3004</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>3</v>
@@ -5048,27 +5127,27 @@
       </c>
       <c r="O88" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>30000002,SR,SSR</t>
         </is>
       </c>
       <c r="P88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级4</t>
+          <t>议会随机议员-生物3004-评级5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>3000040015</v>
+        <v>3000040011</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>4001</v>
@@ -5084,30 +5163,30 @@
       </c>
       <c r="O89" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4001-评级5</t>
+          <t>议会随机议员-生物4001-评级1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>3000040021</v>
+        <v>3000040012</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>3</v>
@@ -5120,30 +5199,30 @@
       </c>
       <c r="O90" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级1</t>
+          <t>议会随机议员-生物4001-评级2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>3000040022</v>
+        <v>3000040013</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>3</v>
@@ -5156,30 +5235,30 @@
       </c>
       <c r="O91" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级2</t>
+          <t>议会随机议员-生物4001-评级3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>3000040023</v>
+        <v>3000040014</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>3</v>
@@ -5192,30 +5271,30 @@
       </c>
       <c r="O92" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W92" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级3</t>
+          <t>议会随机议员-生物4001-评级4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>3000040024</v>
+        <v>3000040015</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>3</v>
@@ -5228,27 +5307,27 @@
       </c>
       <c r="O93" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级4</t>
+          <t>议会随机议员-生物4001-评级5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>3000040025</v>
+        <v>3000040021</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>4002</v>
@@ -5264,30 +5343,30 @@
       </c>
       <c r="O94" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4002-评级5</t>
+          <t>议会随机议员-生物4002-评级1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>3000040031</v>
+        <v>3000040022</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>3</v>
@@ -5300,30 +5379,30 @@
       </c>
       <c r="O95" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级1</t>
+          <t>议会随机议员-生物4002-评级2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>3000040032</v>
+        <v>3000040023</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>3</v>
@@ -5336,30 +5415,30 @@
       </c>
       <c r="O96" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级2</t>
+          <t>议会随机议员-生物4002-评级3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>3000040033</v>
+        <v>3000040024</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>3</v>
@@ -5372,30 +5451,30 @@
       </c>
       <c r="O97" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W97" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级3</t>
+          <t>议会随机议员-生物4002-评级4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>3000040034</v>
+        <v>3000040025</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>3</v>
@@ -5408,27 +5487,27 @@
       </c>
       <c r="O98" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级4</t>
+          <t>议会随机议员-生物4002-评级5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>3000040035</v>
+        <v>3000040031</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>4003</v>
@@ -5444,30 +5523,30 @@
       </c>
       <c r="O99" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4003-评级5</t>
+          <t>议会随机议员-生物4003-评级1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>3000040041</v>
+        <v>3000040032</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>3</v>
@@ -5480,30 +5559,30 @@
       </c>
       <c r="O100" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级1</t>
+          <t>议会随机议员-生物4003-评级2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>3000040042</v>
+        <v>3000040033</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>3</v>
@@ -5516,30 +5595,30 @@
       </c>
       <c r="O101" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级2</t>
+          <t>议会随机议员-生物4003-评级3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>3000040043</v>
+        <v>3000040034</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>3</v>
@@ -5552,30 +5631,30 @@
       </c>
       <c r="O102" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W102" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级3</t>
+          <t>议会随机议员-生物4003-评级4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>3000040044</v>
+        <v>3000040035</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>3</v>
@@ -5588,27 +5667,27 @@
       </c>
       <c r="O103" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级4</t>
+          <t>议会随机议员-生物4003-评级5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>3000040045</v>
+        <v>3000040041</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>4004</v>
@@ -5624,30 +5703,30 @@
       </c>
       <c r="O104" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4004-评级5</t>
+          <t>议会随机议员-生物4004-评级1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>3000040051</v>
+        <v>3000040042</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>3</v>
@@ -5660,30 +5739,30 @@
       </c>
       <c r="O105" s="0" t="inlineStr">
         <is>
-          <t>40000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W105" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级1</t>
+          <t>议会随机议员-生物4004-评级2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>3000040052</v>
+        <v>3000040043</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>3</v>
@@ -5696,30 +5775,30 @@
       </c>
       <c r="O106" s="0" t="inlineStr">
         <is>
-          <t>40000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级2</t>
+          <t>议会随机议员-生物4004-评级3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>3000040053</v>
+        <v>3000040044</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>3</v>
@@ -5732,30 +5811,30 @@
       </c>
       <c r="O107" s="0" t="inlineStr">
         <is>
-          <t>40000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W107" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级3</t>
+          <t>议会随机议员-生物4004-评级4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>3000040054</v>
+        <v>3000040045</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>3</v>
@@ -5768,27 +5847,27 @@
       </c>
       <c r="O108" s="0" t="inlineStr">
         <is>
-          <t>40000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级4</t>
+          <t>议会随机议员-生物4004-评级5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>3000040055</v>
+        <v>3000040051</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>4005</v>
@@ -5804,30 +5883,30 @@
       </c>
       <c r="O109" s="0" t="inlineStr">
         <is>
-          <t>40000002,SR,SSR</t>
+          <t>40000002,N</t>
         </is>
       </c>
       <c r="P109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物4005-评级5</t>
+          <t>议会随机议员-生物4005-评级1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>3000050011</v>
+        <v>3000040052</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>3</v>
@@ -5840,30 +5919,30 @@
       </c>
       <c r="O110" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>40000002,N,R</t>
         </is>
       </c>
       <c r="P110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级1</t>
+          <t>议会随机议员-生物4005-评级2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>3000050012</v>
+        <v>3000040053</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>3</v>
@@ -5876,30 +5955,30 @@
       </c>
       <c r="O111" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>40000002,R</t>
         </is>
       </c>
       <c r="P111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级2</t>
+          <t>议会随机议员-生物4005-评级3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000050013</v>
+        <v>3000040054</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>3</v>
@@ -5912,30 +5991,30 @@
       </c>
       <c r="O112" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>40000002,R,SR</t>
         </is>
       </c>
       <c r="P112" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W112" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级3</t>
+          <t>议会随机议员-生物4005-评级4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>3000050014</v>
+        <v>3000040055</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>3</v>
@@ -5948,27 +6027,27 @@
       </c>
       <c r="O113" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>40000002,SR,SSR</t>
         </is>
       </c>
       <c r="P113" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级4</t>
+          <t>议会随机议员-生物4005-评级5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>3000050015</v>
+        <v>3000050011</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>5001</v>
@@ -5984,30 +6063,30 @@
       </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P114" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5001-评级5</t>
+          <t>议会随机议员-生物5001-评级1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>3000050021</v>
+        <v>3000050012</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>3</v>
@@ -6020,30 +6099,30 @@
       </c>
       <c r="O115" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P115" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级1</t>
+          <t>议会随机议员-生物5001-评级2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>3000050022</v>
+        <v>3000050013</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>3</v>
@@ -6056,30 +6135,30 @@
       </c>
       <c r="O116" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P116" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级2</t>
+          <t>议会随机议员-生物5001-评级3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>3000050023</v>
+        <v>3000050014</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>3</v>
@@ -6092,30 +6171,30 @@
       </c>
       <c r="O117" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P117" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W117" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级3</t>
+          <t>议会随机议员-生物5001-评级4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>3000050024</v>
+        <v>3000050015</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>3</v>
@@ -6128,27 +6207,27 @@
       </c>
       <c r="O118" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P118" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级4</t>
+          <t>议会随机议员-生物5001-评级5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>3000050025</v>
+        <v>3000050021</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>5002</v>
@@ -6164,30 +6243,30 @@
       </c>
       <c r="O119" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P119" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5002-评级5</t>
+          <t>议会随机议员-生物5002-评级1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>3000050031</v>
+        <v>3000050022</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>3</v>
@@ -6200,30 +6279,30 @@
       </c>
       <c r="O120" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P120" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W120" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级1</t>
+          <t>议会随机议员-生物5002-评级2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>3000050032</v>
+        <v>3000050023</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>3</v>
@@ -6236,30 +6315,30 @@
       </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P121" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级2</t>
+          <t>议会随机议员-生物5002-评级3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>3000050033</v>
+        <v>3000050024</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>3</v>
@@ -6272,30 +6351,30 @@
       </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P122" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W122" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级3</t>
+          <t>议会随机议员-生物5002-评级4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>3000050034</v>
+        <v>3000050025</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>3</v>
@@ -6308,27 +6387,27 @@
       </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P123" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级4</t>
+          <t>议会随机议员-生物5002-评级5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>3000050035</v>
+        <v>3000050031</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>5003</v>
@@ -6344,30 +6423,30 @@
       </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5003-评级5</t>
+          <t>议会随机议员-生物5003-评级1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>3000050041</v>
+        <v>3000050032</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>3</v>
@@ -6380,30 +6459,30 @@
       </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
-          <t>50000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P125" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级1</t>
+          <t>议会随机议员-生物5003-评级2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>3000050042</v>
+        <v>3000050033</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>3</v>
@@ -6416,30 +6495,30 @@
       </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
-          <t>50000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级2</t>
+          <t>议会随机议员-生物5003-评级3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000050043</v>
+        <v>3000050034</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>3</v>
@@ -6452,30 +6531,30 @@
       </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
-          <t>50000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W127" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级3</t>
+          <t>议会随机议员-生物5003-评级4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000050044</v>
+        <v>3000050035</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>3</v>
@@ -6488,27 +6567,27 @@
       </c>
       <c r="O128" s="0" t="inlineStr">
         <is>
-          <t>50000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P128" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级4</t>
+          <t>议会随机议员-生物5003-评级5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000050045</v>
+        <v>3000050041</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>5004</v>
@@ -6524,30 +6603,30 @@
       </c>
       <c r="O129" s="0" t="inlineStr">
         <is>
-          <t>50000002,SR,SSR</t>
+          <t>50000002,N</t>
         </is>
       </c>
       <c r="P129" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W129" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物5004-评级5</t>
+          <t>议会随机议员-生物5004-评级1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000060011</v>
+        <v>3000050042</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>3</v>
@@ -6560,30 +6639,30 @@
       </c>
       <c r="O130" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>50000002,N,R</t>
         </is>
       </c>
       <c r="P130" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W130" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级1</t>
+          <t>议会随机议员-生物5004-评级2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000060012</v>
+        <v>3000050043</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C131" s="0" t="n">
         <v>3</v>
@@ -6596,30 +6675,30 @@
       </c>
       <c r="O131" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>50000002,R</t>
         </is>
       </c>
       <c r="P131" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W131" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级2</t>
+          <t>议会随机议员-生物5004-评级3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000060013</v>
+        <v>3000050044</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C132" s="0" t="n">
         <v>3</v>
@@ -6632,30 +6711,30 @@
       </c>
       <c r="O132" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>50000002,R,SR</t>
         </is>
       </c>
       <c r="P132" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W132" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级3</t>
+          <t>议会随机议员-生物5004-评级4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000060014</v>
+        <v>3000050045</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>6001</v>
+        <v>5004</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>3</v>
@@ -6668,27 +6747,27 @@
       </c>
       <c r="O133" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>50000002,SR,SSR</t>
         </is>
       </c>
       <c r="P133" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级4</t>
+          <t>议会随机议员-生物5004-评级5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000060015</v>
+        <v>3000060011</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>6001</v>
@@ -6704,30 +6783,30 @@
       </c>
       <c r="O134" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P134" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W134" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6001-评级5</t>
+          <t>议会随机议员-生物6001-评级1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000060021</v>
+        <v>3000060012</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>3</v>
@@ -6740,30 +6819,30 @@
       </c>
       <c r="O135" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P135" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W135" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级1</t>
+          <t>议会随机议员-生物6001-评级2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>3000060022</v>
+        <v>3000060013</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>3</v>
@@ -6776,30 +6855,30 @@
       </c>
       <c r="O136" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P136" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W136" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级2</t>
+          <t>议会随机议员-生物6001-评级3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>3000060023</v>
+        <v>3000060014</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>3</v>
@@ -6812,30 +6891,30 @@
       </c>
       <c r="O137" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P137" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W137" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级3</t>
+          <t>议会随机议员-生物6001-评级4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>3000060024</v>
+        <v>3000060015</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>3</v>
@@ -6848,27 +6927,27 @@
       </c>
       <c r="O138" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P138" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W138" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y138" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级4</t>
+          <t>议会随机议员-生物6001-评级5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>3000060025</v>
+        <v>3000060021</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>6002</v>
@@ -6884,30 +6963,30 @@
       </c>
       <c r="O139" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P139" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W139" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y139" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6002-评级5</t>
+          <t>议会随机议员-生物6002-评级1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>3000060031</v>
+        <v>3000060022</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C140" s="0" t="n">
         <v>3</v>
@@ -6920,30 +6999,30 @@
       </c>
       <c r="O140" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P140" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W140" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y140" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级1</t>
+          <t>议会随机议员-生物6002-评级2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>3000060032</v>
+        <v>3000060023</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C141" s="0" t="n">
         <v>3</v>
@@ -6956,30 +7035,30 @@
       </c>
       <c r="O141" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P141" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W141" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y141" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级2</t>
+          <t>议会随机议员-生物6002-评级3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>3000060033</v>
+        <v>3000060024</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C142" s="0" t="n">
         <v>3</v>
@@ -6992,30 +7071,30 @@
       </c>
       <c r="O142" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P142" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W142" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y142" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级3</t>
+          <t>议会随机议员-生物6002-评级4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>3000060034</v>
+        <v>3000060025</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C143" s="0" t="n">
         <v>3</v>
@@ -7028,27 +7107,27 @@
       </c>
       <c r="O143" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P143" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W143" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y143" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级4</t>
+          <t>议会随机议员-生物6002-评级5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>3000060035</v>
+        <v>3000060031</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>6003</v>
@@ -7064,30 +7143,30 @@
       </c>
       <c r="O144" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P144" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W144" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y144" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6003-评级5</t>
+          <t>议会随机议员-生物6003-评级1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>3000060041</v>
+        <v>3000060032</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C145" s="0" t="n">
         <v>3</v>
@@ -7100,30 +7179,30 @@
       </c>
       <c r="O145" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P145" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W145" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y145" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级1</t>
+          <t>议会随机议员-生物6003-评级2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>3000060042</v>
+        <v>3000060033</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C146" s="0" t="n">
         <v>3</v>
@@ -7136,30 +7215,30 @@
       </c>
       <c r="O146" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P146" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W146" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y146" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级2</t>
+          <t>议会随机议员-生物6003-评级3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>3000060043</v>
+        <v>3000060034</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C147" s="0" t="n">
         <v>3</v>
@@ -7172,30 +7251,30 @@
       </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P147" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W147" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y147" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级3</t>
+          <t>议会随机议员-生物6003-评级4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>3000060044</v>
+        <v>3000060035</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C148" s="0" t="n">
         <v>3</v>
@@ -7208,27 +7287,27 @@
       </c>
       <c r="O148" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P148" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W148" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y148" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级4</t>
+          <t>议会随机议员-生物6003-评级5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>3000060045</v>
+        <v>3000060041</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>6004</v>
@@ -7244,30 +7323,30 @@
       </c>
       <c r="O149" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P149" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W149" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y149" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6004-评级5</t>
+          <t>议会随机议员-生物6004-评级1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>3000060051</v>
+        <v>3000060042</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C150" s="0" t="n">
         <v>3</v>
@@ -7280,30 +7359,30 @@
       </c>
       <c r="O150" s="0" t="inlineStr">
         <is>
-          <t>60000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P150" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y150" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级1</t>
+          <t>议会随机议员-生物6004-评级2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>3000060052</v>
+        <v>3000060043</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C151" s="0" t="n">
         <v>3</v>
@@ -7316,30 +7395,30 @@
       </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
-          <t>60000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P151" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W151" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y151" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级2</t>
+          <t>议会随机议员-生物6004-评级3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>3000060053</v>
+        <v>3000060044</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C152" s="0" t="n">
         <v>3</v>
@@ -7352,30 +7431,30 @@
       </c>
       <c r="O152" s="0" t="inlineStr">
         <is>
-          <t>60000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P152" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W152" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y152" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级3</t>
+          <t>议会随机议员-生物6004-评级4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>3000060054</v>
+        <v>3000060045</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C153" s="0" t="n">
         <v>3</v>
@@ -7388,27 +7467,27 @@
       </c>
       <c r="O153" s="0" t="inlineStr">
         <is>
-          <t>60000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P153" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W153" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y153" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级4</t>
+          <t>议会随机议员-生物6004-评级5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>3000060055</v>
+        <v>3000060051</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>6005</v>
@@ -7424,30 +7503,30 @@
       </c>
       <c r="O154" s="0" t="inlineStr">
         <is>
-          <t>60000002,SR,SSR</t>
+          <t>60000002,N</t>
         </is>
       </c>
       <c r="P154" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W154" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y154" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物6005-评级5</t>
+          <t>议会随机议员-生物6005-评级1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>3000070011</v>
+        <v>3000060052</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C155" s="0" t="n">
         <v>3</v>
@@ -7460,30 +7539,30 @@
       </c>
       <c r="O155" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>60000002,N,R</t>
         </is>
       </c>
       <c r="P155" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W155" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y155" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级1</t>
+          <t>议会随机议员-生物6005-评级2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>3000070012</v>
+        <v>3000060053</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C156" s="0" t="n">
         <v>3</v>
@@ -7496,30 +7575,30 @@
       </c>
       <c r="O156" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>60000002,R</t>
         </is>
       </c>
       <c r="P156" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W156" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y156" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级2</t>
+          <t>议会随机议员-生物6005-评级3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>3000070013</v>
+        <v>3000060054</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C157" s="0" t="n">
         <v>3</v>
@@ -7532,30 +7611,30 @@
       </c>
       <c r="O157" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>60000002,R,SR</t>
         </is>
       </c>
       <c r="P157" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W157" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y157" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级3</t>
+          <t>议会随机议员-生物6005-评级4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>3000070014</v>
+        <v>3000060055</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>7001</v>
+        <v>6005</v>
       </c>
       <c r="C158" s="0" t="n">
         <v>3</v>
@@ -7568,27 +7647,27 @@
       </c>
       <c r="O158" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>60000002,SR,SSR</t>
         </is>
       </c>
       <c r="P158" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W158" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y158" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级4</t>
+          <t>议会随机议员-生物6005-评级5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>3000070015</v>
+        <v>3000070011</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>7001</v>
@@ -7604,30 +7683,30 @@
       </c>
       <c r="O159" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P159" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W159" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y159" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7001-评级5</t>
+          <t>议会随机议员-生物7001-评级1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>3000070021</v>
+        <v>3000070012</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C160" s="0" t="n">
         <v>3</v>
@@ -7640,30 +7719,30 @@
       </c>
       <c r="O160" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P160" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W160" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y160" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级1</t>
+          <t>议会随机议员-生物7001-评级2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>3000070022</v>
+        <v>3000070013</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C161" s="0" t="n">
         <v>3</v>
@@ -7676,30 +7755,30 @@
       </c>
       <c r="O161" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P161" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W161" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y161" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级2</t>
+          <t>议会随机议员-生物7001-评级3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>3000070023</v>
+        <v>3000070014</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C162" s="0" t="n">
         <v>3</v>
@@ -7712,30 +7791,30 @@
       </c>
       <c r="O162" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P162" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W162" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y162" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级3</t>
+          <t>议会随机议员-生物7001-评级4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>3000070024</v>
+        <v>3000070015</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C163" s="0" t="n">
         <v>3</v>
@@ -7748,27 +7827,27 @@
       </c>
       <c r="O163" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P163" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W163" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y163" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级4</t>
+          <t>议会随机议员-生物7001-评级5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000070025</v>
+        <v>3000070021</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>7002</v>
@@ -7784,30 +7863,30 @@
       </c>
       <c r="O164" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P164" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W164" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y164" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7002-评级5</t>
+          <t>议会随机议员-生物7002-评级1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000070031</v>
+        <v>3000070022</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C165" s="0" t="n">
         <v>3</v>
@@ -7820,30 +7899,30 @@
       </c>
       <c r="O165" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P165" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W165" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y165" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级1</t>
+          <t>议会随机议员-生物7002-评级2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000070032</v>
+        <v>3000070023</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C166" s="0" t="n">
         <v>3</v>
@@ -7856,30 +7935,30 @@
       </c>
       <c r="O166" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P166" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W166" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y166" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级2</t>
+          <t>议会随机议员-生物7002-评级3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000070033</v>
+        <v>3000070024</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C167" s="0" t="n">
         <v>3</v>
@@ -7892,30 +7971,30 @@
       </c>
       <c r="O167" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P167" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q167" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W167" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y167" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级3</t>
+          <t>议会随机议员-生物7002-评级4</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000070034</v>
+        <v>3000070025</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C168" s="0" t="n">
         <v>3</v>
@@ -7928,27 +8007,27 @@
       </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P168" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q168" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W168" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y168" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级4</t>
+          <t>议会随机议员-生物7002-评级5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000070035</v>
+        <v>3000070031</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>7003</v>
@@ -7964,30 +8043,30 @@
       </c>
       <c r="O169" s="0" t="inlineStr">
         <is>
-          <t>70000002,SR,SSR</t>
+          <t>70000002,N</t>
         </is>
       </c>
       <c r="P169" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q169" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W169" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y169" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7003-评级5</t>
+          <t>议会随机议员-生物7003-评级1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000070041</v>
+        <v>3000070032</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C170" s="0" t="n">
         <v>3</v>
@@ -8000,30 +8079,30 @@
       </c>
       <c r="O170" s="0" t="inlineStr">
         <is>
-          <t>70000002,N</t>
+          <t>70000002,N,R</t>
         </is>
       </c>
       <c r="P170" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q170" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W170" s="0" t="n">
         <v>1</v>
       </c>
       <c r="Y170" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级1</t>
+          <t>议会随机议员-生物7003-评级2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000070042</v>
+        <v>3000070033</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C171" s="0" t="n">
         <v>3</v>
@@ -8036,30 +8115,30 @@
       </c>
       <c r="O171" s="0" t="inlineStr">
         <is>
-          <t>70000002,N,R</t>
+          <t>70000002,R</t>
         </is>
       </c>
       <c r="P171" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q171" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W171" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y171" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级2</t>
+          <t>议会随机议员-生物7003-评级3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000070043</v>
+        <v>3000070034</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C172" s="0" t="n">
         <v>3</v>
@@ -8072,30 +8151,30 @@
       </c>
       <c r="O172" s="0" t="inlineStr">
         <is>
-          <t>70000002,R</t>
+          <t>70000002,R,SR</t>
         </is>
       </c>
       <c r="P172" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q172" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W172" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y172" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级3</t>
+          <t>议会随机议员-生物7003-评级4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000070044</v>
+        <v>3000070035</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C173" s="0" t="n">
         <v>3</v>
@@ -8108,27 +8187,27 @@
       </c>
       <c r="O173" s="0" t="inlineStr">
         <is>
-          <t>70000002,R,SR</t>
+          <t>70000002,SR,SSR</t>
         </is>
       </c>
       <c r="P173" s="0" t="n">
         <v>0</v>
       </c>
       <c r="Q173" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W173" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y173" s="0" t="inlineStr">
         <is>
-          <t>议会随机议员-生物7004-评级4</t>
+          <t>议会随机议员-生物7003-评级5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000070045</v>
+        <v>3000070041</v>
       </c>
       <c r="B174" s="0" t="n">
         <v>7004</v>
@@ -8144,19 +8223,163 @@
       </c>
       <c r="O174" s="0" t="inlineStr">
         <is>
+          <t>70000002,N</t>
+        </is>
+      </c>
+      <c r="P174" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y174" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="n">
+        <v>3000070042</v>
+      </c>
+      <c r="B175" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O175" s="0" t="inlineStr">
+        <is>
+          <t>70000002,N,R</t>
+        </is>
+      </c>
+      <c r="P175" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y175" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="n">
+        <v>3000070043</v>
+      </c>
+      <c r="B176" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D176" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O176" s="0" t="inlineStr">
+        <is>
+          <t>70000002,R</t>
+        </is>
+      </c>
+      <c r="P176" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y176" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级3</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="n">
+        <v>3000070044</v>
+      </c>
+      <c r="B177" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O177" s="0" t="inlineStr">
+        <is>
+          <t>70000002,R,SR</t>
+        </is>
+      </c>
+      <c r="P177" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y177" s="0" t="inlineStr">
+        <is>
+          <t>议会随机议员-生物7004-评级4</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="n">
+        <v>3000070045</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="O178" s="0" t="inlineStr">
+        <is>
           <t>70000002,SR,SSR</t>
         </is>
       </c>
-      <c r="P174" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" s="0" t="n">
+      <c r="P178" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="W174" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y174" s="0" t="inlineStr">
+      <c r="W178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y178" s="0" t="inlineStr">
         <is>
           <t>议会随机议员-生物7004-评级5</t>
         </is>
